--- a/customers/cpall/excel_templates/logistic_plan_รอบเช้าต่างจังหวัด.xlsx
+++ b/customers/cpall/excel_templates/logistic_plan_รอบเช้าต่างจังหวัด.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User7\Desktop\PRD-Plan\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE11151-F012-43CF-B5CC-B4CF4BB18762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C2B910-0C0E-44BB-97D5-787E99529B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="582" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="582" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บางบัวทอง-ผลิต" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'บางบัวทอง-ผลิต (2)'!$B$10:$R$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'บางบัวทอง-ผลิต (4)'!$B$10:$R$54</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,10 +35,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -46,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
@@ -54,7 +51,7 @@
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2639,9 +2636,6 @@
     <xf numFmtId="3" fontId="91" fillId="2" borderId="31" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="4" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="52" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2654,22 +2648,52 @@
     <xf numFmtId="3" fontId="53" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="89" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="85" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="85" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="86" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="86" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="86" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="86" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2678,10 +2702,181 @@
     <xf numFmtId="0" fontId="88" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="10" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="7" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="7" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2723,274 +2918,16 @@
     <xf numFmtId="0" fontId="58" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="7" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="10" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="7" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="89" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="86" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="63" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="68" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="68" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="53" fillId="12" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="53" fillId="12" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3041,29 +2978,119 @@
     <xf numFmtId="0" fontId="35" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="68" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="68" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="53" fillId="12" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="53" fillId="12" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="63" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3074,19 +3101,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3104,40 +3125,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3147,6 +3141,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3240,9 +3237,6 @@
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_ClassificationId">
@@ -3595,34 +3589,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:AK57"/>
-  <sheetFormatPr defaultColWidth="5.69921875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="30" customWidth="1"/>
     <col min="2" max="2" width="18" style="3" customWidth="1"/>
-    <col min="3" max="3" width="134.19921875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="23.19921875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.3984375" style="3" customWidth="1"/>
-    <col min="6" max="10" width="35.09765625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="28.59765625" style="3" customWidth="1"/>
-    <col min="12" max="14" width="35.09765625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="35.09765625" style="29" customWidth="1"/>
-    <col min="16" max="16" width="29.69921875" style="29" customWidth="1"/>
-    <col min="17" max="17" width="34.19921875" style="29" customWidth="1"/>
-    <col min="18" max="18" width="34.19921875" style="36" customWidth="1"/>
+    <col min="3" max="3" width="134.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.375" style="3" customWidth="1"/>
+    <col min="6" max="10" width="35.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="28.625" style="3" customWidth="1"/>
+    <col min="12" max="14" width="35.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="35.125" style="29" customWidth="1"/>
+    <col min="16" max="16" width="29.75" style="29" customWidth="1"/>
+    <col min="17" max="17" width="34.25" style="29" customWidth="1"/>
+    <col min="18" max="18" width="34.25" style="36" customWidth="1"/>
     <col min="19" max="19" width="26" style="29" customWidth="1"/>
-    <col min="20" max="20" width="25.19921875" style="127" customWidth="1"/>
-    <col min="21" max="21" width="8.3984375" style="67" customWidth="1"/>
-    <col min="22" max="22" width="27.8984375" style="206" customWidth="1"/>
-    <col min="23" max="23" width="24.8984375" style="206" customWidth="1"/>
-    <col min="24" max="24" width="27.8984375" style="206" customWidth="1"/>
+    <col min="20" max="20" width="25.25" style="127" customWidth="1"/>
+    <col min="21" max="21" width="8.375" style="67" customWidth="1"/>
+    <col min="22" max="22" width="27.875" style="206" customWidth="1"/>
+    <col min="23" max="23" width="24.875" style="206" customWidth="1"/>
+    <col min="24" max="24" width="27.875" style="206" customWidth="1"/>
     <col min="25" max="25" width="22" style="206" customWidth="1"/>
-    <col min="26" max="26" width="27.8984375" style="206" customWidth="1"/>
-    <col min="27" max="36" width="5.69921875" style="3"/>
-    <col min="37" max="37" width="13.69921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="5.69921875" style="3"/>
+    <col min="26" max="26" width="27.875" style="206" customWidth="1"/>
+    <col min="27" max="36" width="5.75" style="3"/>
+    <col min="37" max="37" width="13.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="5.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:37" s="30" customFormat="1" ht="31.95" customHeight="1">
+    <row r="4" spans="2:37" s="30" customFormat="1" ht="31.9" customHeight="1">
       <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -3633,8 +3627,8 @@
       <c r="I4" s="37"/>
       <c r="J4" s="28"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="287"/>
-      <c r="M4" s="287"/>
+      <c r="L4" s="298"/>
+      <c r="M4" s="298"/>
       <c r="N4" s="54"/>
       <c r="O4" s="55"/>
       <c r="P4" s="55"/>
@@ -3730,39 +3724,39 @@
       <c r="O8" s="36"/>
     </row>
     <row r="9" spans="2:37" ht="15" customHeight="1">
-      <c r="E9" s="304" t="s">
+      <c r="E9" s="313" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="304"/>
-      <c r="G9" s="304"/>
-      <c r="H9" s="304"/>
-      <c r="I9" s="304"/>
-      <c r="J9" s="304"/>
-      <c r="K9" s="304"/>
-      <c r="L9" s="304"/>
-      <c r="M9" s="304"/>
-      <c r="N9" s="304"/>
-      <c r="O9" s="304"/>
-      <c r="P9" s="304"/>
-    </row>
-    <row r="10" spans="2:37" s="30" customFormat="1" ht="71.400000000000006" customHeight="1" thickBot="1">
-      <c r="B10" s="292" t="s">
+      <c r="F9" s="313"/>
+      <c r="G9" s="313"/>
+      <c r="H9" s="313"/>
+      <c r="I9" s="313"/>
+      <c r="J9" s="313"/>
+      <c r="K9" s="313"/>
+      <c r="L9" s="313"/>
+      <c r="M9" s="313"/>
+      <c r="N9" s="313"/>
+      <c r="O9" s="313"/>
+      <c r="P9" s="313"/>
+    </row>
+    <row r="10" spans="2:37" s="30" customFormat="1" ht="71.45" customHeight="1" thickBot="1">
+      <c r="B10" s="301" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="292"/>
-      <c r="D10" s="292"/>
-      <c r="E10" s="304"/>
-      <c r="F10" s="304"/>
-      <c r="G10" s="304"/>
-      <c r="H10" s="304"/>
-      <c r="I10" s="304"/>
-      <c r="J10" s="304"/>
-      <c r="K10" s="304"/>
-      <c r="L10" s="304"/>
-      <c r="M10" s="304"/>
-      <c r="N10" s="304"/>
-      <c r="O10" s="304"/>
-      <c r="P10" s="304"/>
+      <c r="C10" s="301"/>
+      <c r="D10" s="301"/>
+      <c r="E10" s="313"/>
+      <c r="F10" s="313"/>
+      <c r="G10" s="313"/>
+      <c r="H10" s="313"/>
+      <c r="I10" s="313"/>
+      <c r="J10" s="313"/>
+      <c r="K10" s="313"/>
+      <c r="L10" s="313"/>
+      <c r="M10" s="313"/>
+      <c r="N10" s="313"/>
+      <c r="O10" s="313"/>
+      <c r="P10" s="313"/>
       <c r="Q10" s="197"/>
       <c r="R10" s="197"/>
       <c r="S10" s="29"/>
@@ -3776,9 +3770,9 @@
       <c r="AA10" s="35"/>
     </row>
     <row r="11" spans="2:37" s="30" customFormat="1" ht="3" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="293"/>
-      <c r="C11" s="293"/>
-      <c r="D11" s="293"/>
+      <c r="B11" s="302"/>
+      <c r="C11" s="302"/>
+      <c r="D11" s="302"/>
       <c r="E11" s="198"/>
       <c r="F11" s="198"/>
       <c r="G11" s="198"/>
@@ -3797,108 +3791,108 @@
       <c r="T11" s="128"/>
       <c r="U11" s="34"/>
       <c r="V11" s="206"/>
-      <c r="W11" s="266"/>
-      <c r="X11" s="267"/>
-      <c r="Y11" s="267"/>
-      <c r="Z11" s="267"/>
-      <c r="AA11" s="268"/>
-    </row>
-    <row r="12" spans="2:37" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
-      <c r="B12" s="322" t="s">
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
+      <c r="Y11" s="333"/>
+      <c r="Z11" s="333"/>
+      <c r="AA11" s="334"/>
+    </row>
+    <row r="12" spans="2:37" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
+      <c r="B12" s="282" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="323"/>
-      <c r="D12" s="328" t="s">
+      <c r="C12" s="283"/>
+      <c r="D12" s="288" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="331" t="s">
+      <c r="E12" s="291" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="332"/>
-      <c r="G12" s="333" t="s">
+      <c r="F12" s="292"/>
+      <c r="G12" s="293" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="334"/>
-      <c r="I12" s="313" t="s">
+      <c r="H12" s="294"/>
+      <c r="I12" s="273" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="314"/>
-      <c r="K12" s="298" t="s">
+      <c r="J12" s="274"/>
+      <c r="K12" s="307" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="299"/>
-      <c r="M12" s="300"/>
-      <c r="N12" s="308" t="s">
+      <c r="L12" s="308"/>
+      <c r="M12" s="309"/>
+      <c r="N12" s="317" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="309"/>
-      <c r="P12" s="310"/>
-      <c r="Q12" s="315" t="s">
+      <c r="O12" s="318"/>
+      <c r="P12" s="319"/>
+      <c r="Q12" s="275" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="316"/>
-      <c r="S12" s="319" t="s">
+      <c r="R12" s="276"/>
+      <c r="S12" s="279" t="s">
         <v>78</v>
       </c>
-      <c r="T12" s="335" t="s">
+      <c r="T12" s="295" t="s">
         <v>79</v>
       </c>
-      <c r="V12" s="262" t="s">
+      <c r="V12" s="345" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="260" t="s">
+      <c r="W12" s="269" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="258" t="s">
+      <c r="X12" s="343" t="s">
         <v>85</v>
       </c>
-      <c r="Y12" s="260" t="s">
+      <c r="Y12" s="269" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="264" t="s">
+      <c r="Z12" s="330" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:37" s="30" customFormat="1" ht="60.6" customHeight="1" thickBot="1">
-      <c r="B13" s="324"/>
-      <c r="C13" s="325"/>
-      <c r="D13" s="329"/>
-      <c r="E13" s="311" t="s">
+      <c r="B13" s="284"/>
+      <c r="C13" s="285"/>
+      <c r="D13" s="289"/>
+      <c r="E13" s="271" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="312"/>
-      <c r="G13" s="294" t="s">
+      <c r="F13" s="272"/>
+      <c r="G13" s="303" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="295"/>
-      <c r="I13" s="296" t="s">
+      <c r="H13" s="304"/>
+      <c r="I13" s="305" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="297"/>
-      <c r="K13" s="301" t="s">
+      <c r="J13" s="306"/>
+      <c r="K13" s="310" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="302"/>
-      <c r="M13" s="303"/>
-      <c r="N13" s="305" t="s">
+      <c r="L13" s="311"/>
+      <c r="M13" s="312"/>
+      <c r="N13" s="314" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="306"/>
-      <c r="P13" s="307"/>
-      <c r="Q13" s="317"/>
-      <c r="R13" s="318"/>
-      <c r="S13" s="320"/>
-      <c r="T13" s="336"/>
-      <c r="V13" s="263"/>
-      <c r="W13" s="261"/>
-      <c r="X13" s="259"/>
-      <c r="Y13" s="261"/>
-      <c r="Z13" s="265"/>
+      <c r="O13" s="315"/>
+      <c r="P13" s="316"/>
+      <c r="Q13" s="277"/>
+      <c r="R13" s="278"/>
+      <c r="S13" s="280"/>
+      <c r="T13" s="296"/>
+      <c r="V13" s="346"/>
+      <c r="W13" s="270"/>
+      <c r="X13" s="344"/>
+      <c r="Y13" s="270"/>
+      <c r="Z13" s="331"/>
     </row>
     <row r="14" spans="2:37" s="30" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B14" s="326"/>
-      <c r="C14" s="327"/>
-      <c r="D14" s="330"/>
+      <c r="B14" s="286"/>
+      <c r="C14" s="287"/>
+      <c r="D14" s="290"/>
       <c r="E14" s="182" t="s">
         <v>0</v>
       </c>
@@ -3941,8 +3935,8 @@
       <c r="R14" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="S14" s="321"/>
-      <c r="T14" s="337"/>
+      <c r="S14" s="281"/>
+      <c r="T14" s="297"/>
       <c r="V14" s="207"/>
       <c r="W14" s="208"/>
       <c r="X14" s="209"/>
@@ -3952,14 +3946,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B15" s="288">
+    <row r="15" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B15" s="258">
         <v>1</v>
       </c>
       <c r="C15" s="199" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="299">
         <v>36</v>
       </c>
       <c r="E15" s="235"/>
@@ -3974,18 +3968,18 @@
       <c r="N15" s="236"/>
       <c r="O15" s="237"/>
       <c r="P15" s="237"/>
-      <c r="Q15" s="254">
+      <c r="Q15" s="260">
         <f>SUM(E15:P15)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="256">
+      <c r="R15" s="264">
         <f>'บางบัวทอง-รถ'!C10</f>
         <v>0</v>
       </c>
-      <c r="S15" s="250">
+      <c r="S15" s="249">
         <v>260</v>
       </c>
-      <c r="T15" s="252">
+      <c r="T15" s="251">
         <f>SUM(S15-Q15)</f>
         <v>260</v>
       </c>
@@ -4014,12 +4008,12 @@
         <v>32 P</v>
       </c>
     </row>
-    <row r="16" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B16" s="289"/>
+    <row r="16" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B16" s="259"/>
       <c r="C16" s="203" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="291"/>
+      <c r="D16" s="300"/>
       <c r="E16" s="238" t="str">
         <f t="shared" ref="E16:P16" si="1">IF(E15=0, "", IF(MOD(E15, $D$15) = 0, E15 / $D$15, IF(INT(E15 / $D$15) = 0, MOD(E15, $D$15) &amp; " P", INT(E15 / $D$15) &amp; " + " &amp; MOD(E15, $D$15) &amp; " P")))</f>
         <v/>
@@ -4068,10 +4062,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="255"/>
-      <c r="R16" s="257"/>
-      <c r="S16" s="251"/>
-      <c r="T16" s="253"/>
+      <c r="Q16" s="261"/>
+      <c r="R16" s="263"/>
+      <c r="S16" s="250"/>
+      <c r="T16" s="252"/>
       <c r="V16" s="215"/>
       <c r="W16" s="216"/>
       <c r="X16" s="217"/>
@@ -4081,14 +4075,14 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B17" s="288">
+    <row r="17" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B17" s="258">
         <v>2</v>
       </c>
       <c r="C17" s="200" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="288">
+      <c r="D17" s="258">
         <v>32</v>
       </c>
       <c r="E17" s="235"/>
@@ -4103,18 +4097,18 @@
       <c r="N17" s="236"/>
       <c r="O17" s="237"/>
       <c r="P17" s="237"/>
-      <c r="Q17" s="254">
+      <c r="Q17" s="260">
         <f>SUM(E17:P17)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="256">
+      <c r="R17" s="264">
         <f>'บางบัวทอง-รถ'!C11</f>
         <v>0</v>
       </c>
-      <c r="S17" s="250">
+      <c r="S17" s="249">
         <v>650</v>
       </c>
-      <c r="T17" s="252">
+      <c r="T17" s="251">
         <f>SUM(S17-Q17)</f>
         <v>650</v>
       </c>
@@ -4143,12 +4137,12 @@
         <v>4 + 1 P</v>
       </c>
     </row>
-    <row r="18" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B18" s="289"/>
+    <row r="18" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B18" s="259"/>
       <c r="C18" s="204" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="289"/>
+      <c r="D18" s="259"/>
       <c r="E18" s="238" t="str">
         <f>IF(E17=0, "", IF(MOD(E17, $D$17) = 0, E17 / $D$17, IF(INT(E17 / $D$17) = 0, MOD(E17, $D$17) &amp; " P", INT(E17 / $D$17) &amp; " + " &amp; MOD(E17, $D$17) &amp; " P")))</f>
         <v/>
@@ -4197,10 +4191,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="255"/>
-      <c r="R18" s="257"/>
-      <c r="S18" s="251"/>
-      <c r="T18" s="253"/>
+      <c r="Q18" s="261"/>
+      <c r="R18" s="263"/>
+      <c r="S18" s="250"/>
+      <c r="T18" s="252"/>
       <c r="V18" s="215"/>
       <c r="W18" s="216"/>
       <c r="X18" s="217"/>
@@ -4210,14 +4204,14 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B19" s="288">
+    <row r="19" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B19" s="258">
         <v>3</v>
       </c>
       <c r="C19" s="200" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="288">
+      <c r="D19" s="258">
         <v>36</v>
       </c>
       <c r="E19" s="240"/>
@@ -4232,18 +4226,18 @@
       <c r="N19" s="241"/>
       <c r="O19" s="243"/>
       <c r="P19" s="243"/>
-      <c r="Q19" s="254">
+      <c r="Q19" s="260">
         <f>SUM(E19:P19)</f>
         <v>0</v>
       </c>
-      <c r="R19" s="256">
+      <c r="R19" s="264">
         <f>'บางบัวทอง-รถ'!C12</f>
         <v>0</v>
       </c>
-      <c r="S19" s="250">
+      <c r="S19" s="249">
         <v>260</v>
       </c>
-      <c r="T19" s="252">
+      <c r="T19" s="251">
         <f>SUM(S19-Q19)</f>
         <v>260</v>
       </c>
@@ -4272,12 +4266,12 @@
         <v>1 + 18 P</v>
       </c>
     </row>
-    <row r="20" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B20" s="289"/>
+    <row r="20" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B20" s="259"/>
       <c r="C20" s="205" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="289"/>
+      <c r="D20" s="259"/>
       <c r="E20" s="238" t="str">
         <f>IF(E19=0, "", IF(MOD(E19, $D$19) = 0, E19 / $D$19, IF(INT(E19 / $D$19) = 0, MOD(E19, $D$19) &amp; " P", INT(E19 / $D$19) &amp; " + " &amp; MOD(E19, $D$19) &amp; " P")))</f>
         <v/>
@@ -4326,10 +4320,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="255"/>
-      <c r="R20" s="257"/>
-      <c r="S20" s="251"/>
-      <c r="T20" s="253"/>
+      <c r="Q20" s="261"/>
+      <c r="R20" s="263"/>
+      <c r="S20" s="250"/>
+      <c r="T20" s="252"/>
       <c r="V20" s="215"/>
       <c r="W20" s="216"/>
       <c r="X20" s="217"/>
@@ -4339,14 +4333,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B21" s="288">
+    <row r="21" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B21" s="258">
         <v>4</v>
       </c>
       <c r="C21" s="200" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="288">
+      <c r="D21" s="258">
         <v>14</v>
       </c>
       <c r="E21" s="235"/>
@@ -4361,18 +4355,18 @@
       <c r="N21" s="235"/>
       <c r="O21" s="235"/>
       <c r="P21" s="235"/>
-      <c r="Q21" s="254">
+      <c r="Q21" s="260">
         <f>SUM(E21:P21)</f>
         <v>0</v>
       </c>
-      <c r="R21" s="256">
+      <c r="R21" s="264">
         <f>'บางบัวทอง-รถ'!C13</f>
         <v>0</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="249">
         <v>220</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="251">
         <f>SUM(S21-Q21)</f>
         <v>220</v>
       </c>
@@ -4401,12 +4395,12 @@
         <v>12 P</v>
       </c>
     </row>
-    <row r="22" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
-      <c r="B22" s="289"/>
+    <row r="22" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+      <c r="B22" s="259"/>
       <c r="C22" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="289"/>
+      <c r="D22" s="259"/>
       <c r="E22" s="238" t="str">
         <f t="shared" ref="E22:P22" si="7">IF(E21=0, "", IF(MOD(E21, $D$21) = 0, E21/ $D$21, IF(INT(E21 / $D$21) = 0, MOD(E21, $D$21) &amp; " P", INT(E21 / $D$21) &amp; " + " &amp; MOD(E21, $D$21) &amp; " P")))</f>
         <v/>
@@ -4455,10 +4449,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q22" s="255"/>
-      <c r="R22" s="257"/>
-      <c r="S22" s="251"/>
-      <c r="T22" s="253"/>
+      <c r="Q22" s="261"/>
+      <c r="R22" s="263"/>
+      <c r="S22" s="250"/>
+      <c r="T22" s="252"/>
       <c r="V22" s="215"/>
       <c r="W22" s="216"/>
       <c r="X22" s="217"/>
@@ -4468,14 +4462,14 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="23" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B23" s="174">
         <v>5</v>
       </c>
       <c r="C23" s="200" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="341">
+      <c r="D23" s="256">
         <v>14</v>
       </c>
       <c r="E23" s="235"/>
@@ -4490,18 +4484,18 @@
       <c r="N23" s="235"/>
       <c r="O23" s="235"/>
       <c r="P23" s="235"/>
-      <c r="Q23" s="254">
+      <c r="Q23" s="260">
         <f>SUM(E23:P23)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="256">
+      <c r="R23" s="264">
         <f>'บางบัวทอง-รถ'!C14</f>
         <v>0</v>
       </c>
-      <c r="S23" s="250">
+      <c r="S23" s="249">
         <v>230</v>
       </c>
-      <c r="T23" s="252">
+      <c r="T23" s="251">
         <f>SUM(S23-Q23)</f>
         <v>230</v>
       </c>
@@ -4530,12 +4524,12 @@
         <v>16 + 3 P</v>
       </c>
     </row>
-    <row r="24" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="24" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B24" s="175"/>
       <c r="C24" s="204" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="342"/>
+      <c r="D24" s="257"/>
       <c r="E24" s="244" t="str">
         <f t="shared" ref="E24:P24" si="9">IF(E23=0, "", IF(MOD(E23, $D$23) = 0, E23/ $D$23, IF(INT(E23 / $D$23) = 0, MOD(E23, $D$23) &amp; " P", INT(E23 / $D$23) &amp; " + " &amp; MOD(E23, $D$23) &amp; " P")))</f>
         <v/>
@@ -4584,10 +4578,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q24" s="255"/>
-      <c r="R24" s="257"/>
-      <c r="S24" s="251"/>
-      <c r="T24" s="253"/>
+      <c r="Q24" s="261"/>
+      <c r="R24" s="263"/>
+      <c r="S24" s="250"/>
+      <c r="T24" s="252"/>
       <c r="V24" s="215"/>
       <c r="W24" s="216"/>
       <c r="X24" s="217"/>
@@ -4597,14 +4591,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="25" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B25" s="174">
         <v>6</v>
       </c>
       <c r="C25" s="200" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="288">
+      <c r="D25" s="258">
         <v>32</v>
       </c>
       <c r="E25" s="235"/>
@@ -4619,18 +4613,18 @@
       <c r="N25" s="236"/>
       <c r="O25" s="237"/>
       <c r="P25" s="237"/>
-      <c r="Q25" s="254">
+      <c r="Q25" s="260">
         <f>SUM(E25:P25)</f>
         <v>0</v>
       </c>
-      <c r="R25" s="256">
+      <c r="R25" s="264">
         <f>'บางบัวทอง-รถ'!C15</f>
         <v>0</v>
       </c>
-      <c r="S25" s="250">
+      <c r="S25" s="249">
         <v>320</v>
       </c>
-      <c r="T25" s="252">
+      <c r="T25" s="251">
         <f>SUM(S25-Q25)</f>
         <v>320</v>
       </c>
@@ -4659,12 +4653,12 @@
         <v>25 P</v>
       </c>
     </row>
-    <row r="26" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="26" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B26" s="175"/>
       <c r="C26" s="204" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="289"/>
+      <c r="D26" s="259"/>
       <c r="E26" s="238" t="str">
         <f t="shared" ref="E26:P26" si="11">IF(E25=0, "", IF(MOD(E25, $D$25) = 0, E25/ $D$25, IF(INT(E25 / $D$25) = 0, MOD(E25, $D$25) &amp; " P", INT(E25 / $D$25) &amp; " + " &amp; MOD(E25, $D$25) &amp; " P")))</f>
         <v/>
@@ -4713,10 +4707,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q26" s="255"/>
-      <c r="R26" s="257"/>
-      <c r="S26" s="251"/>
-      <c r="T26" s="253"/>
+      <c r="Q26" s="261"/>
+      <c r="R26" s="263"/>
+      <c r="S26" s="250"/>
+      <c r="T26" s="252"/>
       <c r="V26" s="215"/>
       <c r="W26" s="216"/>
       <c r="X26" s="217"/>
@@ -4726,14 +4720,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="27" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B27" s="174">
         <v>7</v>
       </c>
       <c r="C27" s="201" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="341">
+      <c r="D27" s="256">
         <v>27</v>
       </c>
       <c r="E27" s="235"/>
@@ -4748,18 +4742,18 @@
       <c r="N27" s="236"/>
       <c r="O27" s="237"/>
       <c r="P27" s="237"/>
-      <c r="Q27" s="254">
+      <c r="Q27" s="260">
         <f>SUM(E27:P27)</f>
         <v>0</v>
       </c>
-      <c r="R27" s="256">
+      <c r="R27" s="264">
         <f>'บางบัวทอง-รถ'!C16</f>
         <v>0</v>
       </c>
-      <c r="S27" s="250">
+      <c r="S27" s="249">
         <v>280</v>
       </c>
-      <c r="T27" s="252">
+      <c r="T27" s="251">
         <f>SUM(S27-Q27)</f>
         <v>280</v>
       </c>
@@ -4788,12 +4782,12 @@
         <v>2 P</v>
       </c>
     </row>
-    <row r="28" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="28" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B28" s="175"/>
       <c r="C28" s="204" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="342"/>
+      <c r="D28" s="257"/>
       <c r="E28" s="238" t="str">
         <f t="shared" ref="E28:P28" si="13">IF(E27=0, "", IF(MOD(E27, $D$27) = 0, E27/ $D$27, IF(INT(E27 / $D$27) = 0, MOD(E27, $D$27) &amp; " P", INT(E27 / $D$27) &amp; " + " &amp; MOD(E27, $D$27) &amp; " P")))</f>
         <v/>
@@ -4842,10 +4836,10 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q28" s="255"/>
-      <c r="R28" s="257"/>
-      <c r="S28" s="251"/>
-      <c r="T28" s="253"/>
+      <c r="Q28" s="261"/>
+      <c r="R28" s="263"/>
+      <c r="S28" s="250"/>
+      <c r="T28" s="252"/>
       <c r="V28" s="211"/>
       <c r="W28" s="216"/>
       <c r="X28" s="217"/>
@@ -4855,7 +4849,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="29" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B29" s="174">
         <v>8</v>
       </c>
@@ -4877,18 +4871,18 @@
       <c r="N29" s="241"/>
       <c r="O29" s="243"/>
       <c r="P29" s="243"/>
-      <c r="Q29" s="254">
+      <c r="Q29" s="260">
         <f>SUM(E29:P29)</f>
         <v>0</v>
       </c>
-      <c r="R29" s="256">
+      <c r="R29" s="264">
         <f>'บางบัวทอง-รถ'!C17</f>
         <v>0</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="249">
         <v>680</v>
       </c>
-      <c r="T29" s="252">
+      <c r="T29" s="251">
         <f>SUM(S29-Q29)</f>
         <v>680</v>
       </c>
@@ -4917,7 +4911,7 @@
         <v>2 + 2 P</v>
       </c>
     </row>
-    <row r="30" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="30" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B30" s="175"/>
       <c r="C30" s="204" t="s">
         <v>113</v>
@@ -4971,10 +4965,10 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q30" s="255"/>
-      <c r="R30" s="257"/>
-      <c r="S30" s="251"/>
-      <c r="T30" s="253"/>
+      <c r="Q30" s="261"/>
+      <c r="R30" s="263"/>
+      <c r="S30" s="250"/>
+      <c r="T30" s="252"/>
       <c r="V30" s="211"/>
       <c r="W30" s="216"/>
       <c r="X30" s="217"/>
@@ -4984,7 +4978,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="31" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B31" s="174">
         <v>9</v>
       </c>
@@ -5006,18 +5000,18 @@
       <c r="N31" s="241"/>
       <c r="O31" s="243"/>
       <c r="P31" s="243"/>
-      <c r="Q31" s="254">
+      <c r="Q31" s="260">
         <f>SUM(E31:P31)</f>
         <v>0</v>
       </c>
-      <c r="R31" s="343">
+      <c r="R31" s="262">
         <f>'บางบัวทอง-รถ'!C18</f>
         <v>0</v>
       </c>
-      <c r="S31" s="250">
+      <c r="S31" s="249">
         <v>160</v>
       </c>
-      <c r="T31" s="252">
+      <c r="T31" s="251">
         <f>SUM(S31-Q31)</f>
         <v>160</v>
       </c>
@@ -5046,7 +5040,7 @@
         <v>1 + 14 P</v>
       </c>
     </row>
-    <row r="32" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="32" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B32" s="175"/>
       <c r="C32" s="205" t="s">
         <v>107</v>
@@ -5100,10 +5094,10 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q32" s="255"/>
-      <c r="R32" s="257"/>
-      <c r="S32" s="251"/>
-      <c r="T32" s="253"/>
+      <c r="Q32" s="261"/>
+      <c r="R32" s="263"/>
+      <c r="S32" s="250"/>
+      <c r="T32" s="252"/>
       <c r="V32" s="211"/>
       <c r="W32" s="216"/>
       <c r="X32" s="217"/>
@@ -5113,14 +5107,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="33" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B33" s="174">
         <v>10</v>
       </c>
       <c r="C33" s="202" t="s">
         <v>129</v>
       </c>
-      <c r="D33" s="346">
+      <c r="D33" s="267">
         <v>15</v>
       </c>
       <c r="E33" s="240"/>
@@ -5135,18 +5129,18 @@
       <c r="N33" s="241"/>
       <c r="O33" s="243"/>
       <c r="P33" s="243"/>
-      <c r="Q33" s="254">
+      <c r="Q33" s="260">
         <f>SUM(E33:P33)</f>
         <v>0</v>
       </c>
-      <c r="R33" s="343">
+      <c r="R33" s="262">
         <f>'บางบัวทอง-รถ'!C19</f>
         <v>0</v>
       </c>
-      <c r="S33" s="250">
+      <c r="S33" s="249">
         <v>160</v>
       </c>
-      <c r="T33" s="252">
+      <c r="T33" s="251">
         <f>SUM(S33-Q33)</f>
         <v>160</v>
       </c>
@@ -5175,12 +5169,12 @@
         <v>1 + 13 P</v>
       </c>
     </row>
-    <row r="34" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="34" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B34" s="175"/>
       <c r="C34" s="204" t="s">
         <v>130</v>
       </c>
-      <c r="D34" s="347"/>
+      <c r="D34" s="268"/>
       <c r="E34" s="238" t="str">
         <f>IF(E33=0, "", IF(MOD(E33, $D$33) = 0, E33/ $D$33, IF(INT(E33 / $D$33) = 0, MOD(E33, $D$33) &amp; " P", INT(E33 / $D$33) &amp; " + " &amp; MOD(E33, $D$33) &amp; " P")))</f>
         <v/>
@@ -5229,10 +5223,10 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="Q34" s="255"/>
-      <c r="R34" s="257"/>
-      <c r="S34" s="251"/>
-      <c r="T34" s="253"/>
+      <c r="Q34" s="261"/>
+      <c r="R34" s="263"/>
+      <c r="S34" s="250"/>
+      <c r="T34" s="252"/>
       <c r="V34" s="211"/>
       <c r="W34" s="216"/>
       <c r="X34" s="217"/>
@@ -5242,7 +5236,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="35" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B35" s="174">
         <v>11</v>
       </c>
@@ -5264,18 +5258,18 @@
       <c r="N35" s="242"/>
       <c r="O35" s="246"/>
       <c r="P35" s="246"/>
-      <c r="Q35" s="254">
+      <c r="Q35" s="260">
         <f>SUM(E35:P35)</f>
         <v>0</v>
       </c>
-      <c r="R35" s="256">
+      <c r="R35" s="264">
         <f>'บางบัวทอง-รถ'!C20</f>
         <v>0</v>
       </c>
-      <c r="S35" s="250">
+      <c r="S35" s="249">
         <v>50</v>
       </c>
-      <c r="T35" s="252">
+      <c r="T35" s="251">
         <f t="shared" ref="T35" si="18">SUM(S35-Q35)</f>
         <v>50</v>
       </c>
@@ -5304,7 +5298,7 @@
         <v>2 + 4 P</v>
       </c>
     </row>
-    <row r="36" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="36" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B36" s="175"/>
       <c r="C36" s="205" t="s">
         <v>114</v>
@@ -5358,17 +5352,17 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q36" s="255"/>
-      <c r="R36" s="257"/>
-      <c r="S36" s="251"/>
-      <c r="T36" s="253"/>
+      <c r="Q36" s="261"/>
+      <c r="R36" s="263"/>
+      <c r="S36" s="250"/>
+      <c r="T36" s="252"/>
       <c r="V36" s="211"/>
       <c r="W36" s="216"/>
       <c r="X36" s="217"/>
       <c r="Y36" s="212"/>
       <c r="Z36" s="218"/>
     </row>
-    <row r="37" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="37" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B37" s="174">
         <v>12</v>
       </c>
@@ -5390,18 +5384,18 @@
       <c r="N37" s="235"/>
       <c r="O37" s="235"/>
       <c r="P37" s="235"/>
-      <c r="Q37" s="254">
+      <c r="Q37" s="260">
         <f>SUM(E37:P37)</f>
         <v>0</v>
       </c>
-      <c r="R37" s="256">
+      <c r="R37" s="264">
         <f>'บางบัวทอง-รถ'!C21</f>
         <v>0</v>
       </c>
-      <c r="S37" s="250">
+      <c r="S37" s="249">
         <v>190</v>
       </c>
-      <c r="T37" s="252">
+      <c r="T37" s="251">
         <f t="shared" ref="T37" si="20">SUM(S37-Q37)</f>
         <v>190</v>
       </c>
@@ -5430,7 +5424,7 @@
         <v>2 + 3 P</v>
       </c>
     </row>
-    <row r="38" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="38" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B38" s="175"/>
       <c r="C38" s="205" t="s">
         <v>134</v>
@@ -5484,17 +5478,17 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Q38" s="255"/>
-      <c r="R38" s="257"/>
-      <c r="S38" s="251"/>
-      <c r="T38" s="253"/>
+      <c r="Q38" s="261"/>
+      <c r="R38" s="263"/>
+      <c r="S38" s="250"/>
+      <c r="T38" s="252"/>
       <c r="V38" s="211"/>
       <c r="W38" s="216"/>
       <c r="X38" s="217"/>
       <c r="Y38" s="212"/>
       <c r="Z38" s="218"/>
     </row>
-    <row r="39" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="39" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B39" s="174">
         <v>13</v>
       </c>
@@ -5516,18 +5510,18 @@
       <c r="N39" s="235"/>
       <c r="O39" s="235"/>
       <c r="P39" s="235"/>
-      <c r="Q39" s="254">
+      <c r="Q39" s="260">
         <f>SUM(E39:P39)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="256">
+      <c r="R39" s="264">
         <f>'บางบัวทอง-รถ'!C22</f>
         <v>0</v>
       </c>
-      <c r="S39" s="250">
+      <c r="S39" s="249">
         <v>100</v>
       </c>
-      <c r="T39" s="252">
+      <c r="T39" s="251">
         <f t="shared" ref="T39" si="22">SUM(S39-Q39)</f>
         <v>100</v>
       </c>
@@ -5556,7 +5550,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="40" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B40" s="175"/>
       <c r="C40" s="205" t="s">
         <v>118</v>
@@ -5610,17 +5604,17 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q40" s="255"/>
-      <c r="R40" s="257"/>
-      <c r="S40" s="251"/>
-      <c r="T40" s="253"/>
+      <c r="Q40" s="261"/>
+      <c r="R40" s="263"/>
+      <c r="S40" s="250"/>
+      <c r="T40" s="252"/>
       <c r="V40" s="211"/>
       <c r="W40" s="216"/>
       <c r="X40" s="217"/>
       <c r="Y40" s="212"/>
       <c r="Z40" s="218"/>
     </row>
-    <row r="41" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="41" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B41" s="174">
         <v>14</v>
       </c>
@@ -5642,18 +5636,18 @@
       <c r="N41" s="235"/>
       <c r="O41" s="235"/>
       <c r="P41" s="235"/>
-      <c r="Q41" s="254">
+      <c r="Q41" s="260">
         <f>SUM(E41:P41)</f>
         <v>0</v>
       </c>
-      <c r="R41" s="256">
+      <c r="R41" s="264">
         <f>'บางบัวทอง-รถ'!C23</f>
         <v>0</v>
       </c>
-      <c r="S41" s="250">
+      <c r="S41" s="249">
         <v>812</v>
       </c>
-      <c r="T41" s="252">
+      <c r="T41" s="251">
         <f t="shared" ref="T41" si="24">SUM(S41-Q41)</f>
         <v>812</v>
       </c>
@@ -5682,7 +5676,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="42" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B42" s="175"/>
       <c r="C42" s="205" t="s">
         <v>132</v>
@@ -5736,17 +5730,17 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="Q42" s="255"/>
-      <c r="R42" s="257"/>
-      <c r="S42" s="251"/>
-      <c r="T42" s="253"/>
+      <c r="Q42" s="261"/>
+      <c r="R42" s="263"/>
+      <c r="S42" s="250"/>
+      <c r="T42" s="252"/>
       <c r="V42" s="211"/>
       <c r="W42" s="216"/>
       <c r="X42" s="217"/>
       <c r="Y42" s="212"/>
       <c r="Z42" s="218"/>
     </row>
-    <row r="43" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="43" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B43" s="174">
         <v>15</v>
       </c>
@@ -5768,18 +5762,18 @@
       <c r="N43" s="235"/>
       <c r="O43" s="235"/>
       <c r="P43" s="235"/>
-      <c r="Q43" s="254">
+      <c r="Q43" s="260">
         <f>SUM(E43:P43)</f>
         <v>0</v>
       </c>
-      <c r="R43" s="256">
+      <c r="R43" s="264">
         <f>'บางบัวทอง-รถ'!C24</f>
         <v>0</v>
       </c>
-      <c r="S43" s="250">
+      <c r="S43" s="249">
         <v>400</v>
       </c>
-      <c r="T43" s="252">
+      <c r="T43" s="251">
         <f t="shared" ref="T43" si="26">SUM(S43-Q43)</f>
         <v>400</v>
       </c>
@@ -5808,7 +5802,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="44" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B44" s="175"/>
       <c r="C44" s="204" t="s">
         <v>115</v>
@@ -5862,17 +5856,17 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="Q44" s="255"/>
-      <c r="R44" s="257"/>
-      <c r="S44" s="251"/>
-      <c r="T44" s="253"/>
+      <c r="Q44" s="261"/>
+      <c r="R44" s="263"/>
+      <c r="S44" s="250"/>
+      <c r="T44" s="252"/>
       <c r="V44" s="211"/>
       <c r="W44" s="216"/>
       <c r="X44" s="217"/>
       <c r="Y44" s="212"/>
       <c r="Z44" s="218"/>
     </row>
-    <row r="45" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="45" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B45" s="174">
         <v>16</v>
       </c>
@@ -5894,18 +5888,18 @@
       <c r="N45" s="235"/>
       <c r="O45" s="235"/>
       <c r="P45" s="235"/>
-      <c r="Q45" s="254">
+      <c r="Q45" s="260">
         <f>SUM(E45:P45)</f>
         <v>0</v>
       </c>
-      <c r="R45" s="256">
+      <c r="R45" s="264">
         <f>'บางบัวทอง-รถ'!C25</f>
         <v>0</v>
       </c>
-      <c r="S45" s="250">
+      <c r="S45" s="249">
         <v>200</v>
       </c>
-      <c r="T45" s="252">
+      <c r="T45" s="251">
         <f t="shared" ref="T45" si="28">SUM(S45-Q45)</f>
         <v>200</v>
       </c>
@@ -5934,7 +5928,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="46" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B46" s="175"/>
       <c r="C46" s="204" t="s">
         <v>116</v>
@@ -5949,7 +5943,7 @@
         <v/>
       </c>
       <c r="G46" s="238" t="str">
-        <f t="shared" ref="G46:P46" si="29">IF(G45=0, "", IF(MOD(G45, $D$45) = 0, G45/ $D$45, IF(INT(G45 / $D$45) = 0, MOD(G45, $D$45) &amp; " P", INT(G45 / $D$45) &amp; " + " &amp; MOD(G45, $D$45) &amp; " P")))</f>
+        <f t="shared" ref="F46:P46" si="29">IF(G45=0, "", IF(MOD(G45, $D$45) = 0, G45/ $D$45, IF(INT(G45 / $D$45) = 0, MOD(G45, $D$45) &amp; " P", INT(G45 / $D$45) &amp; " + " &amp; MOD(G45, $D$45) &amp; " P")))</f>
         <v/>
       </c>
       <c r="H46" s="248" t="str">
@@ -5988,17 +5982,17 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="Q46" s="255"/>
-      <c r="R46" s="257"/>
-      <c r="S46" s="251"/>
-      <c r="T46" s="253"/>
+      <c r="Q46" s="261"/>
+      <c r="R46" s="263"/>
+      <c r="S46" s="250"/>
+      <c r="T46" s="252"/>
       <c r="V46" s="211"/>
       <c r="W46" s="216"/>
       <c r="X46" s="217"/>
       <c r="Y46" s="212"/>
       <c r="Z46" s="218"/>
     </row>
-    <row r="47" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="47" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B47" s="223">
         <v>17</v>
       </c>
@@ -6020,18 +6014,18 @@
       <c r="N47" s="235"/>
       <c r="O47" s="235"/>
       <c r="P47" s="235"/>
-      <c r="Q47" s="254">
+      <c r="Q47" s="260">
         <f>SUM(E47:P47)</f>
         <v>0</v>
       </c>
-      <c r="R47" s="256">
+      <c r="R47" s="264">
         <f>'บางบัวทอง-รถ'!C26</f>
         <v>0</v>
       </c>
-      <c r="S47" s="250">
+      <c r="S47" s="249">
         <v>110</v>
       </c>
-      <c r="T47" s="252">
+      <c r="T47" s="251">
         <f t="shared" ref="T47" si="30">SUM(S47-Q47)</f>
         <v>110</v>
       </c>
@@ -6060,7 +6054,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="48" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B48" s="224"/>
       <c r="C48" s="205" t="s">
         <v>117</v>
@@ -6114,17 +6108,17 @@
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="Q48" s="255"/>
-      <c r="R48" s="257"/>
-      <c r="S48" s="251"/>
-      <c r="T48" s="253"/>
+      <c r="Q48" s="261"/>
+      <c r="R48" s="263"/>
+      <c r="S48" s="250"/>
+      <c r="T48" s="252"/>
       <c r="V48" s="211"/>
       <c r="W48" s="216"/>
       <c r="X48" s="217"/>
       <c r="Y48" s="212"/>
       <c r="Z48" s="218"/>
     </row>
-    <row r="49" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="49" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B49" s="174">
         <v>18</v>
       </c>
@@ -6132,7 +6126,7 @@
         <v>146</v>
       </c>
       <c r="D49" s="230">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E49" s="235"/>
       <c r="F49" s="235"/>
@@ -6146,18 +6140,18 @@
       <c r="N49" s="235"/>
       <c r="O49" s="235"/>
       <c r="P49" s="235"/>
-      <c r="Q49" s="254">
+      <c r="Q49" s="260">
         <f>SUM(E49:P49)</f>
         <v>0</v>
       </c>
-      <c r="R49" s="256">
+      <c r="R49" s="264">
         <f>'บางบัวทอง-รถ'!C27</f>
         <v>0</v>
       </c>
-      <c r="S49" s="250">
+      <c r="S49" s="249">
         <v>50</v>
       </c>
-      <c r="T49" s="252">
+      <c r="T49" s="251">
         <f t="shared" ref="T49" si="32">SUM(S49-Q49)</f>
         <v>50</v>
       </c>
@@ -6186,7 +6180,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+    <row r="50" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
       <c r="B50" s="175"/>
       <c r="C50" s="233" t="s">
         <v>145</v>
@@ -6240,67 +6234,67 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="Q50" s="255"/>
-      <c r="R50" s="257"/>
-      <c r="S50" s="251"/>
-      <c r="T50" s="253"/>
+      <c r="Q50" s="261"/>
+      <c r="R50" s="263"/>
+      <c r="S50" s="250"/>
+      <c r="T50" s="252"/>
       <c r="V50" s="211"/>
       <c r="W50" s="216"/>
       <c r="X50" s="217"/>
       <c r="Y50" s="212"/>
       <c r="Z50" s="218"/>
     </row>
-    <row r="51" spans="2:37" s="30" customFormat="1" ht="79.95" customHeight="1" thickBot="1">
-      <c r="B51" s="274" t="s">
+    <row r="51" spans="2:37" s="30" customFormat="1" ht="79.900000000000006" customHeight="1" thickBot="1">
+      <c r="B51" s="340" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="275"/>
-      <c r="D51" s="276"/>
-      <c r="E51" s="249">
+      <c r="C51" s="341"/>
+      <c r="D51" s="342"/>
+      <c r="E51" s="418">
         <f>-SUM(ROUNDUP(E15/$D$15,0), ROUNDUP(E17/$D$17,0), ROUNDUP(E19/$D$19,0), ROUNDUP(E21/$D$21,0), ROUNDUP(E23/$D$23,0), ROUNDUP(E25/$D$25,0), ROUNDUP(E27/$D$27,0), ROUNDUP(E29/$D$29,0), ROUNDUP(E31/$D$31,0), ROUNDUP(E33/$D$33,0), ROUNDUP(E35/$D$35,0), ROUNDUP(E37/$D$37,0), ROUNDUP(E39/$D$39,0), ROUNDUP(E41/$D$41,0), ROUNDUP(E43/$D$43,0), ROUNDUP(E45/$D$45,0), ROUNDUP(E47/$D$47,0), ROUNDUP(E49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="F51" s="249">
+      <c r="F51" s="418">
         <f>-SUM(ROUNDUP(F15/$D$15,0), ROUNDUP(F17/$D$17,0), ROUNDUP(F19/$D$19,0), ROUNDUP(F21/$D$21,0), ROUNDUP(F23/$D$23,0), ROUNDUP(F25/$D$25,0), ROUNDUP(F27/$D$27,0), ROUNDUP(F29/$D$29,0), ROUNDUP(F31/$D$31,0), ROUNDUP(F33/$D$33,0), ROUNDUP(F35/$D$35,0), ROUNDUP(F37/$D$37,0), ROUNDUP(F39/$D$39,0), ROUNDUP(F41/$D$41,0), ROUNDUP(F43/$D$43,0), ROUNDUP(F45/$D$45,0), ROUNDUP(F47/$D$47,0), ROUNDUP(F49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="G51" s="249">
+      <c r="G51" s="418">
         <f>-SUM(ROUNDUP(G15/$D$15,0), ROUNDUP(G17/$D$17,0), ROUNDUP(G19/$D$19,0), ROUNDUP(G21/$D$21,0), ROUNDUP(G23/$D$23,0), ROUNDUP(G25/$D$25,0), ROUNDUP(G27/$D$27,0), ROUNDUP(G29/$D$29,0), ROUNDUP(G31/$D$31,0), ROUNDUP(G33/$D$33,0), ROUNDUP(G35/$D$35,0), ROUNDUP(G37/$D$37,0), ROUNDUP(G39/$D$39,0), ROUNDUP(G41/$D$41,0), ROUNDUP(G43/$D$43,0), ROUNDUP(G45/$D$45,0), ROUNDUP(G47/$D$47,0), ROUNDUP(G49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="H51" s="249">
+      <c r="H51" s="418">
         <f>-SUM(ROUNDUP(H15/$D$15,0), ROUNDUP(H17/$D$17,0), ROUNDUP(H19/$D$19,0), ROUNDUP(H21/$D$21,0), ROUNDUP(H23/$D$23,0), ROUNDUP(H25/$D$25,0), ROUNDUP(H27/$D$27,0), ROUNDUP(H29/$D$29,0), ROUNDUP(H31/$D$31,0), ROUNDUP(H33/$D$33,0), ROUNDUP(H35/$D$35,0), ROUNDUP(H37/$D$37,0), ROUNDUP(H39/$D$39,0), ROUNDUP(H41/$D$41,0), ROUNDUP(H43/$D$43,0), ROUNDUP(H45/$D$45,0), ROUNDUP(H47/$D$47,0), ROUNDUP(H49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="I51" s="249">
+      <c r="I51" s="418">
         <f>-SUM(ROUNDUP(I15/$D$15,0), ROUNDUP(I17/$D$17,0), ROUNDUP(I19/$D$19,0), ROUNDUP(I21/$D$21,0), ROUNDUP(I23/$D$23,0), ROUNDUP(I25/$D$25,0), ROUNDUP(I27/$D$27,0), ROUNDUP(I29/$D$29,0), ROUNDUP(I31/$D$31,0), ROUNDUP(I33/$D$33,0), ROUNDUP(I35/$D$35,0), ROUNDUP(I37/$D$37,0), ROUNDUP(I39/$D$39,0), ROUNDUP(I41/$D$41,0), ROUNDUP(I43/$D$43,0), ROUNDUP(I45/$D$45,0), ROUNDUP(I47/$D$47,0), ROUNDUP(I49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="J51" s="249">
-        <f t="shared" ref="J51:P51" si="34">-SUM(ROUNDUP(J15/$D$15,0), ROUNDUP(J17/$D$17,0), ROUNDUP(J19/$D$19,0), ROUNDUP(J21/$D$21,0), ROUNDUP(J23/$D$23,0), ROUNDUP(J25/$D$25,0), ROUNDUP(J27/$D$27,0), ROUNDUP(J29/$D$29,0), ROUNDUP(J31/$D$31,0), ROUNDUP(J33/$D$33,0), ROUNDUP(J35/$D$35,0), ROUNDUP(J37/$D$37,0), ROUNDUP(J39/$D$39,0), ROUNDUP(J41/$D$41,0), ROUNDUP(J43/$D$43,0), ROUNDUP(J45/$D$45,0), ROUNDUP(J47/$D$47,0), ROUNDUP(J49/$D$49,0))</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="249">
+      <c r="J51" s="418">
+        <f t="shared" ref="F51:P51" si="34">-SUM(ROUNDUP(J15/$D$15,0), ROUNDUP(J17/$D$17,0), ROUNDUP(J19/$D$19,0), ROUNDUP(J21/$D$21,0), ROUNDUP(J23/$D$23,0), ROUNDUP(J25/$D$25,0), ROUNDUP(J27/$D$27,0), ROUNDUP(J29/$D$29,0), ROUNDUP(J31/$D$31,0), ROUNDUP(J33/$D$33,0), ROUNDUP(J35/$D$35,0), ROUNDUP(J37/$D$37,0), ROUNDUP(J39/$D$39,0), ROUNDUP(J41/$D$41,0), ROUNDUP(J43/$D$43,0), ROUNDUP(J45/$D$45,0), ROUNDUP(J47/$D$47,0), ROUNDUP(J49/$D$49,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="418">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="L51" s="249">
+      <c r="L51" s="418">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="M51" s="249">
+      <c r="M51" s="418">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="N51" s="249">
+      <c r="N51" s="418">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="O51" s="249">
+      <c r="O51" s="418">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="P51" s="249">
+      <c r="P51" s="418">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
@@ -6317,38 +6311,38 @@
       <c r="Y51" s="222"/>
       <c r="Z51" s="221"/>
     </row>
-    <row r="52" spans="2:37" ht="22.95" customHeight="1" thickBot="1"/>
-    <row r="53" spans="2:37" s="30" customFormat="1" ht="58.2" customHeight="1" thickBot="1">
-      <c r="B53" s="281" t="s">
+    <row r="52" spans="2:37" ht="22.9" customHeight="1" thickBot="1"/>
+    <row r="53" spans="2:37" s="30" customFormat="1" ht="58.15" customHeight="1" thickBot="1">
+      <c r="B53" s="324" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="282"/>
-      <c r="D53" s="281" t="s">
+      <c r="C53" s="325"/>
+      <c r="D53" s="324" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="282"/>
-      <c r="F53" s="281" t="s">
+      <c r="E53" s="325"/>
+      <c r="F53" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="G53" s="282"/>
-      <c r="H53" s="281" t="s">
+      <c r="G53" s="325"/>
+      <c r="H53" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="I53" s="282"/>
-      <c r="J53" s="344" t="s">
+      <c r="I53" s="325"/>
+      <c r="J53" s="265" t="s">
         <v>88</v>
       </c>
-      <c r="K53" s="345"/>
-      <c r="L53" s="345"/>
-      <c r="M53" s="345"/>
-      <c r="N53" s="345"/>
-      <c r="O53" s="345"/>
-      <c r="P53" s="345"/>
-      <c r="Q53" s="338">
+      <c r="K53" s="266"/>
+      <c r="L53" s="266"/>
+      <c r="M53" s="266"/>
+      <c r="N53" s="266"/>
+      <c r="O53" s="266"/>
+      <c r="P53" s="266"/>
+      <c r="Q53" s="253">
         <f>SUM(R51)</f>
         <v>0</v>
       </c>
-      <c r="R53" s="340" t="s">
+      <c r="R53" s="255" t="s">
         <v>89</v>
       </c>
       <c r="T53" s="36"/>
@@ -6358,26 +6352,26 @@
       <c r="Y53" s="206"/>
       <c r="Z53" s="206"/>
     </row>
-    <row r="54" spans="2:37" s="30" customFormat="1" ht="52.95" customHeight="1">
-      <c r="B54" s="283" t="s">
+    <row r="54" spans="2:37" s="30" customFormat="1" ht="52.9" customHeight="1">
+      <c r="B54" s="326" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="284"/>
-      <c r="D54" s="285"/>
-      <c r="E54" s="286"/>
-      <c r="F54" s="285"/>
-      <c r="G54" s="286"/>
-      <c r="H54" s="285"/>
-      <c r="I54" s="286"/>
-      <c r="J54" s="344"/>
-      <c r="K54" s="345"/>
-      <c r="L54" s="345"/>
-      <c r="M54" s="345"/>
-      <c r="N54" s="345"/>
-      <c r="O54" s="345"/>
-      <c r="P54" s="345"/>
-      <c r="Q54" s="339"/>
-      <c r="R54" s="340"/>
+      <c r="C54" s="327"/>
+      <c r="D54" s="328"/>
+      <c r="E54" s="329"/>
+      <c r="F54" s="328"/>
+      <c r="G54" s="329"/>
+      <c r="H54" s="328"/>
+      <c r="I54" s="329"/>
+      <c r="J54" s="265"/>
+      <c r="K54" s="266"/>
+      <c r="L54" s="266"/>
+      <c r="M54" s="266"/>
+      <c r="N54" s="266"/>
+      <c r="O54" s="266"/>
+      <c r="P54" s="266"/>
+      <c r="Q54" s="254"/>
+      <c r="R54" s="255"/>
       <c r="T54" s="36"/>
       <c r="V54" s="206"/>
       <c r="W54" s="206"/>
@@ -6385,26 +6379,26 @@
       <c r="Y54" s="206"/>
       <c r="Z54" s="206"/>
     </row>
-    <row r="55" spans="2:37" s="30" customFormat="1" ht="52.95" customHeight="1" thickBot="1">
-      <c r="B55" s="269" t="s">
+    <row r="55" spans="2:37" s="30" customFormat="1" ht="52.9" customHeight="1" thickBot="1">
+      <c r="B55" s="335" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="270"/>
-      <c r="D55" s="271"/>
-      <c r="E55" s="272"/>
-      <c r="F55" s="271"/>
-      <c r="G55" s="272"/>
-      <c r="H55" s="271"/>
-      <c r="I55" s="272"/>
+      <c r="C55" s="336"/>
+      <c r="D55" s="337"/>
+      <c r="E55" s="338"/>
+      <c r="F55" s="337"/>
+      <c r="G55" s="338"/>
+      <c r="H55" s="337"/>
+      <c r="I55" s="338"/>
       <c r="J55" s="38"/>
       <c r="M55" s="67"/>
-      <c r="N55" s="273" t="s">
+      <c r="N55" s="339" t="s">
         <v>73</v>
       </c>
-      <c r="O55" s="273"/>
-      <c r="P55" s="273"/>
-      <c r="Q55" s="273"/>
-      <c r="R55" s="273"/>
+      <c r="O55" s="339"/>
+      <c r="P55" s="339"/>
+      <c r="Q55" s="339"/>
+      <c r="R55" s="339"/>
       <c r="T55" s="36"/>
       <c r="V55" s="206"/>
       <c r="W55" s="206"/>
@@ -6412,17 +6406,17 @@
       <c r="Y55" s="206"/>
       <c r="Z55" s="206"/>
     </row>
-    <row r="56" spans="2:37" s="30" customFormat="1" ht="52.95" customHeight="1" thickBot="1">
-      <c r="B56" s="277" t="s">
+    <row r="56" spans="2:37" s="30" customFormat="1" ht="52.9" customHeight="1" thickBot="1">
+      <c r="B56" s="320" t="s">
         <v>76</v>
       </c>
-      <c r="C56" s="278"/>
-      <c r="D56" s="279"/>
-      <c r="E56" s="280"/>
-      <c r="F56" s="279"/>
-      <c r="G56" s="280"/>
-      <c r="H56" s="279"/>
-      <c r="I56" s="280"/>
+      <c r="C56" s="321"/>
+      <c r="D56" s="322"/>
+      <c r="E56" s="323"/>
+      <c r="F56" s="322"/>
+      <c r="G56" s="323"/>
+      <c r="H56" s="322"/>
+      <c r="I56" s="323"/>
       <c r="J56" s="38"/>
       <c r="K56" s="234" t="s">
         <v>77</v>
@@ -6447,7 +6441,7 @@
       <c r="Y56" s="206"/>
       <c r="Z56" s="206"/>
     </row>
-    <row r="57" spans="2:37" s="30" customFormat="1" ht="64.2" customHeight="1" thickBot="1">
+    <row r="57" spans="2:37" s="30" customFormat="1" ht="64.150000000000006" customHeight="1" thickBot="1">
       <c r="B57" s="38"/>
       <c r="C57" s="38"/>
       <c r="D57" s="89"/>
@@ -6474,6 +6468,111 @@
     </row>
   </sheetData>
   <mergeCells count="129">
+    <mergeCell ref="S45:S46"/>
+    <mergeCell ref="T45:T46"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="W12:W13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="N55:R55"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="Q49:Q50"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="T49:T50"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B10:D11"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="E9:P10"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="Q12:R13"/>
+    <mergeCell ref="S12:S14"/>
+    <mergeCell ref="B12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="T12:T14"/>
     <mergeCell ref="S47:S48"/>
     <mergeCell ref="T47:T48"/>
     <mergeCell ref="Q53:Q54"/>
@@ -6498,111 +6597,6 @@
     <mergeCell ref="S23:S24"/>
     <mergeCell ref="T23:T24"/>
     <mergeCell ref="S29:S30"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="Q12:R13"/>
-    <mergeCell ref="S12:S14"/>
-    <mergeCell ref="B12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="T12:T14"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B10:D11"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="E9:P10"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="W11:AA11"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="N55:R55"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="Q49:Q50"/>
-    <mergeCell ref="R49:R50"/>
-    <mergeCell ref="S49:S50"/>
-    <mergeCell ref="T49:T50"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="S45:S46"/>
-    <mergeCell ref="T45:T46"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="S43:S44"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="X12:X13"/>
-    <mergeCell ref="W12:W13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="T33:T34"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:S36"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="Q23:Q24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6614,28 +6608,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F73E104-985C-4BC0-B1FE-3BA893F14D77}">
   <dimension ref="B4:AK54"/>
-  <sheetFormatPr defaultColWidth="5.69921875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22.59765625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="183.59765625" style="30" customWidth="1"/>
-    <col min="4" max="4" width="29.19921875" style="30" customWidth="1"/>
-    <col min="5" max="8" width="54.09765625" style="30" customWidth="1"/>
-    <col min="9" max="14" width="49.69921875" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="49.69921875" style="29" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="49.69921875" style="29" customWidth="1"/>
-    <col min="18" max="18" width="49.69921875" style="36" customWidth="1"/>
-    <col min="19" max="19" width="27.3984375" style="29" customWidth="1"/>
-    <col min="20" max="20" width="27.3984375" style="127" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="30" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="183.625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="29.25" style="30" customWidth="1"/>
+    <col min="5" max="8" width="54.125" style="30" customWidth="1"/>
+    <col min="9" max="14" width="49.75" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="49.75" style="29" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="49.75" style="29" customWidth="1"/>
+    <col min="18" max="18" width="49.75" style="36" customWidth="1"/>
+    <col min="19" max="19" width="27.375" style="29" customWidth="1"/>
+    <col min="20" max="20" width="27.375" style="127" customWidth="1"/>
     <col min="21" max="21" width="9.5" style="67" customWidth="1"/>
-    <col min="22" max="25" width="35.8984375" style="67" customWidth="1"/>
-    <col min="26" max="26" width="35.8984375" style="30" customWidth="1"/>
-    <col min="27" max="36" width="5.69921875" style="30"/>
-    <col min="37" max="37" width="10.09765625" style="30" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="5.69921875" style="30"/>
+    <col min="22" max="25" width="35.875" style="67" customWidth="1"/>
+    <col min="26" max="26" width="35.875" style="30" customWidth="1"/>
+    <col min="27" max="36" width="5.75" style="30"/>
+    <col min="37" max="37" width="10.125" style="30" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="5.75" style="30"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:37" ht="31.95" customHeight="1">
+    <row r="4" spans="2:37" ht="31.9" customHeight="1">
       <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -6646,8 +6640,8 @@
       <c r="I4" s="37"/>
       <c r="J4" s="28"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="287"/>
-      <c r="M4" s="287"/>
+      <c r="L4" s="298"/>
+      <c r="M4" s="298"/>
       <c r="N4" s="54"/>
       <c r="O4" s="55"/>
       <c r="P4" s="55"/>
@@ -6677,157 +6671,157 @@
       <c r="M7" s="49"/>
     </row>
     <row r="9" spans="2:37" ht="15" customHeight="1" thickBot="1"/>
-    <row r="10" spans="2:37" ht="71.400000000000006" customHeight="1" thickBot="1">
-      <c r="B10" s="367" t="s">
+    <row r="10" spans="2:37" ht="71.45" customHeight="1" thickBot="1">
+      <c r="B10" s="347" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="367"/>
-      <c r="D10" s="367"/>
-      <c r="E10" s="369" t="s">
+      <c r="C10" s="347"/>
+      <c r="D10" s="347"/>
+      <c r="E10" s="349" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="370"/>
-      <c r="G10" s="370"/>
-      <c r="H10" s="370"/>
-      <c r="I10" s="370"/>
-      <c r="J10" s="370"/>
-      <c r="K10" s="370"/>
-      <c r="L10" s="370"/>
-      <c r="M10" s="370"/>
-      <c r="N10" s="370"/>
-      <c r="O10" s="370"/>
-      <c r="P10" s="370"/>
-      <c r="Q10" s="370"/>
-      <c r="R10" s="371"/>
+      <c r="F10" s="350"/>
+      <c r="G10" s="350"/>
+      <c r="H10" s="350"/>
+      <c r="I10" s="350"/>
+      <c r="J10" s="350"/>
+      <c r="K10" s="350"/>
+      <c r="L10" s="350"/>
+      <c r="M10" s="350"/>
+      <c r="N10" s="350"/>
+      <c r="O10" s="350"/>
+      <c r="P10" s="350"/>
+      <c r="Q10" s="350"/>
+      <c r="R10" s="351"/>
       <c r="U10" s="29"/>
       <c r="Z10" s="67"/>
       <c r="AA10" s="35"/>
     </row>
     <row r="11" spans="2:37" ht="3" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="368"/>
-      <c r="C11" s="368"/>
-      <c r="D11" s="368"/>
-      <c r="E11" s="372"/>
-      <c r="F11" s="373"/>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
-      <c r="K11" s="373"/>
-      <c r="L11" s="373"/>
-      <c r="M11" s="373"/>
-      <c r="N11" s="373"/>
-      <c r="O11" s="373"/>
-      <c r="P11" s="373"/>
-      <c r="Q11" s="373"/>
-      <c r="R11" s="374"/>
+      <c r="B11" s="348"/>
+      <c r="C11" s="348"/>
+      <c r="D11" s="348"/>
+      <c r="E11" s="352"/>
+      <c r="F11" s="353"/>
+      <c r="G11" s="353"/>
+      <c r="H11" s="353"/>
+      <c r="I11" s="353"/>
+      <c r="J11" s="353"/>
+      <c r="K11" s="353"/>
+      <c r="L11" s="353"/>
+      <c r="M11" s="353"/>
+      <c r="N11" s="353"/>
+      <c r="O11" s="353"/>
+      <c r="P11" s="353"/>
+      <c r="Q11" s="353"/>
+      <c r="R11" s="354"/>
       <c r="S11" s="68"/>
       <c r="T11" s="128"/>
       <c r="U11" s="34"/>
-      <c r="W11" s="266"/>
-      <c r="X11" s="267"/>
-      <c r="Y11" s="267"/>
-      <c r="Z11" s="267"/>
-      <c r="AA11" s="268"/>
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
+      <c r="Y11" s="333"/>
+      <c r="Z11" s="333"/>
+      <c r="AA11" s="334"/>
     </row>
     <row r="12" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B12" s="322" t="s">
+      <c r="B12" s="282" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="323"/>
-      <c r="D12" s="328" t="s">
+      <c r="C12" s="283"/>
+      <c r="D12" s="288" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="331" t="s">
+      <c r="E12" s="291" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="332"/>
-      <c r="G12" s="333" t="s">
+      <c r="F12" s="292"/>
+      <c r="G12" s="293" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="334"/>
-      <c r="I12" s="313" t="s">
+      <c r="H12" s="294"/>
+      <c r="I12" s="273" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="314"/>
-      <c r="K12" s="298" t="s">
+      <c r="J12" s="274"/>
+      <c r="K12" s="307" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="299"/>
-      <c r="M12" s="300"/>
-      <c r="N12" s="308" t="s">
+      <c r="L12" s="308"/>
+      <c r="M12" s="309"/>
+      <c r="N12" s="317" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="309"/>
+      <c r="O12" s="318"/>
       <c r="P12" s="139"/>
-      <c r="Q12" s="315" t="s">
+      <c r="Q12" s="275" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="316"/>
-      <c r="S12" s="319" t="s">
+      <c r="R12" s="276"/>
+      <c r="S12" s="279" t="s">
         <v>78</v>
       </c>
-      <c r="T12" s="335" t="s">
+      <c r="T12" s="295" t="s">
         <v>79</v>
       </c>
       <c r="U12" s="30"/>
-      <c r="V12" s="381" t="s">
+      <c r="V12" s="361" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="377" t="s">
+      <c r="W12" s="357" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="375" t="s">
+      <c r="X12" s="355" t="s">
         <v>85</v>
       </c>
-      <c r="Y12" s="377" t="s">
+      <c r="Y12" s="357" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="379" t="s">
+      <c r="Z12" s="359" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B13" s="324"/>
-      <c r="C13" s="325"/>
-      <c r="D13" s="329"/>
-      <c r="E13" s="331" t="s">
+      <c r="B13" s="284"/>
+      <c r="C13" s="285"/>
+      <c r="D13" s="289"/>
+      <c r="E13" s="291" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="332"/>
-      <c r="G13" s="333" t="s">
+      <c r="F13" s="292"/>
+      <c r="G13" s="293" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="334"/>
-      <c r="I13" s="313" t="s">
+      <c r="H13" s="294"/>
+      <c r="I13" s="273" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="314"/>
-      <c r="K13" s="298" t="s">
+      <c r="J13" s="274"/>
+      <c r="K13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="299"/>
-      <c r="M13" s="300"/>
-      <c r="N13" s="308" t="s">
+      <c r="L13" s="308"/>
+      <c r="M13" s="309"/>
+      <c r="N13" s="317" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="309"/>
+      <c r="O13" s="318"/>
       <c r="P13" s="139"/>
-      <c r="Q13" s="317"/>
-      <c r="R13" s="318"/>
-      <c r="S13" s="320"/>
-      <c r="T13" s="336"/>
+      <c r="Q13" s="277"/>
+      <c r="R13" s="278"/>
+      <c r="S13" s="280"/>
+      <c r="T13" s="296"/>
       <c r="U13" s="30"/>
-      <c r="V13" s="382"/>
-      <c r="W13" s="378"/>
-      <c r="X13" s="376"/>
-      <c r="Y13" s="378"/>
-      <c r="Z13" s="380"/>
+      <c r="V13" s="362"/>
+      <c r="W13" s="358"/>
+      <c r="X13" s="356"/>
+      <c r="Y13" s="358"/>
+      <c r="Z13" s="360"/>
     </row>
     <row r="14" spans="2:37" ht="129" customHeight="1" thickBot="1">
-      <c r="B14" s="326"/>
-      <c r="C14" s="327"/>
-      <c r="D14" s="330"/>
+      <c r="B14" s="286"/>
+      <c r="C14" s="287"/>
+      <c r="D14" s="290"/>
       <c r="E14" s="130" t="s">
         <v>0</v>
       </c>
@@ -6870,8 +6864,8 @@
       <c r="R14" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="S14" s="321"/>
-      <c r="T14" s="337"/>
+      <c r="S14" s="281"/>
+      <c r="T14" s="297"/>
       <c r="U14" s="30"/>
       <c r="V14" s="91"/>
       <c r="W14" s="92"/>
@@ -6883,13 +6877,13 @@
       </c>
     </row>
     <row r="15" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B15" s="361">
+      <c r="B15" s="363">
         <v>1</v>
       </c>
       <c r="C15" s="161" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="365">
+      <c r="D15" s="371">
         <v>36</v>
       </c>
       <c r="E15" s="145">
@@ -6912,17 +6906,17 @@
       <c r="N15" s="146"/>
       <c r="O15" s="147"/>
       <c r="P15" s="147"/>
-      <c r="Q15" s="352">
+      <c r="Q15" s="367">
         <f>SUM(E15:P15)</f>
         <v>141</v>
       </c>
-      <c r="R15" s="354">
+      <c r="R15" s="369">
         <v>6</v>
       </c>
-      <c r="S15" s="250">
+      <c r="S15" s="249">
         <v>350</v>
       </c>
-      <c r="T15" s="252">
+      <c r="T15" s="251">
         <f>SUM(S15-Q15)</f>
         <v>209</v>
       </c>
@@ -6953,11 +6947,11 @@
       </c>
     </row>
     <row r="16" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B16" s="362"/>
+      <c r="B16" s="364"/>
       <c r="C16" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="366"/>
+      <c r="D16" s="372"/>
       <c r="E16" s="148" t="str">
         <f t="shared" ref="E16:P16" si="1">IF(E15=0, "", IF(MOD(E15, $D$15) = 0, E15 / $D$15, IF(INT(E15 / $D$15) = 0, MOD(E15, $D$15) &amp; " P", INT(E15 / $D$15) &amp; " + " &amp; MOD(E15, $D$15) &amp; " P")))</f>
         <v>18 P</v>
@@ -7006,10 +7000,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="353"/>
-      <c r="R16" s="355"/>
-      <c r="S16" s="251"/>
-      <c r="T16" s="253"/>
+      <c r="Q16" s="368"/>
+      <c r="R16" s="370"/>
+      <c r="S16" s="250"/>
+      <c r="T16" s="252"/>
       <c r="U16" s="30"/>
       <c r="V16" s="99"/>
       <c r="W16" s="100"/>
@@ -7021,13 +7015,13 @@
       </c>
     </row>
     <row r="17" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B17" s="361">
+      <c r="B17" s="363">
         <v>2</v>
       </c>
       <c r="C17" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="363">
+      <c r="D17" s="365">
         <v>32</v>
       </c>
       <c r="E17" s="145">
@@ -7050,17 +7044,17 @@
       <c r="N17" s="146"/>
       <c r="O17" s="147"/>
       <c r="P17" s="147"/>
-      <c r="Q17" s="352">
+      <c r="Q17" s="367">
         <f>SUM(E17:P17)</f>
         <v>298</v>
       </c>
-      <c r="R17" s="354">
+      <c r="R17" s="369">
         <v>12</v>
       </c>
-      <c r="S17" s="250">
+      <c r="S17" s="249">
         <v>790</v>
       </c>
-      <c r="T17" s="252">
+      <c r="T17" s="251">
         <f>SUM(S17-Q17)</f>
         <v>492</v>
       </c>
@@ -7091,11 +7085,11 @@
       </c>
     </row>
     <row r="18" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B18" s="362"/>
+      <c r="B18" s="364"/>
       <c r="C18" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="364"/>
+      <c r="D18" s="366"/>
       <c r="E18" s="148" t="str">
         <f t="shared" ref="E18:P18" si="3">IF(E17=0, "", IF(MOD(E17, $D$17) = 0, E17 / $D$17, IF(INT(E17 / $D$17) = 0, MOD(E17, $D$17) &amp; " P", INT(E17 / $D$17) &amp; " + " &amp; MOD(E17, $D$17) &amp; " P")))</f>
         <v>1 + 3 P</v>
@@ -7144,10 +7138,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="353"/>
-      <c r="R18" s="355"/>
-      <c r="S18" s="251"/>
-      <c r="T18" s="253"/>
+      <c r="Q18" s="368"/>
+      <c r="R18" s="370"/>
+      <c r="S18" s="250"/>
+      <c r="T18" s="252"/>
       <c r="U18" s="30"/>
       <c r="V18" s="99"/>
       <c r="W18" s="100"/>
@@ -7159,13 +7153,13 @@
       </c>
     </row>
     <row r="19" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B19" s="361">
+      <c r="B19" s="363">
         <v>3</v>
       </c>
       <c r="C19" s="163" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="363">
+      <c r="D19" s="365">
         <v>36</v>
       </c>
       <c r="E19" s="150">
@@ -7188,17 +7182,17 @@
       <c r="N19" s="151"/>
       <c r="O19" s="153"/>
       <c r="P19" s="153"/>
-      <c r="Q19" s="352">
+      <c r="Q19" s="367">
         <f>SUM(E19:P19)</f>
         <v>73</v>
       </c>
-      <c r="R19" s="354">
+      <c r="R19" s="369">
         <v>5</v>
       </c>
-      <c r="S19" s="250">
+      <c r="S19" s="249">
         <v>240</v>
       </c>
-      <c r="T19" s="252">
+      <c r="T19" s="251">
         <f>SUM(S19-Q19)</f>
         <v>167</v>
       </c>
@@ -7229,11 +7223,11 @@
       </c>
     </row>
     <row r="20" spans="2:37" ht="72" customHeight="1" thickBot="1">
-      <c r="B20" s="362"/>
+      <c r="B20" s="364"/>
       <c r="C20" s="165" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="364"/>
+      <c r="D20" s="366"/>
       <c r="E20" s="148" t="str">
         <f t="shared" ref="E20:P20" si="5">IF(E19=0, "", IF(MOD(E19, $D$19) = 0, E19/ $D$19, IF(INT(E19 / $D$19) = 0, MOD(E19, $D$19) &amp; " P", INT(E19 / $D$19) &amp; " + " &amp; MOD(E19, $D$19) &amp; " P")))</f>
         <v>3 P</v>
@@ -7282,10 +7276,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="353"/>
-      <c r="R20" s="355"/>
-      <c r="S20" s="251"/>
-      <c r="T20" s="253"/>
+      <c r="Q20" s="368"/>
+      <c r="R20" s="370"/>
+      <c r="S20" s="250"/>
+      <c r="T20" s="252"/>
       <c r="U20" s="30"/>
       <c r="V20" s="99"/>
       <c r="W20" s="100"/>
@@ -7297,13 +7291,13 @@
       </c>
     </row>
     <row r="21" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B21" s="361">
+      <c r="B21" s="363">
         <v>4</v>
       </c>
       <c r="C21" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="363">
+      <c r="D21" s="365">
         <v>32</v>
       </c>
       <c r="E21" s="145">
@@ -7326,17 +7320,17 @@
       <c r="N21" s="146"/>
       <c r="O21" s="147"/>
       <c r="P21" s="147"/>
-      <c r="Q21" s="352">
+      <c r="Q21" s="367">
         <f>SUM(E21:P21)</f>
         <v>699</v>
       </c>
-      <c r="R21" s="354">
+      <c r="R21" s="369">
         <v>24</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="249">
         <v>1272</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="251">
         <f>SUM(S21-Q21)</f>
         <v>573</v>
       </c>
@@ -7367,11 +7361,11 @@
       </c>
     </row>
     <row r="22" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B22" s="362"/>
+      <c r="B22" s="364"/>
       <c r="C22" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="364"/>
+      <c r="D22" s="366"/>
       <c r="E22" s="148" t="str">
         <f t="shared" ref="E22:P22" si="7">IF(E21=0, "", IF(MOD(E21, $D$21) = 0, E21/ $D$21, IF(INT(E21 / $D$21) = 0, MOD(E21, $D$21) &amp; " P", INT(E21 / $D$21) &amp; " + " &amp; MOD(E21, $D$21) &amp; " P")))</f>
         <v>4 + 3 P</v>
@@ -7420,10 +7414,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q22" s="353"/>
-      <c r="R22" s="355"/>
-      <c r="S22" s="251"/>
-      <c r="T22" s="253"/>
+      <c r="Q22" s="368"/>
+      <c r="R22" s="370"/>
+      <c r="S22" s="250"/>
+      <c r="T22" s="252"/>
       <c r="U22" s="30"/>
       <c r="V22" s="99"/>
       <c r="W22" s="100"/>
@@ -7441,7 +7435,7 @@
       <c r="C23" s="166" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="359">
+      <c r="D23" s="373">
         <v>18</v>
       </c>
       <c r="E23" s="154">
@@ -7464,17 +7458,17 @@
       <c r="N23" s="155"/>
       <c r="O23" s="157"/>
       <c r="P23" s="157"/>
-      <c r="Q23" s="352">
+      <c r="Q23" s="367">
         <f>SUM(E23:P23)</f>
         <v>34</v>
       </c>
-      <c r="R23" s="354">
+      <c r="R23" s="369">
         <v>4</v>
       </c>
-      <c r="S23" s="250">
+      <c r="S23" s="249">
         <v>100</v>
       </c>
-      <c r="T23" s="252">
+      <c r="T23" s="251">
         <f>SUM(S23-Q23)</f>
         <v>66</v>
       </c>
@@ -7509,7 +7503,7 @@
       <c r="C24" s="164" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="360"/>
+      <c r="D24" s="374"/>
       <c r="E24" s="158" t="str">
         <f t="shared" ref="E24:P24" si="9">IF(E23=0, "", IF(MOD(E23, $D$23) = 0, E23/ $D$23, IF(INT(E23 / $D$23) = 0, MOD(E23, $D$23) &amp; " P", INT(E23 / $D$23) &amp; " + " &amp; MOD(E23, $D$23) &amp; " P")))</f>
         <v>3 P</v>
@@ -7558,10 +7552,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q24" s="353"/>
-      <c r="R24" s="355"/>
-      <c r="S24" s="251"/>
-      <c r="T24" s="253"/>
+      <c r="Q24" s="368"/>
+      <c r="R24" s="370"/>
+      <c r="S24" s="250"/>
+      <c r="T24" s="252"/>
       <c r="U24" s="30"/>
       <c r="V24" s="99"/>
       <c r="W24" s="100"/>
@@ -7579,7 +7573,7 @@
       <c r="C25" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="350">
+      <c r="D25" s="375">
         <v>36</v>
       </c>
       <c r="E25" s="145">
@@ -7602,17 +7596,17 @@
       <c r="N25" s="146"/>
       <c r="O25" s="147"/>
       <c r="P25" s="147"/>
-      <c r="Q25" s="352">
+      <c r="Q25" s="367">
         <f>SUM(E25:P25)</f>
         <v>192</v>
       </c>
-      <c r="R25" s="354">
+      <c r="R25" s="369">
         <v>8</v>
       </c>
-      <c r="S25" s="250">
+      <c r="S25" s="249">
         <v>650</v>
       </c>
-      <c r="T25" s="252">
+      <c r="T25" s="251">
         <f>SUM(S25-Q25)</f>
         <v>458</v>
       </c>
@@ -7647,7 +7641,7 @@
       <c r="C26" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="351"/>
+      <c r="D26" s="376"/>
       <c r="E26" s="148" t="str">
         <f t="shared" ref="E26:P26" si="11">IF(E25=0, "", IF(MOD(E25, $D$25) = 0, E25/ $D$25, IF(INT(E25 / $D$25) = 0, MOD(E25, $D$25) &amp; " P", INT(E25 / $D$25) &amp; " + " &amp; MOD(E25, $D$25) &amp; " P")))</f>
         <v>10 P</v>
@@ -7696,10 +7690,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q26" s="353"/>
-      <c r="R26" s="355"/>
-      <c r="S26" s="251"/>
-      <c r="T26" s="253"/>
+      <c r="Q26" s="368"/>
+      <c r="R26" s="370"/>
+      <c r="S26" s="250"/>
+      <c r="T26" s="252"/>
       <c r="U26" s="30"/>
       <c r="V26" s="99"/>
       <c r="W26" s="100"/>
@@ -7717,7 +7711,7 @@
       <c r="C27" s="163" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="350">
+      <c r="D27" s="375">
         <v>20</v>
       </c>
       <c r="E27" s="145">
@@ -7740,17 +7734,17 @@
       <c r="N27" s="146"/>
       <c r="O27" s="147"/>
       <c r="P27" s="147"/>
-      <c r="Q27" s="352">
+      <c r="Q27" s="367">
         <f>SUM(E27:P27)</f>
         <v>49</v>
       </c>
-      <c r="R27" s="354">
+      <c r="R27" s="369">
         <v>5</v>
       </c>
-      <c r="S27" s="250">
+      <c r="S27" s="249">
         <v>140</v>
       </c>
-      <c r="T27" s="252">
+      <c r="T27" s="251">
         <f>SUM(S27-Q27)</f>
         <v>91</v>
       </c>
@@ -7785,7 +7779,7 @@
       <c r="C28" s="165" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="351"/>
+      <c r="D28" s="376"/>
       <c r="E28" s="148" t="str">
         <f t="shared" ref="E28:P28" si="13">IF(E27=0, "", IF(MOD(E27, $D$27) = 0, E27/ $D$27, IF(INT(E27 / $D$27) = 0, MOD(E27, $D$27) &amp; " P", INT(E27 / $D$27) &amp; " + " &amp; MOD(E27, $D$27) &amp; " P")))</f>
         <v>7 P</v>
@@ -7834,10 +7828,10 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q28" s="353"/>
-      <c r="R28" s="355"/>
-      <c r="S28" s="251"/>
-      <c r="T28" s="253"/>
+      <c r="Q28" s="368"/>
+      <c r="R28" s="370"/>
+      <c r="S28" s="250"/>
+      <c r="T28" s="252"/>
       <c r="U28" s="30"/>
       <c r="V28" s="95"/>
       <c r="W28" s="100"/>
@@ -7855,7 +7849,7 @@
       <c r="C29" s="167" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="350">
+      <c r="D29" s="375">
         <v>15</v>
       </c>
       <c r="E29" s="150">
@@ -7878,17 +7872,17 @@
       <c r="N29" s="151"/>
       <c r="O29" s="153"/>
       <c r="P29" s="153"/>
-      <c r="Q29" s="352">
+      <c r="Q29" s="367">
         <f>SUM(E29:P29)</f>
         <v>94</v>
       </c>
-      <c r="R29" s="354">
+      <c r="R29" s="369">
         <v>8</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="249">
         <v>240</v>
       </c>
-      <c r="T29" s="252">
+      <c r="T29" s="251">
         <f>SUM(S29-Q29)</f>
         <v>146</v>
       </c>
@@ -7923,7 +7917,7 @@
       <c r="C30" s="164" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="351"/>
+      <c r="D30" s="376"/>
       <c r="E30" s="148" t="str">
         <f t="shared" ref="E30:P30" si="14">IF(E29=0, "", IF(MOD(E29, $D$29) = 0, E29/ $D$29, IF(INT(E29 / $D$29) = 0, MOD(E29, $D$29) &amp; " P", INT(E29 / $D$29) &amp; " + " &amp; MOD(E29, $D$29) &amp; " P")))</f>
         <v>10 P</v>
@@ -7972,10 +7966,10 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q30" s="353"/>
-      <c r="R30" s="355"/>
-      <c r="S30" s="251"/>
-      <c r="T30" s="253"/>
+      <c r="Q30" s="368"/>
+      <c r="R30" s="370"/>
+      <c r="S30" s="250"/>
+      <c r="T30" s="252"/>
       <c r="U30" s="30"/>
       <c r="V30" s="95"/>
       <c r="W30" s="100"/>
@@ -7993,7 +7987,7 @@
       <c r="C31" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="350">
+      <c r="D31" s="375">
         <v>45</v>
       </c>
       <c r="E31" s="150">
@@ -8016,17 +8010,17 @@
       <c r="N31" s="151"/>
       <c r="O31" s="153"/>
       <c r="P31" s="153"/>
-      <c r="Q31" s="352">
+      <c r="Q31" s="367">
         <f>SUM(E31:P31)</f>
         <v>9</v>
       </c>
-      <c r="R31" s="358">
+      <c r="R31" s="377">
         <v>3</v>
       </c>
-      <c r="S31" s="250">
+      <c r="S31" s="249">
         <v>70</v>
       </c>
-      <c r="T31" s="252">
+      <c r="T31" s="251">
         <f>SUM(S31-Q31)</f>
         <v>61</v>
       </c>
@@ -8061,7 +8055,7 @@
       <c r="C32" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="351"/>
+      <c r="D32" s="376"/>
       <c r="E32" s="148" t="str">
         <f t="shared" ref="E32:P32" si="16">IF(E31=0, "", IF(MOD(E31, $D$31) = 0, E31/ $D$31, IF(INT(E31 / $D$31) = 0, MOD(E31, $D$31) &amp; " P", INT(E31 / $D$31) &amp; " + " &amp; MOD(E31, $D$31) &amp; " P")))</f>
         <v>1 P</v>
@@ -8110,10 +8104,10 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q32" s="353"/>
-      <c r="R32" s="355"/>
-      <c r="S32" s="251"/>
-      <c r="T32" s="253"/>
+      <c r="Q32" s="368"/>
+      <c r="R32" s="370"/>
+      <c r="S32" s="250"/>
+      <c r="T32" s="252"/>
       <c r="U32" s="30"/>
       <c r="V32" s="95"/>
       <c r="W32" s="100"/>
@@ -8131,7 +8125,7 @@
       <c r="C33" s="167" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="350">
+      <c r="D33" s="375">
         <v>15</v>
       </c>
       <c r="E33" s="150">
@@ -8154,17 +8148,17 @@
       <c r="N33" s="151"/>
       <c r="O33" s="153"/>
       <c r="P33" s="153"/>
-      <c r="Q33" s="352">
+      <c r="Q33" s="367">
         <f>SUM(E33:P33)</f>
         <v>134</v>
       </c>
-      <c r="R33" s="358">
+      <c r="R33" s="377">
         <v>11</v>
       </c>
-      <c r="S33" s="250">
+      <c r="S33" s="249">
         <v>320</v>
       </c>
-      <c r="T33" s="252">
+      <c r="T33" s="251">
         <f t="shared" ref="T33" si="17">SUM(S33-Q33)</f>
         <v>186</v>
       </c>
@@ -8199,7 +8193,7 @@
       <c r="C34" s="165" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="351"/>
+      <c r="D34" s="376"/>
       <c r="E34" s="148" t="str">
         <f>IF(E33=0, "", IF(MOD(E33, $D$33) = 0, E33/ $D$33, IF(INT(E33 / $D$33) = 0, MOD(E33, $D$33) &amp; " P", INT(E33 / $D$33) &amp; " + " &amp; MOD(E33, $D$33) &amp; " P")))</f>
         <v>1 + 8 P</v>
@@ -8248,10 +8242,10 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q34" s="353"/>
-      <c r="R34" s="355"/>
-      <c r="S34" s="251"/>
-      <c r="T34" s="253"/>
+      <c r="Q34" s="368"/>
+      <c r="R34" s="370"/>
+      <c r="S34" s="250"/>
+      <c r="T34" s="252"/>
       <c r="U34" s="30"/>
       <c r="V34" s="95"/>
       <c r="W34" s="100"/>
@@ -8269,7 +8263,7 @@
       <c r="C35" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="350">
+      <c r="D35" s="375">
         <v>15</v>
       </c>
       <c r="E35" s="159">
@@ -8292,17 +8286,17 @@
       <c r="N35" s="152"/>
       <c r="O35" s="160"/>
       <c r="P35" s="160"/>
-      <c r="Q35" s="352">
+      <c r="Q35" s="367">
         <f>SUM(E35:P35)</f>
         <v>82</v>
       </c>
-      <c r="R35" s="354">
+      <c r="R35" s="369">
         <v>7</v>
       </c>
-      <c r="S35" s="250">
+      <c r="S35" s="249">
         <v>190</v>
       </c>
-      <c r="T35" s="356">
+      <c r="T35" s="378">
         <f t="shared" ref="T35" si="19">SUM(S35-Q35)</f>
         <v>108</v>
       </c>
@@ -8337,7 +8331,7 @@
       <c r="C36" s="165" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="351"/>
+      <c r="D36" s="376"/>
       <c r="E36" s="148" t="str">
         <f>IF(E35=0, "", IF(MOD(E35, $D$35) = 0, E35/ $D$35, IF(INT(E35 / $D$35) = 0, MOD(E35, $D$35) &amp; " P", INT(E35 / $D$35) &amp; " + " &amp; MOD(E35, $D$35) &amp; " P")))</f>
         <v>9 P</v>
@@ -8386,10 +8380,10 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q36" s="353"/>
-      <c r="R36" s="355"/>
-      <c r="S36" s="251"/>
-      <c r="T36" s="357"/>
+      <c r="Q36" s="368"/>
+      <c r="R36" s="370"/>
+      <c r="S36" s="250"/>
+      <c r="T36" s="379"/>
       <c r="U36" s="30"/>
       <c r="V36" s="95"/>
       <c r="W36" s="100"/>
@@ -8404,7 +8398,7 @@
       <c r="C37" s="167" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="350">
+      <c r="D37" s="375">
         <v>27</v>
       </c>
       <c r="E37" s="145">
@@ -8427,17 +8421,17 @@
       <c r="N37" s="145"/>
       <c r="O37" s="145"/>
       <c r="P37" s="145"/>
-      <c r="Q37" s="352">
+      <c r="Q37" s="367">
         <f>SUM(E37:P37)</f>
         <v>192</v>
       </c>
-      <c r="R37" s="354">
+      <c r="R37" s="369">
         <v>9</v>
       </c>
-      <c r="S37" s="250">
+      <c r="S37" s="249">
         <v>440</v>
       </c>
-      <c r="T37" s="356">
+      <c r="T37" s="378">
         <f t="shared" ref="T37" si="21">SUM(S37-Q37)</f>
         <v>248</v>
       </c>
@@ -8472,7 +8466,7 @@
       <c r="C38" s="165" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="351"/>
+      <c r="D38" s="376"/>
       <c r="E38" s="148" t="str">
         <f>IF(E37=0, "", IF(MOD(E37, $D$37) = 0, E37/ $D$37, IF(INT(E37 / $D$37) = 0, MOD(E37, $D$37) &amp; " P", INT(E37 / $D$37) &amp; " + " &amp; MOD(E37, $D$37) &amp; " P")))</f>
         <v>1 + 2 P</v>
@@ -8521,10 +8515,10 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q38" s="353"/>
-      <c r="R38" s="355"/>
-      <c r="S38" s="251"/>
-      <c r="T38" s="357"/>
+      <c r="Q38" s="368"/>
+      <c r="R38" s="370"/>
+      <c r="S38" s="250"/>
+      <c r="T38" s="379"/>
       <c r="U38" s="30"/>
       <c r="V38" s="95"/>
       <c r="W38" s="100"/>
@@ -8539,7 +8533,7 @@
       <c r="C39" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="350">
+      <c r="D39" s="375">
         <v>20</v>
       </c>
       <c r="E39" s="145">
@@ -8562,17 +8556,17 @@
       <c r="N39" s="145"/>
       <c r="O39" s="145"/>
       <c r="P39" s="145"/>
-      <c r="Q39" s="352">
+      <c r="Q39" s="367">
         <f>SUM(E39:P39)</f>
         <v>213</v>
       </c>
-      <c r="R39" s="354">
+      <c r="R39" s="369">
         <v>12</v>
       </c>
-      <c r="S39" s="250">
+      <c r="S39" s="249">
         <v>450</v>
       </c>
-      <c r="T39" s="356">
+      <c r="T39" s="378">
         <f t="shared" ref="T39" si="23">SUM(S39-Q39)</f>
         <v>237</v>
       </c>
@@ -8607,7 +8601,7 @@
       <c r="C40" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="D40" s="351"/>
+      <c r="D40" s="376"/>
       <c r="E40" s="148" t="str">
         <f>IF(E39=0, "", IF(MOD(E39, $D$39) = 0, E39/ $D$39, IF(INT(E39 / $D$39) = 0, MOD(E39, $D$39) &amp; " P", INT(E39 / $D$39) &amp; " + " &amp; MOD(E39, $D$39) &amp; " P")))</f>
         <v>14 P</v>
@@ -8656,10 +8650,10 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="Q40" s="353"/>
-      <c r="R40" s="355"/>
-      <c r="S40" s="251"/>
-      <c r="T40" s="357"/>
+      <c r="Q40" s="368"/>
+      <c r="R40" s="370"/>
+      <c r="S40" s="250"/>
+      <c r="T40" s="379"/>
       <c r="U40" s="30"/>
       <c r="V40" s="95"/>
       <c r="W40" s="100"/>
@@ -8674,7 +8668,7 @@
       <c r="C41" s="166" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="350">
+      <c r="D41" s="375">
         <v>32</v>
       </c>
       <c r="E41" s="145">
@@ -8697,17 +8691,17 @@
       <c r="N41" s="145"/>
       <c r="O41" s="145"/>
       <c r="P41" s="145"/>
-      <c r="Q41" s="352">
+      <c r="Q41" s="367">
         <f>SUM(E41:P41)</f>
         <v>93</v>
       </c>
-      <c r="R41" s="354">
+      <c r="R41" s="369">
         <v>5</v>
       </c>
-      <c r="S41" s="250">
+      <c r="S41" s="249">
         <v>220</v>
       </c>
-      <c r="T41" s="252">
+      <c r="T41" s="251">
         <f t="shared" ref="T41" si="25">SUM(S41-Q41)</f>
         <v>127</v>
       </c>
@@ -8742,7 +8736,7 @@
       <c r="C42" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="D42" s="351"/>
+      <c r="D42" s="376"/>
       <c r="E42" s="148" t="str">
         <f>IF(E41=0, "", IF(MOD(E41, $D$41) = 0, E41/ $D$41, IF(INT(E41 / $D$41) = 0, MOD(E41, $D$41) &amp; " P", INT(E41 / $D$41) &amp; " + " &amp; MOD(E41, $D$41) &amp; " P")))</f>
         <v>7 P</v>
@@ -8791,10 +8785,10 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="Q42" s="353"/>
-      <c r="R42" s="355"/>
-      <c r="S42" s="251"/>
-      <c r="T42" s="253"/>
+      <c r="Q42" s="368"/>
+      <c r="R42" s="370"/>
+      <c r="S42" s="250"/>
+      <c r="T42" s="252"/>
       <c r="U42" s="30"/>
       <c r="V42" s="95"/>
       <c r="W42" s="100"/>
@@ -8809,7 +8803,7 @@
       <c r="C43" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="350">
+      <c r="D43" s="375">
         <v>15</v>
       </c>
       <c r="E43" s="145">
@@ -8832,17 +8826,17 @@
       <c r="N43" s="145"/>
       <c r="O43" s="145"/>
       <c r="P43" s="145"/>
-      <c r="Q43" s="352">
+      <c r="Q43" s="367">
         <f>SUM(E43:P43)</f>
         <v>40</v>
       </c>
-      <c r="R43" s="354">
+      <c r="R43" s="369">
         <v>5</v>
       </c>
-      <c r="S43" s="250">
+      <c r="S43" s="249">
         <v>100</v>
       </c>
-      <c r="T43" s="252">
+      <c r="T43" s="251">
         <f t="shared" ref="T43" si="27">SUM(S43-Q43)</f>
         <v>60</v>
       </c>
@@ -8877,7 +8871,7 @@
       <c r="C44" s="165" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="351"/>
+      <c r="D44" s="376"/>
       <c r="E44" s="148" t="str">
         <f>IF(E43=0, "", IF(MOD(E43, $D$43) = 0, E43/ $D$43, IF(INT(E43 / $D$43) = 0, MOD(E43, $D$43) &amp; " P", INT(E43 / $D$43) &amp; " + " &amp; MOD(E43, $D$43) &amp; " P")))</f>
         <v>5 P</v>
@@ -8926,10 +8920,10 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="Q44" s="353"/>
-      <c r="R44" s="355"/>
-      <c r="S44" s="251"/>
-      <c r="T44" s="253"/>
+      <c r="Q44" s="368"/>
+      <c r="R44" s="370"/>
+      <c r="S44" s="250"/>
+      <c r="T44" s="252"/>
       <c r="U44" s="30"/>
       <c r="V44" s="95"/>
       <c r="W44" s="100"/>
@@ -8938,11 +8932,11 @@
       <c r="Z44" s="102"/>
     </row>
     <row r="45" spans="2:37" ht="73.5" customHeight="1" thickBot="1">
-      <c r="B45" s="274" t="s">
+      <c r="B45" s="340" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="275"/>
-      <c r="D45" s="276"/>
+      <c r="C45" s="341"/>
+      <c r="D45" s="342"/>
       <c r="E45" s="84">
         <v>-22</v>
       </c>
@@ -8979,7 +8973,7 @@
       <c r="Y45" s="106"/>
       <c r="Z45" s="105"/>
     </row>
-    <row r="46" spans="2:37" ht="13.2" customHeight="1" thickBot="1">
+    <row r="46" spans="2:37" ht="13.15" customHeight="1" thickBot="1">
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -9007,92 +9001,92 @@
     <row r="47" spans="2:37" ht="105" hidden="1" customHeight="1" thickBot="1"/>
     <row r="48" spans="2:37" ht="37.5" hidden="1" customHeight="1" thickBot="1"/>
     <row r="49" spans="2:20" ht="48.75" hidden="1" customHeight="1" thickBot="1"/>
-    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.95" customHeight="1" thickBot="1">
-      <c r="B50" s="281" t="s">
+    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.900000000000006" customHeight="1" thickBot="1">
+      <c r="B50" s="324" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="282"/>
-      <c r="D50" s="281" t="s">
+      <c r="C50" s="325"/>
+      <c r="D50" s="324" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="282"/>
-      <c r="F50" s="281" t="s">
+      <c r="E50" s="325"/>
+      <c r="F50" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="G50" s="282"/>
-      <c r="H50" s="281" t="s">
+      <c r="G50" s="325"/>
+      <c r="H50" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="282"/>
+      <c r="I50" s="325"/>
       <c r="J50" s="38"/>
-      <c r="M50" s="345" t="s">
+      <c r="M50" s="266" t="s">
         <v>88</v>
       </c>
-      <c r="N50" s="345"/>
-      <c r="O50" s="345"/>
-      <c r="P50" s="345"/>
-      <c r="Q50" s="348">
+      <c r="N50" s="266"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="380">
         <f>SUM(R45)</f>
         <v>124</v>
       </c>
-      <c r="R50" s="340" t="s">
+      <c r="R50" s="255" t="s">
         <v>89</v>
       </c>
       <c r="T50" s="36"/>
     </row>
-    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1">
-      <c r="B51" s="283" t="s">
+    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1">
+      <c r="B51" s="326" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="284"/>
-      <c r="D51" s="285"/>
-      <c r="E51" s="286"/>
-      <c r="F51" s="285"/>
-      <c r="G51" s="286"/>
-      <c r="H51" s="285"/>
-      <c r="I51" s="286"/>
+      <c r="C51" s="327"/>
+      <c r="D51" s="328"/>
+      <c r="E51" s="329"/>
+      <c r="F51" s="328"/>
+      <c r="G51" s="329"/>
+      <c r="H51" s="328"/>
+      <c r="I51" s="329"/>
       <c r="J51" s="38"/>
-      <c r="M51" s="345"/>
-      <c r="N51" s="345"/>
-      <c r="O51" s="345"/>
-      <c r="P51" s="345"/>
-      <c r="Q51" s="349"/>
-      <c r="R51" s="340"/>
+      <c r="M51" s="266"/>
+      <c r="N51" s="266"/>
+      <c r="O51" s="266"/>
+      <c r="P51" s="266"/>
+      <c r="Q51" s="381"/>
+      <c r="R51" s="255"/>
       <c r="T51" s="36"/>
     </row>
-    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
-      <c r="B52" s="269" t="s">
+    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
+      <c r="B52" s="335" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="270"/>
-      <c r="D52" s="271"/>
-      <c r="E52" s="272"/>
-      <c r="F52" s="271"/>
-      <c r="G52" s="272"/>
-      <c r="H52" s="271"/>
-      <c r="I52" s="272"/>
+      <c r="C52" s="336"/>
+      <c r="D52" s="337"/>
+      <c r="E52" s="338"/>
+      <c r="F52" s="337"/>
+      <c r="G52" s="338"/>
+      <c r="H52" s="337"/>
+      <c r="I52" s="338"/>
       <c r="J52" s="38"/>
       <c r="M52" s="67"/>
-      <c r="N52" s="273" t="s">
+      <c r="N52" s="339" t="s">
         <v>73</v>
       </c>
-      <c r="O52" s="273"/>
-      <c r="P52" s="273"/>
-      <c r="Q52" s="273"/>
-      <c r="R52" s="273"/>
+      <c r="O52" s="339"/>
+      <c r="P52" s="339"/>
+      <c r="Q52" s="339"/>
+      <c r="R52" s="339"/>
       <c r="T52" s="36"/>
     </row>
-    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
-      <c r="B53" s="277" t="s">
+    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
+      <c r="B53" s="320" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="278"/>
-      <c r="D53" s="279"/>
-      <c r="E53" s="280"/>
-      <c r="F53" s="279"/>
-      <c r="G53" s="280"/>
-      <c r="H53" s="279"/>
-      <c r="I53" s="280"/>
+      <c r="C53" s="321"/>
+      <c r="D53" s="322"/>
+      <c r="E53" s="323"/>
+      <c r="F53" s="322"/>
+      <c r="G53" s="323"/>
+      <c r="H53" s="322"/>
+      <c r="I53" s="323"/>
       <c r="J53" s="38"/>
       <c r="K53" s="53" t="s">
         <v>77</v>
@@ -9114,7 +9108,7 @@
       </c>
       <c r="T53" s="36"/>
     </row>
-    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.2" customHeight="1" thickBot="1">
+    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.150000000000006" customHeight="1" thickBot="1">
       <c r="B54" s="38"/>
       <c r="C54" s="38"/>
       <c r="D54" s="89"/>
@@ -9136,6 +9130,106 @@
     </row>
   </sheetData>
   <mergeCells count="124">
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="N52:R52"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="M50:P51"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="E10:R11"/>
@@ -9160,106 +9254,6 @@
     <mergeCell ref="T12:T14"/>
     <mergeCell ref="V12:V13"/>
     <mergeCell ref="W12:W13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="T33:T34"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:S36"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="S43:S44"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="N52:R52"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="M50:P51"/>
-    <mergeCell ref="Q50:Q51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0"/>
@@ -9270,29 +9264,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96D3011-5F30-4B22-86C3-114347F44C10}">
   <dimension ref="B4:AK54"/>
-  <sheetFormatPr defaultColWidth="5.69921875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22.59765625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="174.8984375" style="30" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" style="30" customWidth="1"/>
-    <col min="5" max="8" width="34.69921875" style="30" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="47.8984375" style="30" customWidth="1"/>
-    <col min="15" max="15" width="47.8984375" style="29" customWidth="1"/>
-    <col min="16" max="16" width="47.8984375" style="29" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="47.8984375" style="29" customWidth="1"/>
-    <col min="18" max="18" width="47.8984375" style="36" customWidth="1"/>
-    <col min="19" max="19" width="27.3984375" style="29" customWidth="1"/>
-    <col min="20" max="20" width="27.3984375" style="127" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="30" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="174.875" style="30" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="30" customWidth="1"/>
+    <col min="5" max="8" width="34.75" style="30" hidden="1" customWidth="1"/>
+    <col min="9" max="14" width="47.875" style="30" customWidth="1"/>
+    <col min="15" max="15" width="47.875" style="29" customWidth="1"/>
+    <col min="16" max="16" width="47.875" style="29" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="47.875" style="29" customWidth="1"/>
+    <col min="18" max="18" width="47.875" style="36" customWidth="1"/>
+    <col min="19" max="19" width="27.375" style="29" customWidth="1"/>
+    <col min="20" max="20" width="27.375" style="127" customWidth="1"/>
     <col min="21" max="21" width="9.5" style="67" customWidth="1"/>
-    <col min="22" max="25" width="35.8984375" style="67" customWidth="1"/>
-    <col min="26" max="26" width="35.8984375" style="30" customWidth="1"/>
-    <col min="27" max="36" width="5.69921875" style="30"/>
-    <col min="37" max="37" width="10.09765625" style="30" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="5.69921875" style="30"/>
+    <col min="22" max="25" width="35.875" style="67" customWidth="1"/>
+    <col min="26" max="26" width="35.875" style="30" customWidth="1"/>
+    <col min="27" max="36" width="5.75" style="30"/>
+    <col min="37" max="37" width="10.125" style="30" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="5.75" style="30"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:37" ht="31.95" customHeight="1">
+    <row r="4" spans="2:37" ht="31.9" customHeight="1">
       <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -9303,8 +9297,8 @@
       <c r="I4" s="37"/>
       <c r="J4" s="28"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="287"/>
-      <c r="M4" s="287"/>
+      <c r="L4" s="298"/>
+      <c r="M4" s="298"/>
       <c r="N4" s="54"/>
       <c r="O4" s="55"/>
       <c r="P4" s="55"/>
@@ -9334,157 +9328,157 @@
       <c r="M7" s="49"/>
     </row>
     <row r="9" spans="2:37" ht="15" customHeight="1" thickBot="1"/>
-    <row r="10" spans="2:37" ht="71.400000000000006" customHeight="1" thickBot="1">
-      <c r="B10" s="367" t="s">
+    <row r="10" spans="2:37" ht="71.45" customHeight="1" thickBot="1">
+      <c r="B10" s="347" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="367"/>
-      <c r="D10" s="367"/>
-      <c r="E10" s="369" t="s">
+      <c r="C10" s="347"/>
+      <c r="D10" s="347"/>
+      <c r="E10" s="349" t="s">
         <v>137</v>
       </c>
-      <c r="F10" s="370"/>
-      <c r="G10" s="370"/>
-      <c r="H10" s="370"/>
-      <c r="I10" s="370"/>
-      <c r="J10" s="370"/>
-      <c r="K10" s="370"/>
-      <c r="L10" s="370"/>
-      <c r="M10" s="370"/>
-      <c r="N10" s="370"/>
-      <c r="O10" s="370"/>
-      <c r="P10" s="370"/>
-      <c r="Q10" s="370"/>
-      <c r="R10" s="371"/>
+      <c r="F10" s="350"/>
+      <c r="G10" s="350"/>
+      <c r="H10" s="350"/>
+      <c r="I10" s="350"/>
+      <c r="J10" s="350"/>
+      <c r="K10" s="350"/>
+      <c r="L10" s="350"/>
+      <c r="M10" s="350"/>
+      <c r="N10" s="350"/>
+      <c r="O10" s="350"/>
+      <c r="P10" s="350"/>
+      <c r="Q10" s="350"/>
+      <c r="R10" s="351"/>
       <c r="U10" s="29"/>
       <c r="Z10" s="67"/>
       <c r="AA10" s="35"/>
     </row>
     <row r="11" spans="2:37" ht="3" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="368"/>
-      <c r="C11" s="368"/>
-      <c r="D11" s="368"/>
-      <c r="E11" s="372"/>
-      <c r="F11" s="373"/>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
-      <c r="K11" s="373"/>
-      <c r="L11" s="373"/>
-      <c r="M11" s="373"/>
-      <c r="N11" s="373"/>
-      <c r="O11" s="373"/>
-      <c r="P11" s="373"/>
-      <c r="Q11" s="373"/>
-      <c r="R11" s="374"/>
+      <c r="B11" s="348"/>
+      <c r="C11" s="348"/>
+      <c r="D11" s="348"/>
+      <c r="E11" s="352"/>
+      <c r="F11" s="353"/>
+      <c r="G11" s="353"/>
+      <c r="H11" s="353"/>
+      <c r="I11" s="353"/>
+      <c r="J11" s="353"/>
+      <c r="K11" s="353"/>
+      <c r="L11" s="353"/>
+      <c r="M11" s="353"/>
+      <c r="N11" s="353"/>
+      <c r="O11" s="353"/>
+      <c r="P11" s="353"/>
+      <c r="Q11" s="353"/>
+      <c r="R11" s="354"/>
       <c r="S11" s="68"/>
       <c r="T11" s="128"/>
       <c r="U11" s="34"/>
-      <c r="W11" s="266"/>
-      <c r="X11" s="267"/>
-      <c r="Y11" s="267"/>
-      <c r="Z11" s="267"/>
-      <c r="AA11" s="268"/>
+      <c r="W11" s="332"/>
+      <c r="X11" s="333"/>
+      <c r="Y11" s="333"/>
+      <c r="Z11" s="333"/>
+      <c r="AA11" s="334"/>
     </row>
     <row r="12" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B12" s="322" t="s">
+      <c r="B12" s="282" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="323"/>
-      <c r="D12" s="328" t="s">
+      <c r="C12" s="283"/>
+      <c r="D12" s="288" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="331" t="s">
+      <c r="E12" s="291" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="332"/>
-      <c r="G12" s="333" t="s">
+      <c r="F12" s="292"/>
+      <c r="G12" s="293" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="334"/>
-      <c r="I12" s="313" t="s">
+      <c r="H12" s="294"/>
+      <c r="I12" s="273" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="314"/>
-      <c r="K12" s="298" t="s">
+      <c r="J12" s="274"/>
+      <c r="K12" s="307" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="299"/>
-      <c r="M12" s="300"/>
-      <c r="N12" s="308" t="s">
+      <c r="L12" s="308"/>
+      <c r="M12" s="309"/>
+      <c r="N12" s="317" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="309"/>
+      <c r="O12" s="318"/>
       <c r="P12" s="139"/>
-      <c r="Q12" s="315" t="s">
+      <c r="Q12" s="275" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="316"/>
-      <c r="S12" s="319" t="s">
+      <c r="R12" s="276"/>
+      <c r="S12" s="279" t="s">
         <v>78</v>
       </c>
-      <c r="T12" s="335" t="s">
+      <c r="T12" s="295" t="s">
         <v>79</v>
       </c>
       <c r="U12" s="30"/>
-      <c r="V12" s="381" t="s">
+      <c r="V12" s="361" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="377" t="s">
+      <c r="W12" s="357" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="375" t="s">
+      <c r="X12" s="355" t="s">
         <v>85</v>
       </c>
-      <c r="Y12" s="377" t="s">
+      <c r="Y12" s="357" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="379" t="s">
+      <c r="Z12" s="359" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B13" s="324"/>
-      <c r="C13" s="325"/>
-      <c r="D13" s="329"/>
-      <c r="E13" s="331" t="s">
+      <c r="B13" s="284"/>
+      <c r="C13" s="285"/>
+      <c r="D13" s="289"/>
+      <c r="E13" s="291" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="332"/>
-      <c r="G13" s="333" t="s">
+      <c r="F13" s="292"/>
+      <c r="G13" s="293" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="334"/>
-      <c r="I13" s="313" t="s">
+      <c r="H13" s="294"/>
+      <c r="I13" s="273" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="314"/>
-      <c r="K13" s="298" t="s">
+      <c r="J13" s="274"/>
+      <c r="K13" s="307" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="299"/>
-      <c r="M13" s="300"/>
-      <c r="N13" s="308" t="s">
+      <c r="L13" s="308"/>
+      <c r="M13" s="309"/>
+      <c r="N13" s="317" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="309"/>
+      <c r="O13" s="318"/>
       <c r="P13" s="139"/>
-      <c r="Q13" s="317"/>
-      <c r="R13" s="318"/>
-      <c r="S13" s="320"/>
-      <c r="T13" s="336"/>
+      <c r="Q13" s="277"/>
+      <c r="R13" s="278"/>
+      <c r="S13" s="280"/>
+      <c r="T13" s="296"/>
       <c r="U13" s="30"/>
-      <c r="V13" s="382"/>
-      <c r="W13" s="378"/>
-      <c r="X13" s="376"/>
-      <c r="Y13" s="378"/>
-      <c r="Z13" s="380"/>
+      <c r="V13" s="362"/>
+      <c r="W13" s="358"/>
+      <c r="X13" s="356"/>
+      <c r="Y13" s="358"/>
+      <c r="Z13" s="360"/>
     </row>
     <row r="14" spans="2:37" ht="129" customHeight="1" thickBot="1">
-      <c r="B14" s="326"/>
-      <c r="C14" s="327"/>
-      <c r="D14" s="330"/>
+      <c r="B14" s="286"/>
+      <c r="C14" s="287"/>
+      <c r="D14" s="290"/>
       <c r="E14" s="130" t="s">
         <v>0</v>
       </c>
@@ -9527,8 +9521,8 @@
       <c r="R14" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="S14" s="321"/>
-      <c r="T14" s="337"/>
+      <c r="S14" s="281"/>
+      <c r="T14" s="297"/>
       <c r="U14" s="30"/>
       <c r="V14" s="91"/>
       <c r="W14" s="92"/>
@@ -9540,13 +9534,13 @@
       </c>
     </row>
     <row r="15" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B15" s="361">
+      <c r="B15" s="363">
         <v>1</v>
       </c>
       <c r="C15" s="161" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="389">
+      <c r="D15" s="384">
         <v>36</v>
       </c>
       <c r="E15" s="115"/>
@@ -9575,17 +9569,17 @@
         <v>18</v>
       </c>
       <c r="P15" s="117"/>
-      <c r="Q15" s="352">
+      <c r="Q15" s="367">
         <f>SUM(E15:P15)</f>
         <v>168</v>
       </c>
-      <c r="R15" s="354">
+      <c r="R15" s="369">
         <v>8</v>
       </c>
-      <c r="S15" s="250">
+      <c r="S15" s="249">
         <v>350</v>
       </c>
-      <c r="T15" s="252">
+      <c r="T15" s="251">
         <f>SUM(S15-Q15)</f>
         <v>182</v>
       </c>
@@ -9616,11 +9610,11 @@
       </c>
     </row>
     <row r="16" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B16" s="362"/>
+      <c r="B16" s="364"/>
       <c r="C16" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="390"/>
+      <c r="D16" s="385"/>
       <c r="E16" s="118" t="str">
         <f t="shared" ref="E16:P16" si="1">IF(E15=0, "", IF(MOD(E15, $D$15) = 0, E15 / $D$15, IF(INT(E15 / $D$15) = 0, MOD(E15, $D$15) &amp; " P", INT(E15 / $D$15) &amp; " + " &amp; MOD(E15, $D$15) &amp; " P")))</f>
         <v/>
@@ -9669,10 +9663,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="353"/>
-      <c r="R16" s="355"/>
-      <c r="S16" s="251"/>
-      <c r="T16" s="253"/>
+      <c r="Q16" s="368"/>
+      <c r="R16" s="370"/>
+      <c r="S16" s="250"/>
+      <c r="T16" s="252"/>
       <c r="U16" s="30"/>
       <c r="V16" s="99"/>
       <c r="W16" s="100"/>
@@ -9684,13 +9678,13 @@
       </c>
     </row>
     <row r="17" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B17" s="361">
+      <c r="B17" s="363">
         <v>2</v>
       </c>
       <c r="C17" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="387">
+      <c r="D17" s="382">
         <v>32</v>
       </c>
       <c r="E17" s="115"/>
@@ -9719,17 +9713,17 @@
         <v>23</v>
       </c>
       <c r="P17" s="117"/>
-      <c r="Q17" s="352">
+      <c r="Q17" s="367">
         <f>SUM(E17:P17)</f>
         <v>455</v>
       </c>
-      <c r="R17" s="354">
+      <c r="R17" s="369">
         <v>18</v>
       </c>
-      <c r="S17" s="250">
+      <c r="S17" s="249">
         <v>790</v>
       </c>
-      <c r="T17" s="252">
+      <c r="T17" s="251">
         <f>SUM(S17-Q17)</f>
         <v>335</v>
       </c>
@@ -9760,11 +9754,11 @@
       </c>
     </row>
     <row r="18" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B18" s="362"/>
+      <c r="B18" s="364"/>
       <c r="C18" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="388"/>
+      <c r="D18" s="383"/>
       <c r="E18" s="118" t="str">
         <f t="shared" ref="E18:P18" si="3">IF(E17=0, "", IF(MOD(E17, $D$17) = 0, E17 / $D$17, IF(INT(E17 / $D$17) = 0, MOD(E17, $D$17) &amp; " P", INT(E17 / $D$17) &amp; " + " &amp; MOD(E17, $D$17) &amp; " P")))</f>
         <v/>
@@ -9813,10 +9807,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="353"/>
-      <c r="R18" s="355"/>
-      <c r="S18" s="251"/>
-      <c r="T18" s="253"/>
+      <c r="Q18" s="368"/>
+      <c r="R18" s="370"/>
+      <c r="S18" s="250"/>
+      <c r="T18" s="252"/>
       <c r="U18" s="30"/>
       <c r="V18" s="99"/>
       <c r="W18" s="100"/>
@@ -9828,13 +9822,13 @@
       </c>
     </row>
     <row r="19" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B19" s="361">
+      <c r="B19" s="363">
         <v>3</v>
       </c>
       <c r="C19" s="163" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="387">
+      <c r="D19" s="382">
         <v>36</v>
       </c>
       <c r="E19" s="119"/>
@@ -9863,17 +9857,17 @@
         <v>6</v>
       </c>
       <c r="P19" s="122"/>
-      <c r="Q19" s="352">
+      <c r="Q19" s="367">
         <f>SUM(E19:P19)</f>
         <v>117</v>
       </c>
-      <c r="R19" s="354">
+      <c r="R19" s="369">
         <v>8</v>
       </c>
-      <c r="S19" s="250">
+      <c r="S19" s="249">
         <v>240</v>
       </c>
-      <c r="T19" s="252">
+      <c r="T19" s="251">
         <f>SUM(S19-Q19)</f>
         <v>123</v>
       </c>
@@ -9904,11 +9898,11 @@
       </c>
     </row>
     <row r="20" spans="2:37" ht="72" customHeight="1" thickBot="1">
-      <c r="B20" s="362"/>
+      <c r="B20" s="364"/>
       <c r="C20" s="165" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="388"/>
+      <c r="D20" s="383"/>
       <c r="E20" s="118" t="str">
         <f t="shared" ref="E20:P20" si="5">IF(E19=0, "", IF(MOD(E19, $D$19) = 0, E19/ $D$19, IF(INT(E19 / $D$19) = 0, MOD(E19, $D$19) &amp; " P", INT(E19 / $D$19) &amp; " + " &amp; MOD(E19, $D$19) &amp; " P")))</f>
         <v/>
@@ -9957,10 +9951,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="353"/>
-      <c r="R20" s="355"/>
-      <c r="S20" s="251"/>
-      <c r="T20" s="253"/>
+      <c r="Q20" s="368"/>
+      <c r="R20" s="370"/>
+      <c r="S20" s="250"/>
+      <c r="T20" s="252"/>
       <c r="U20" s="30"/>
       <c r="V20" s="99"/>
       <c r="W20" s="100"/>
@@ -9972,13 +9966,13 @@
       </c>
     </row>
     <row r="21" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B21" s="361">
+      <c r="B21" s="363">
         <v>4</v>
       </c>
       <c r="C21" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="387">
+      <c r="D21" s="382">
         <v>32</v>
       </c>
       <c r="E21" s="115"/>
@@ -10007,17 +10001,17 @@
         <v>68</v>
       </c>
       <c r="P21" s="117"/>
-      <c r="Q21" s="352">
+      <c r="Q21" s="367">
         <f>SUM(E21:P21)</f>
         <v>571</v>
       </c>
-      <c r="R21" s="354">
+      <c r="R21" s="369">
         <v>23</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="249">
         <v>1272</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="251">
         <f>SUM(S21-Q21)</f>
         <v>701</v>
       </c>
@@ -10048,11 +10042,11 @@
       </c>
     </row>
     <row r="22" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B22" s="362"/>
+      <c r="B22" s="364"/>
       <c r="C22" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="388"/>
+      <c r="D22" s="383"/>
       <c r="E22" s="118" t="str">
         <f t="shared" ref="E22:P22" si="7">IF(E21=0, "", IF(MOD(E21, $D$21) = 0, E21/ $D$21, IF(INT(E21 / $D$21) = 0, MOD(E21, $D$21) &amp; " P", INT(E21 / $D$21) &amp; " + " &amp; MOD(E21, $D$21) &amp; " P")))</f>
         <v/>
@@ -10101,10 +10095,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q22" s="353"/>
-      <c r="R22" s="355"/>
-      <c r="S22" s="251"/>
-      <c r="T22" s="253"/>
+      <c r="Q22" s="368"/>
+      <c r="R22" s="370"/>
+      <c r="S22" s="250"/>
+      <c r="T22" s="252"/>
       <c r="U22" s="30"/>
       <c r="V22" s="99"/>
       <c r="W22" s="100"/>
@@ -10122,7 +10116,7 @@
       <c r="C23" s="166" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="385">
+      <c r="D23" s="386">
         <v>18</v>
       </c>
       <c r="E23" s="123"/>
@@ -10151,17 +10145,17 @@
         <v>2</v>
       </c>
       <c r="P23" s="125"/>
-      <c r="Q23" s="352">
+      <c r="Q23" s="367">
         <f>SUM(E23:P23)</f>
         <v>40</v>
       </c>
-      <c r="R23" s="354">
+      <c r="R23" s="369">
         <v>8</v>
       </c>
-      <c r="S23" s="250">
+      <c r="S23" s="249">
         <v>100</v>
       </c>
-      <c r="T23" s="252">
+      <c r="T23" s="251">
         <f>SUM(S23-Q23)</f>
         <v>60</v>
       </c>
@@ -10196,7 +10190,7 @@
       <c r="C24" s="164" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="386"/>
+      <c r="D24" s="387"/>
       <c r="E24" s="126" t="str">
         <f t="shared" ref="E24:P24" si="9">IF(E23=0, "", IF(MOD(E23, $D$23) = 0, E23/ $D$23, IF(INT(E23 / $D$23) = 0, MOD(E23, $D$23) &amp; " P", INT(E23 / $D$23) &amp; " + " &amp; MOD(E23, $D$23) &amp; " P")))</f>
         <v/>
@@ -10245,10 +10239,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q24" s="353"/>
-      <c r="R24" s="355"/>
-      <c r="S24" s="251"/>
-      <c r="T24" s="253"/>
+      <c r="Q24" s="368"/>
+      <c r="R24" s="370"/>
+      <c r="S24" s="250"/>
+      <c r="T24" s="252"/>
       <c r="U24" s="30"/>
       <c r="V24" s="99"/>
       <c r="W24" s="100"/>
@@ -10266,7 +10260,7 @@
       <c r="C25" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="383">
+      <c r="D25" s="388">
         <v>36</v>
       </c>
       <c r="E25" s="115"/>
@@ -10295,17 +10289,17 @@
         <v>20</v>
       </c>
       <c r="P25" s="117"/>
-      <c r="Q25" s="352">
+      <c r="Q25" s="367">
         <f>SUM(E25:P25)</f>
         <v>437</v>
       </c>
-      <c r="R25" s="354">
+      <c r="R25" s="369">
         <v>16</v>
       </c>
-      <c r="S25" s="250">
+      <c r="S25" s="249">
         <v>650</v>
       </c>
-      <c r="T25" s="252">
+      <c r="T25" s="251">
         <f>SUM(S25-Q25)</f>
         <v>213</v>
       </c>
@@ -10340,7 +10334,7 @@
       <c r="C26" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="384"/>
+      <c r="D26" s="389"/>
       <c r="E26" s="118" t="str">
         <f t="shared" ref="E26:P26" si="11">IF(E25=0, "", IF(MOD(E25, $D$25) = 0, E25/ $D$25, IF(INT(E25 / $D$25) = 0, MOD(E25, $D$25) &amp; " P", INT(E25 / $D$25) &amp; " + " &amp; MOD(E25, $D$25) &amp; " P")))</f>
         <v/>
@@ -10389,10 +10383,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q26" s="353"/>
-      <c r="R26" s="355"/>
-      <c r="S26" s="251"/>
-      <c r="T26" s="253"/>
+      <c r="Q26" s="368"/>
+      <c r="R26" s="370"/>
+      <c r="S26" s="250"/>
+      <c r="T26" s="252"/>
       <c r="U26" s="30"/>
       <c r="V26" s="99"/>
       <c r="W26" s="100"/>
@@ -10410,7 +10404,7 @@
       <c r="C27" s="163" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="383">
+      <c r="D27" s="388">
         <v>20</v>
       </c>
       <c r="E27" s="115"/>
@@ -10439,17 +10433,17 @@
         <v>8</v>
       </c>
       <c r="P27" s="117"/>
-      <c r="Q27" s="352">
+      <c r="Q27" s="367">
         <f>SUM(E27:P27)</f>
         <v>75</v>
       </c>
-      <c r="R27" s="354">
+      <c r="R27" s="369">
         <v>7</v>
       </c>
-      <c r="S27" s="250">
+      <c r="S27" s="249">
         <v>140</v>
       </c>
-      <c r="T27" s="252">
+      <c r="T27" s="251">
         <f>SUM(S27-Q27)</f>
         <v>65</v>
       </c>
@@ -10484,7 +10478,7 @@
       <c r="C28" s="165" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="384"/>
+      <c r="D28" s="389"/>
       <c r="E28" s="118" t="str">
         <f t="shared" ref="E28:P28" si="13">IF(E27=0, "", IF(MOD(E27, $D$27) = 0, E27/ $D$27, IF(INT(E27 / $D$27) = 0, MOD(E27, $D$27) &amp; " P", INT(E27 / $D$27) &amp; " + " &amp; MOD(E27, $D$27) &amp; " P")))</f>
         <v/>
@@ -10533,10 +10527,10 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q28" s="353"/>
-      <c r="R28" s="355"/>
-      <c r="S28" s="251"/>
-      <c r="T28" s="253"/>
+      <c r="Q28" s="368"/>
+      <c r="R28" s="370"/>
+      <c r="S28" s="250"/>
+      <c r="T28" s="252"/>
       <c r="U28" s="30"/>
       <c r="V28" s="95"/>
       <c r="W28" s="100"/>
@@ -10554,7 +10548,7 @@
       <c r="C29" s="167" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="383">
+      <c r="D29" s="388">
         <v>15</v>
       </c>
       <c r="E29" s="119"/>
@@ -10583,17 +10577,17 @@
         <v>15</v>
       </c>
       <c r="P29" s="122"/>
-      <c r="Q29" s="352">
+      <c r="Q29" s="367">
         <f>SUM(E29:P29)</f>
         <v>122</v>
       </c>
-      <c r="R29" s="354">
+      <c r="R29" s="369">
         <v>10</v>
       </c>
-      <c r="S29" s="250">
+      <c r="S29" s="249">
         <v>240</v>
       </c>
-      <c r="T29" s="252">
+      <c r="T29" s="251">
         <f>SUM(S29-Q29)</f>
         <v>118</v>
       </c>
@@ -10628,7 +10622,7 @@
       <c r="C30" s="164" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="384"/>
+      <c r="D30" s="389"/>
       <c r="E30" s="118" t="str">
         <f t="shared" ref="E30:P30" si="14">IF(E29=0, "", IF(MOD(E29, $D$29) = 0, E29/ $D$29, IF(INT(E29 / $D$29) = 0, MOD(E29, $D$29) &amp; " P", INT(E29 / $D$29) &amp; " + " &amp; MOD(E29, $D$29) &amp; " P")))</f>
         <v/>
@@ -10677,10 +10671,10 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q30" s="353"/>
-      <c r="R30" s="355"/>
-      <c r="S30" s="251"/>
-      <c r="T30" s="253"/>
+      <c r="Q30" s="368"/>
+      <c r="R30" s="370"/>
+      <c r="S30" s="250"/>
+      <c r="T30" s="252"/>
       <c r="U30" s="30"/>
       <c r="V30" s="95"/>
       <c r="W30" s="100"/>
@@ -10698,7 +10692,7 @@
       <c r="C31" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="383">
+      <c r="D31" s="388">
         <v>45</v>
       </c>
       <c r="E31" s="119"/>
@@ -10727,17 +10721,17 @@
         <v>1</v>
       </c>
       <c r="P31" s="122"/>
-      <c r="Q31" s="352">
+      <c r="Q31" s="367">
         <f>SUM(E31:P31)</f>
         <v>17</v>
       </c>
-      <c r="R31" s="358">
+      <c r="R31" s="377">
         <v>5</v>
       </c>
-      <c r="S31" s="250">
+      <c r="S31" s="249">
         <v>70</v>
       </c>
-      <c r="T31" s="252">
+      <c r="T31" s="251">
         <f>SUM(S31-Q31)</f>
         <v>53</v>
       </c>
@@ -10772,7 +10766,7 @@
       <c r="C32" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="384"/>
+      <c r="D32" s="389"/>
       <c r="E32" s="118" t="str">
         <f t="shared" ref="E32:P32" si="16">IF(E31=0, "", IF(MOD(E31, $D$31) = 0, E31/ $D$31, IF(INT(E31 / $D$31) = 0, MOD(E31, $D$31) &amp; " P", INT(E31 / $D$31) &amp; " + " &amp; MOD(E31, $D$31) &amp; " P")))</f>
         <v/>
@@ -10821,10 +10815,10 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q32" s="353"/>
-      <c r="R32" s="355"/>
-      <c r="S32" s="251"/>
-      <c r="T32" s="253"/>
+      <c r="Q32" s="368"/>
+      <c r="R32" s="370"/>
+      <c r="S32" s="250"/>
+      <c r="T32" s="252"/>
       <c r="U32" s="30"/>
       <c r="V32" s="95"/>
       <c r="W32" s="100"/>
@@ -10842,7 +10836,7 @@
       <c r="C33" s="167" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="383">
+      <c r="D33" s="388">
         <v>15</v>
       </c>
       <c r="E33" s="119"/>
@@ -10871,17 +10865,17 @@
         <v>19</v>
       </c>
       <c r="P33" s="122"/>
-      <c r="Q33" s="352">
+      <c r="Q33" s="367">
         <f>SUM(E33:P33)</f>
         <v>179</v>
       </c>
-      <c r="R33" s="358">
+      <c r="R33" s="377">
         <v>17</v>
       </c>
-      <c r="S33" s="250">
+      <c r="S33" s="249">
         <v>320</v>
       </c>
-      <c r="T33" s="252">
+      <c r="T33" s="251">
         <f t="shared" ref="T33" si="17">SUM(S33-Q33)</f>
         <v>141</v>
       </c>
@@ -10916,7 +10910,7 @@
       <c r="C34" s="165" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="384"/>
+      <c r="D34" s="389"/>
       <c r="E34" s="118" t="str">
         <f>IF(E33=0, "", IF(MOD(E33, $D$33) = 0, E33/ $D$33, IF(INT(E33 / $D$33) = 0, MOD(E33, $D$33) &amp; " P", INT(E33 / $D$33) &amp; " + " &amp; MOD(E33, $D$33) &amp; " P")))</f>
         <v/>
@@ -10965,10 +10959,10 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q34" s="353"/>
-      <c r="R34" s="355"/>
-      <c r="S34" s="251"/>
-      <c r="T34" s="253"/>
+      <c r="Q34" s="368"/>
+      <c r="R34" s="370"/>
+      <c r="S34" s="250"/>
+      <c r="T34" s="252"/>
       <c r="U34" s="30"/>
       <c r="V34" s="95"/>
       <c r="W34" s="100"/>
@@ -10986,7 +10980,7 @@
       <c r="C35" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="383">
+      <c r="D35" s="388">
         <v>15</v>
       </c>
       <c r="E35" s="140"/>
@@ -11015,17 +11009,17 @@
         <v>10</v>
       </c>
       <c r="P35" s="141"/>
-      <c r="Q35" s="352">
+      <c r="Q35" s="367">
         <f>SUM(E35:P35)</f>
         <v>141</v>
       </c>
-      <c r="R35" s="354">
+      <c r="R35" s="369">
         <v>11</v>
       </c>
-      <c r="S35" s="250">
+      <c r="S35" s="249">
         <v>190</v>
       </c>
-      <c r="T35" s="356">
+      <c r="T35" s="378">
         <f t="shared" ref="T35" si="19">SUM(S35-Q35)</f>
         <v>49</v>
       </c>
@@ -11060,7 +11054,7 @@
       <c r="C36" s="165" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="384"/>
+      <c r="D36" s="389"/>
       <c r="E36" s="118" t="str">
         <f>IF(E35=0, "", IF(MOD(E35, $D$35) = 0, E35/ $D$35, IF(INT(E35 / $D$35) = 0, MOD(E35, $D$35) &amp; " P", INT(E35 / $D$35) &amp; " + " &amp; MOD(E35, $D$35) &amp; " P")))</f>
         <v/>
@@ -11109,10 +11103,10 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q36" s="353"/>
-      <c r="R36" s="355"/>
-      <c r="S36" s="251"/>
-      <c r="T36" s="357"/>
+      <c r="Q36" s="368"/>
+      <c r="R36" s="370"/>
+      <c r="S36" s="250"/>
+      <c r="T36" s="379"/>
       <c r="U36" s="30"/>
       <c r="V36" s="95"/>
       <c r="W36" s="100"/>
@@ -11127,7 +11121,7 @@
       <c r="C37" s="167" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="383">
+      <c r="D37" s="388">
         <v>27</v>
       </c>
       <c r="E37" s="115"/>
@@ -11156,17 +11150,17 @@
         <v>35</v>
       </c>
       <c r="P37" s="115"/>
-      <c r="Q37" s="352">
+      <c r="Q37" s="367">
         <f>SUM(E37:P37)</f>
         <v>256</v>
       </c>
-      <c r="R37" s="354">
+      <c r="R37" s="369">
         <v>13</v>
       </c>
-      <c r="S37" s="250">
+      <c r="S37" s="249">
         <v>440</v>
       </c>
-      <c r="T37" s="356">
+      <c r="T37" s="378">
         <f t="shared" ref="T37" si="21">SUM(S37-Q37)</f>
         <v>184</v>
       </c>
@@ -11201,7 +11195,7 @@
       <c r="C38" s="165" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="384"/>
+      <c r="D38" s="389"/>
       <c r="E38" s="118" t="str">
         <f>IF(E37=0, "", IF(MOD(E37, $D$37) = 0, E37/ $D$37, IF(INT(E37 / $D$37) = 0, MOD(E37, $D$37) &amp; " P", INT(E37 / $D$37) &amp; " + " &amp; MOD(E37, $D$37) &amp; " P")))</f>
         <v/>
@@ -11250,10 +11244,10 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q38" s="353"/>
-      <c r="R38" s="355"/>
-      <c r="S38" s="251"/>
-      <c r="T38" s="357"/>
+      <c r="Q38" s="368"/>
+      <c r="R38" s="370"/>
+      <c r="S38" s="250"/>
+      <c r="T38" s="379"/>
       <c r="U38" s="30"/>
       <c r="V38" s="95"/>
       <c r="W38" s="100"/>
@@ -11268,7 +11262,7 @@
       <c r="C39" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="383">
+      <c r="D39" s="388">
         <v>20</v>
       </c>
       <c r="E39" s="115"/>
@@ -11297,17 +11291,17 @@
         <v>9</v>
       </c>
       <c r="P39" s="115"/>
-      <c r="Q39" s="352">
+      <c r="Q39" s="367">
         <f>SUM(E39:P39)</f>
         <v>243</v>
       </c>
-      <c r="R39" s="354">
+      <c r="R39" s="369">
         <v>15</v>
       </c>
-      <c r="S39" s="250">
+      <c r="S39" s="249">
         <v>450</v>
       </c>
-      <c r="T39" s="356">
+      <c r="T39" s="378">
         <f t="shared" ref="T39" si="23">SUM(S39-Q39)</f>
         <v>207</v>
       </c>
@@ -11342,7 +11336,7 @@
       <c r="C40" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="D40" s="384"/>
+      <c r="D40" s="389"/>
       <c r="E40" s="118" t="str">
         <f>IF(E39=0, "", IF(MOD(E39, $D$39) = 0, E39/ $D$39, IF(INT(E39 / $D$39) = 0, MOD(E39, $D$39) &amp; " P", INT(E39 / $D$39) &amp; " + " &amp; MOD(E39, $D$39) &amp; " P")))</f>
         <v/>
@@ -11391,10 +11385,10 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="Q40" s="353"/>
-      <c r="R40" s="355"/>
-      <c r="S40" s="251"/>
-      <c r="T40" s="357"/>
+      <c r="Q40" s="368"/>
+      <c r="R40" s="370"/>
+      <c r="S40" s="250"/>
+      <c r="T40" s="379"/>
       <c r="U40" s="30"/>
       <c r="V40" s="95"/>
       <c r="W40" s="100"/>
@@ -11409,7 +11403,7 @@
       <c r="C41" s="166" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="383">
+      <c r="D41" s="388">
         <v>32</v>
       </c>
       <c r="E41" s="115"/>
@@ -11438,17 +11432,17 @@
         <v>2</v>
       </c>
       <c r="P41" s="115"/>
-      <c r="Q41" s="352">
+      <c r="Q41" s="367">
         <f>SUM(E41:P41)</f>
         <v>97</v>
       </c>
-      <c r="R41" s="354">
+      <c r="R41" s="369">
         <v>7</v>
       </c>
-      <c r="S41" s="250">
+      <c r="S41" s="249">
         <v>220</v>
       </c>
-      <c r="T41" s="252">
+      <c r="T41" s="251">
         <f t="shared" ref="T41" si="25">SUM(S41-Q41)</f>
         <v>123</v>
       </c>
@@ -11483,7 +11477,7 @@
       <c r="C42" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="D42" s="384"/>
+      <c r="D42" s="389"/>
       <c r="E42" s="118" t="str">
         <f>IF(E41=0, "", IF(MOD(E41, $D$41) = 0, E41/ $D$41, IF(INT(E41 / $D$41) = 0, MOD(E41, $D$41) &amp; " P", INT(E41 / $D$41) &amp; " + " &amp; MOD(E41, $D$41) &amp; " P")))</f>
         <v/>
@@ -11532,10 +11526,10 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="Q42" s="353"/>
-      <c r="R42" s="355"/>
-      <c r="S42" s="251"/>
-      <c r="T42" s="253"/>
+      <c r="Q42" s="368"/>
+      <c r="R42" s="370"/>
+      <c r="S42" s="250"/>
+      <c r="T42" s="252"/>
       <c r="U42" s="30"/>
       <c r="V42" s="95"/>
       <c r="W42" s="100"/>
@@ -11550,7 +11544,7 @@
       <c r="C43" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="383">
+      <c r="D43" s="388">
         <v>15</v>
       </c>
       <c r="E43" s="115"/>
@@ -11579,17 +11573,17 @@
         <v>0</v>
       </c>
       <c r="P43" s="115"/>
-      <c r="Q43" s="352">
+      <c r="Q43" s="367">
         <f>SUM(E43:P43)</f>
         <v>52</v>
       </c>
-      <c r="R43" s="354">
+      <c r="R43" s="369">
         <v>6</v>
       </c>
-      <c r="S43" s="250">
+      <c r="S43" s="249">
         <v>100</v>
       </c>
-      <c r="T43" s="252">
+      <c r="T43" s="251">
         <f t="shared" ref="T43" si="27">SUM(S43-Q43)</f>
         <v>48</v>
       </c>
@@ -11624,7 +11618,7 @@
       <c r="C44" s="165" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="384"/>
+      <c r="D44" s="389"/>
       <c r="E44" s="118" t="str">
         <f>IF(E43=0, "", IF(MOD(E43, $D$43) = 0, E43/ $D$43, IF(INT(E43 / $D$43) = 0, MOD(E43, $D$43) &amp; " P", INT(E43 / $D$43) &amp; " + " &amp; MOD(E43, $D$43) &amp; " P")))</f>
         <v/>
@@ -11673,10 +11667,10 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="Q44" s="353"/>
-      <c r="R44" s="355"/>
-      <c r="S44" s="251"/>
-      <c r="T44" s="253"/>
+      <c r="Q44" s="368"/>
+      <c r="R44" s="370"/>
+      <c r="S44" s="250"/>
+      <c r="T44" s="252"/>
       <c r="U44" s="30"/>
       <c r="V44" s="95"/>
       <c r="W44" s="100"/>
@@ -11685,11 +11679,11 @@
       <c r="Z44" s="102"/>
     </row>
     <row r="45" spans="2:37" ht="73.5" customHeight="1" thickBot="1">
-      <c r="B45" s="274" t="s">
+      <c r="B45" s="340" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="275"/>
-      <c r="D45" s="276"/>
+      <c r="C45" s="341"/>
+      <c r="D45" s="342"/>
       <c r="E45" s="84"/>
       <c r="F45" s="84"/>
       <c r="G45" s="84"/>
@@ -11732,7 +11726,7 @@
       <c r="Y45" s="106"/>
       <c r="Z45" s="105"/>
     </row>
-    <row r="46" spans="2:37" ht="13.2" customHeight="1" thickBot="1">
+    <row r="46" spans="2:37" ht="13.15" customHeight="1" thickBot="1">
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -11760,92 +11754,92 @@
     <row r="47" spans="2:37" ht="105" hidden="1" customHeight="1" thickBot="1"/>
     <row r="48" spans="2:37" ht="37.5" hidden="1" customHeight="1" thickBot="1"/>
     <row r="49" spans="2:20" ht="48.75" hidden="1" customHeight="1" thickBot="1"/>
-    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.95" customHeight="1" thickBot="1">
-      <c r="B50" s="281" t="s">
+    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.900000000000006" customHeight="1" thickBot="1">
+      <c r="B50" s="324" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="282"/>
-      <c r="D50" s="281" t="s">
+      <c r="C50" s="325"/>
+      <c r="D50" s="324" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="282"/>
-      <c r="F50" s="281" t="s">
+      <c r="E50" s="325"/>
+      <c r="F50" s="324" t="s">
         <v>54</v>
       </c>
-      <c r="G50" s="282"/>
-      <c r="H50" s="281" t="s">
+      <c r="G50" s="325"/>
+      <c r="H50" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="282"/>
+      <c r="I50" s="325"/>
       <c r="J50" s="38"/>
-      <c r="M50" s="345" t="s">
+      <c r="M50" s="266" t="s">
         <v>88</v>
       </c>
-      <c r="N50" s="345"/>
-      <c r="O50" s="345"/>
-      <c r="P50" s="345"/>
-      <c r="Q50" s="348">
+      <c r="N50" s="266"/>
+      <c r="O50" s="266"/>
+      <c r="P50" s="266"/>
+      <c r="Q50" s="380">
         <f>SUM(R45)</f>
         <v>172</v>
       </c>
-      <c r="R50" s="340" t="s">
+      <c r="R50" s="255" t="s">
         <v>89</v>
       </c>
       <c r="T50" s="36"/>
     </row>
-    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1">
-      <c r="B51" s="283" t="s">
+    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1">
+      <c r="B51" s="326" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="284"/>
-      <c r="D51" s="285"/>
-      <c r="E51" s="286"/>
-      <c r="F51" s="285"/>
-      <c r="G51" s="286"/>
-      <c r="H51" s="285"/>
-      <c r="I51" s="286"/>
+      <c r="C51" s="327"/>
+      <c r="D51" s="328"/>
+      <c r="E51" s="329"/>
+      <c r="F51" s="328"/>
+      <c r="G51" s="329"/>
+      <c r="H51" s="328"/>
+      <c r="I51" s="329"/>
       <c r="J51" s="38"/>
-      <c r="M51" s="345"/>
-      <c r="N51" s="345"/>
-      <c r="O51" s="345"/>
-      <c r="P51" s="345"/>
-      <c r="Q51" s="349"/>
-      <c r="R51" s="340"/>
+      <c r="M51" s="266"/>
+      <c r="N51" s="266"/>
+      <c r="O51" s="266"/>
+      <c r="P51" s="266"/>
+      <c r="Q51" s="381"/>
+      <c r="R51" s="255"/>
       <c r="T51" s="36"/>
     </row>
-    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
-      <c r="B52" s="269" t="s">
+    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
+      <c r="B52" s="335" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="270"/>
-      <c r="D52" s="271"/>
-      <c r="E52" s="272"/>
-      <c r="F52" s="271"/>
-      <c r="G52" s="272"/>
-      <c r="H52" s="271"/>
-      <c r="I52" s="272"/>
+      <c r="C52" s="336"/>
+      <c r="D52" s="337"/>
+      <c r="E52" s="338"/>
+      <c r="F52" s="337"/>
+      <c r="G52" s="338"/>
+      <c r="H52" s="337"/>
+      <c r="I52" s="338"/>
       <c r="J52" s="38"/>
       <c r="M52" s="67"/>
-      <c r="N52" s="273" t="s">
+      <c r="N52" s="339" t="s">
         <v>73</v>
       </c>
-      <c r="O52" s="273"/>
-      <c r="P52" s="273"/>
-      <c r="Q52" s="273"/>
-      <c r="R52" s="273"/>
+      <c r="O52" s="339"/>
+      <c r="P52" s="339"/>
+      <c r="Q52" s="339"/>
+      <c r="R52" s="339"/>
       <c r="T52" s="36"/>
     </row>
-    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
-      <c r="B53" s="277" t="s">
+    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
+      <c r="B53" s="320" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="278"/>
-      <c r="D53" s="279"/>
-      <c r="E53" s="280"/>
-      <c r="F53" s="279"/>
-      <c r="G53" s="280"/>
-      <c r="H53" s="279"/>
-      <c r="I53" s="280"/>
+      <c r="C53" s="321"/>
+      <c r="D53" s="322"/>
+      <c r="E53" s="323"/>
+      <c r="F53" s="322"/>
+      <c r="G53" s="323"/>
+      <c r="H53" s="322"/>
+      <c r="I53" s="323"/>
       <c r="J53" s="38"/>
       <c r="K53" s="53" t="s">
         <v>77</v>
@@ -11865,7 +11859,7 @@
       <c r="R53" s="52"/>
       <c r="T53" s="36"/>
     </row>
-    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.2" customHeight="1" thickBot="1">
+    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.150000000000006" customHeight="1" thickBot="1">
       <c r="B54" s="38"/>
       <c r="C54" s="38"/>
       <c r="D54" s="89"/>
@@ -11887,6 +11881,106 @@
     </row>
   </sheetData>
   <mergeCells count="124">
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="N52:R52"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="M50:P51"/>
+    <mergeCell ref="Q50:Q51"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="E10:R11"/>
@@ -11911,106 +12005,6 @@
     <mergeCell ref="T12:T14"/>
     <mergeCell ref="V12:V13"/>
     <mergeCell ref="W12:W13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="T33:T34"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:S36"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="S43:S44"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="N52:R52"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="M50:P51"/>
-    <mergeCell ref="Q50:Q51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0"/>
@@ -12022,49 +12016,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AW50"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="51.69921875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.59765625" style="3" customWidth="1"/>
-    <col min="4" max="12" width="6.69921875" style="3" customWidth="1"/>
-    <col min="13" max="14" width="6.69921875" style="30" customWidth="1"/>
-    <col min="15" max="15" width="10.19921875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="17.19921875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="14.19921875" style="3" customWidth="1"/>
-    <col min="18" max="18" width="10.69921875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="15.69921875" style="3" customWidth="1"/>
-    <col min="20" max="49" width="3.69921875" style="3" hidden="1" customWidth="1"/>
-    <col min="50" max="16384" width="8.8984375" style="3"/>
+    <col min="1" max="1" width="51.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="3" customWidth="1"/>
+    <col min="4" max="12" width="6.75" style="3" customWidth="1"/>
+    <col min="13" max="14" width="6.75" style="30" customWidth="1"/>
+    <col min="15" max="15" width="10.25" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.25" style="3" customWidth="1"/>
+    <col min="17" max="17" width="14.25" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.75" style="3" customWidth="1"/>
+    <col min="19" max="19" width="15.75" style="3" customWidth="1"/>
+    <col min="20" max="49" width="3.75" style="3" hidden="1" customWidth="1"/>
+    <col min="50" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="49.95" customHeight="1">
+    <row r="1" spans="1:49" ht="49.9" customHeight="1">
       <c r="A1" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="412" t="s">
+      <c r="B1" s="390" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="407"/>
-      <c r="D1" s="407"/>
-      <c r="E1" s="407"/>
-      <c r="F1" s="407"/>
-      <c r="G1" s="407"/>
-      <c r="H1" s="407"/>
-      <c r="I1" s="407"/>
-      <c r="J1" s="407"/>
-      <c r="K1" s="407"/>
-      <c r="L1" s="407"/>
-      <c r="M1" s="407"/>
-      <c r="N1" s="407"/>
-      <c r="O1" s="407"/>
-      <c r="Q1" s="413" t="s">
+      <c r="C1" s="391"/>
+      <c r="D1" s="391"/>
+      <c r="E1" s="391"/>
+      <c r="F1" s="391"/>
+      <c r="G1" s="391"/>
+      <c r="H1" s="391"/>
+      <c r="I1" s="391"/>
+      <c r="J1" s="391"/>
+      <c r="K1" s="391"/>
+      <c r="L1" s="391"/>
+      <c r="M1" s="391"/>
+      <c r="N1" s="391"/>
+      <c r="O1" s="391"/>
+      <c r="Q1" s="392" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="413"/>
-      <c r="S1" s="413"/>
-    </row>
-    <row r="2" spans="1:49" ht="10.199999999999999" customHeight="1">
+      <c r="R1" s="392"/>
+      <c r="S1" s="392"/>
+    </row>
+    <row r="2" spans="1:49" ht="10.15" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -12088,23 +12082,23 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="12"/>
-      <c r="Q3" s="413" t="s">
+      <c r="Q3" s="392" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="413"/>
-      <c r="S3" s="413"/>
-    </row>
-    <row r="4" spans="1:49" ht="25.2" customHeight="1">
+      <c r="R3" s="392"/>
+      <c r="S3" s="392"/>
+    </row>
+    <row r="4" spans="1:49" ht="25.15" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="Q4" s="413"/>
-      <c r="R4" s="413"/>
-      <c r="S4" s="413"/>
-    </row>
-    <row r="5" spans="1:49" ht="4.95" customHeight="1">
+      <c r="Q4" s="392"/>
+      <c r="R4" s="392"/>
+      <c r="S4" s="392"/>
+    </row>
+    <row r="5" spans="1:49" ht="4.9000000000000004" customHeight="1">
       <c r="A5" s="5"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -12112,177 +12106,177 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
     </row>
-    <row r="6" spans="1:49" ht="25.2" customHeight="1">
-      <c r="A6" s="414" t="s">
+    <row r="6" spans="1:49" ht="25.15" customHeight="1">
+      <c r="A6" s="393" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="414"/>
-      <c r="C6" s="415" t="s">
+      <c r="B6" s="393"/>
+      <c r="C6" s="394" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="415"/>
-      <c r="E6" s="415"/>
-      <c r="F6" s="415"/>
-      <c r="G6" s="415"/>
-      <c r="H6" s="415"/>
-      <c r="I6" s="415"/>
-      <c r="J6" s="415"/>
-      <c r="K6" s="415"/>
-      <c r="L6" s="415"/>
-      <c r="M6" s="415"/>
-      <c r="N6" s="415"/>
-      <c r="O6" s="415"/>
-      <c r="P6" s="415"/>
-      <c r="Q6" s="415"/>
-      <c r="R6" s="415"/>
-      <c r="S6" s="415"/>
-    </row>
-    <row r="7" spans="1:49" ht="19.95" customHeight="1">
-      <c r="A7" s="414"/>
-      <c r="B7" s="414"/>
-      <c r="C7" s="410" t="s">
+      <c r="D6" s="394"/>
+      <c r="E6" s="394"/>
+      <c r="F6" s="394"/>
+      <c r="G6" s="394"/>
+      <c r="H6" s="394"/>
+      <c r="I6" s="394"/>
+      <c r="J6" s="394"/>
+      <c r="K6" s="394"/>
+      <c r="L6" s="394"/>
+      <c r="M6" s="394"/>
+      <c r="N6" s="394"/>
+      <c r="O6" s="394"/>
+      <c r="P6" s="394"/>
+      <c r="Q6" s="394"/>
+      <c r="R6" s="394"/>
+      <c r="S6" s="394"/>
+    </row>
+    <row r="7" spans="1:49" ht="19.899999999999999" customHeight="1">
+      <c r="A7" s="393"/>
+      <c r="B7" s="393"/>
+      <c r="C7" s="399" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="391" t="s">
+      <c r="D7" s="401" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="392"/>
-      <c r="F7" s="392"/>
-      <c r="G7" s="392"/>
-      <c r="H7" s="392"/>
-      <c r="I7" s="392"/>
-      <c r="J7" s="392"/>
-      <c r="K7" s="392"/>
-      <c r="L7" s="392"/>
-      <c r="M7" s="392"/>
-      <c r="N7" s="392"/>
-      <c r="O7" s="392"/>
-      <c r="P7" s="392"/>
-      <c r="Q7" s="392"/>
-      <c r="R7" s="392"/>
-      <c r="S7" s="393"/>
+      <c r="E7" s="402"/>
+      <c r="F7" s="402"/>
+      <c r="G7" s="402"/>
+      <c r="H7" s="402"/>
+      <c r="I7" s="402"/>
+      <c r="J7" s="402"/>
+      <c r="K7" s="402"/>
+      <c r="L7" s="402"/>
+      <c r="M7" s="402"/>
+      <c r="N7" s="402"/>
+      <c r="O7" s="402"/>
+      <c r="P7" s="402"/>
+      <c r="Q7" s="402"/>
+      <c r="R7" s="402"/>
+      <c r="S7" s="403"/>
     </row>
     <row r="8" spans="1:49" ht="15" customHeight="1">
-      <c r="A8" s="414"/>
-      <c r="B8" s="414"/>
-      <c r="C8" s="411"/>
-      <c r="D8" s="396" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="396" t="s">
+      <c r="A8" s="393"/>
+      <c r="B8" s="393"/>
+      <c r="C8" s="400"/>
+      <c r="D8" s="395" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="395" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="396" t="s">
+      <c r="F8" s="395" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="396" t="s">
+      <c r="G8" s="395" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="396" t="s">
+      <c r="H8" s="395" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="396" t="s">
+      <c r="I8" s="395" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="396" t="s">
+      <c r="J8" s="395" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="396" t="s">
+      <c r="K8" s="395" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="396" t="s">
+      <c r="L8" s="395" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="396" t="s">
+      <c r="M8" s="395" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="396" t="s">
+      <c r="N8" s="395" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="396" t="s">
+      <c r="O8" s="395" t="s">
         <v>92</v>
       </c>
       <c r="P8" s="13"/>
-      <c r="Q8" s="396" t="s">
+      <c r="Q8" s="395" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="396" t="s">
+      <c r="R8" s="395" t="s">
         <v>36</v>
       </c>
-      <c r="S8" s="396" t="s">
+      <c r="S8" s="395" t="s">
         <v>37</v>
       </c>
-      <c r="T8" s="407" t="s">
+      <c r="T8" s="391" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="407"/>
-      <c r="V8" s="407"/>
-      <c r="W8" s="407" t="s">
+      <c r="U8" s="391"/>
+      <c r="V8" s="391"/>
+      <c r="W8" s="391" t="s">
         <v>5</v>
       </c>
-      <c r="X8" s="407"/>
-      <c r="Y8" s="407"/>
-      <c r="Z8" s="407" t="s">
+      <c r="X8" s="391"/>
+      <c r="Y8" s="391"/>
+      <c r="Z8" s="391" t="s">
         <v>7</v>
       </c>
-      <c r="AA8" s="407"/>
-      <c r="AB8" s="407"/>
-      <c r="AC8" s="407" t="s">
+      <c r="AA8" s="391"/>
+      <c r="AB8" s="391"/>
+      <c r="AC8" s="391" t="s">
         <v>8</v>
       </c>
-      <c r="AD8" s="407"/>
-      <c r="AE8" s="407"/>
-      <c r="AF8" s="407" t="s">
+      <c r="AD8" s="391"/>
+      <c r="AE8" s="391"/>
+      <c r="AF8" s="391" t="s">
         <v>9</v>
       </c>
-      <c r="AG8" s="407"/>
-      <c r="AH8" s="407"/>
-      <c r="AI8" s="407" t="s">
+      <c r="AG8" s="391"/>
+      <c r="AH8" s="391"/>
+      <c r="AI8" s="391" t="s">
         <v>10</v>
       </c>
-      <c r="AJ8" s="407"/>
-      <c r="AK8" s="407"/>
-      <c r="AL8" s="407" t="s">
+      <c r="AJ8" s="391"/>
+      <c r="AK8" s="391"/>
+      <c r="AL8" s="391" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="407"/>
-      <c r="AN8" s="407"/>
-      <c r="AO8" s="407" t="s">
+      <c r="AM8" s="391"/>
+      <c r="AN8" s="391"/>
+      <c r="AO8" s="391" t="s">
         <v>12</v>
       </c>
-      <c r="AP8" s="407"/>
-      <c r="AQ8" s="407"/>
-      <c r="AR8" s="407" t="s">
+      <c r="AP8" s="391"/>
+      <c r="AQ8" s="391"/>
+      <c r="AR8" s="391" t="s">
         <v>13</v>
       </c>
-      <c r="AS8" s="407"/>
-      <c r="AT8" s="407"/>
-      <c r="AU8" s="407" t="s">
+      <c r="AS8" s="391"/>
+      <c r="AT8" s="391"/>
+      <c r="AU8" s="391" t="s">
         <v>14</v>
       </c>
-      <c r="AV8" s="407"/>
-      <c r="AW8" s="407"/>
-    </row>
-    <row r="9" spans="1:49" ht="25.2" customHeight="1">
+      <c r="AV8" s="391"/>
+      <c r="AW8" s="391"/>
+    </row>
+    <row r="9" spans="1:49" ht="25.15" customHeight="1">
       <c r="A9" s="57" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="411"/>
-      <c r="D9" s="398"/>
-      <c r="E9" s="398"/>
-      <c r="F9" s="398"/>
-      <c r="G9" s="398"/>
-      <c r="H9" s="398"/>
-      <c r="I9" s="398"/>
-      <c r="J9" s="398"/>
-      <c r="K9" s="398"/>
-      <c r="L9" s="398"/>
-      <c r="M9" s="398"/>
-      <c r="N9" s="398"/>
-      <c r="O9" s="398"/>
+      <c r="C9" s="400"/>
+      <c r="D9" s="396"/>
+      <c r="E9" s="396"/>
+      <c r="F9" s="396"/>
+      <c r="G9" s="396"/>
+      <c r="H9" s="396"/>
+      <c r="I9" s="396"/>
+      <c r="J9" s="396"/>
+      <c r="K9" s="396"/>
+      <c r="L9" s="396"/>
+      <c r="M9" s="396"/>
+      <c r="N9" s="396"/>
+      <c r="O9" s="396"/>
       <c r="P9" s="13" t="s">
         <v>3</v>
       </c>
@@ -12380,7 +12374,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="22.95" customHeight="1">
+    <row r="10" spans="1:49" ht="22.9" customHeight="1">
       <c r="A10" s="176" t="str">
         <f>'[1]บางบัวทอง-ผลิต'!C12</f>
         <v>องุ่นดำไร้เมล็ด 150 กรัม x36P</v>
@@ -12568,7 +12562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="22.95" customHeight="1">
+    <row r="11" spans="1:49" ht="22.9" customHeight="1">
       <c r="A11" s="176" t="str">
         <f>'[1]บางบัวทอง-ผลิต'!C14</f>
         <v>องุ่นแดงนอกมีเมล็ด 200 กรัม x 32 P</v>
@@ -12756,7 +12750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="22.95" customHeight="1">
+    <row r="12" spans="1:49" ht="22.9" customHeight="1">
       <c r="A12" s="179" t="s">
         <v>126</v>
       </c>
@@ -12943,7 +12937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="22.95" customHeight="1">
+    <row r="13" spans="1:49" ht="22.9" customHeight="1">
       <c r="A13" s="179" t="s">
         <v>142</v>
       </c>
@@ -13130,7 +13124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="22.95" customHeight="1">
+    <row r="14" spans="1:49" ht="22.9" customHeight="1">
       <c r="A14" s="179" t="s">
         <v>141</v>
       </c>
@@ -13224,7 +13218,7 @@
       <c r="AV14" s="9"/>
       <c r="AW14" s="10"/>
     </row>
-    <row r="15" spans="1:49" ht="22.95" customHeight="1">
+    <row r="15" spans="1:49" ht="22.9" customHeight="1">
       <c r="A15" s="179" t="s">
         <v>62</v>
       </c>
@@ -13411,7 +13405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="22.95" customHeight="1">
+    <row r="16" spans="1:49" ht="22.9" customHeight="1">
       <c r="A16" s="180" t="s">
         <v>140</v>
       </c>
@@ -13505,7 +13499,7 @@
       <c r="AV16" s="9"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="17" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A17" s="181" t="s">
         <v>63</v>
       </c>
@@ -13599,7 +13593,7 @@
       <c r="AV17" s="32"/>
       <c r="AW17" s="33"/>
     </row>
-    <row r="18" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="18" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A18" s="179" t="s">
         <v>104</v>
       </c>
@@ -13693,7 +13687,7 @@
       <c r="AV18" s="32"/>
       <c r="AW18" s="33"/>
     </row>
-    <row r="19" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="19" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A19" s="181" t="s">
         <v>129</v>
       </c>
@@ -13787,7 +13781,7 @@
       <c r="AV19" s="32"/>
       <c r="AW19" s="33"/>
     </row>
-    <row r="20" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="20" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A20" s="181" t="s">
         <v>64</v>
       </c>
@@ -13881,7 +13875,7 @@
       <c r="AV20" s="32"/>
       <c r="AW20" s="33"/>
     </row>
-    <row r="21" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="21" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A21" s="181" t="s">
         <v>133</v>
       </c>
@@ -13975,7 +13969,7 @@
       <c r="AV21" s="32"/>
       <c r="AW21" s="33"/>
     </row>
-    <row r="22" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="22" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A22" s="181" t="s">
         <v>109</v>
       </c>
@@ -14069,7 +14063,7 @@
       <c r="AV22" s="32"/>
       <c r="AW22" s="33"/>
     </row>
-    <row r="23" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="23" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A23" s="181" t="s">
         <v>131</v>
       </c>
@@ -14163,7 +14157,7 @@
       <c r="AV23" s="32"/>
       <c r="AW23" s="33"/>
     </row>
-    <row r="24" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="24" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A24" s="181" t="s">
         <v>65</v>
       </c>
@@ -14257,7 +14251,7 @@
       <c r="AV24" s="32"/>
       <c r="AW24" s="33"/>
     </row>
-    <row r="25" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="25" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A25" s="180" t="s">
         <v>66</v>
       </c>
@@ -14351,7 +14345,7 @@
       <c r="AV25" s="32"/>
       <c r="AW25" s="33"/>
     </row>
-    <row r="26" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="26" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A26" s="179" t="s">
         <v>105</v>
       </c>
@@ -14445,7 +14439,7 @@
       <c r="AV26" s="32"/>
       <c r="AW26" s="33"/>
     </row>
-    <row r="27" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
+    <row r="27" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="A27" s="179" t="s">
         <v>105</v>
       </c>
@@ -14539,11 +14533,11 @@
       <c r="AV27" s="32"/>
       <c r="AW27" s="33"/>
     </row>
-    <row r="28" spans="1:49" s="25" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A28" s="408" t="s">
+    <row r="28" spans="1:49" s="25" customFormat="1" ht="25.15" customHeight="1">
+      <c r="A28" s="404" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="408"/>
+      <c r="B28" s="404"/>
       <c r="C28" s="109">
         <f>SUM(C10:C27)</f>
         <v>0</v>
@@ -14602,11 +14596,11 @@
       <c r="S28" s="24"/>
     </row>
     <row r="29" spans="1:49" ht="21" customHeight="1">
-      <c r="A29" s="409" t="s">
+      <c r="A29" s="398" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="409"/>
-      <c r="C29" s="409"/>
+      <c r="B29" s="398"/>
+      <c r="C29" s="398"/>
       <c r="D29" s="108">
         <f>SUM(T10:T16)</f>
         <v>0</v>
@@ -14789,7 +14783,7 @@
       <c r="C33" s="11"/>
     </row>
     <row r="34" spans="1:19" ht="18" customHeight="1">
-      <c r="A34" s="404" t="s">
+      <c r="A34" s="406" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="15" t="s">
@@ -14807,7 +14801,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="18" customHeight="1">
-      <c r="A35" s="404"/>
+      <c r="A35" s="406"/>
       <c r="B35" s="15" t="s">
         <v>46</v>
       </c>
@@ -14824,7 +14818,7 @@
       <c r="I35" s="16"/>
     </row>
     <row r="36" spans="1:19" ht="18" customHeight="1">
-      <c r="A36" s="404"/>
+      <c r="A36" s="406"/>
       <c r="B36" s="405" t="s">
         <v>48</v>
       </c>
@@ -14838,7 +14832,7 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="18" customHeight="1">
-      <c r="A37" s="404"/>
+      <c r="A37" s="406"/>
       <c r="B37" s="405" t="s">
         <v>47</v>
       </c>
@@ -14851,7 +14845,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="18" customHeight="1">
-      <c r="A38" s="404"/>
+      <c r="A38" s="406"/>
       <c r="B38" s="405" t="s">
         <v>19</v>
       </c>
@@ -14865,7 +14859,7 @@
       </c>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1">
-      <c r="A39" s="404" t="s">
+      <c r="A39" s="406" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -14883,7 +14877,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="18" customHeight="1">
-      <c r="A40" s="404"/>
+      <c r="A40" s="406"/>
       <c r="B40" s="15" t="s">
         <v>46</v>
       </c>
@@ -14899,7 +14893,7 @@
       </c>
     </row>
     <row r="41" spans="1:19" ht="18" customHeight="1">
-      <c r="A41" s="404"/>
+      <c r="A41" s="406"/>
       <c r="B41" s="405" t="s">
         <v>48</v>
       </c>
@@ -14913,7 +14907,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1">
-      <c r="A42" s="404"/>
+      <c r="A42" s="406"/>
       <c r="B42" s="405" t="s">
         <v>47</v>
       </c>
@@ -14925,8 +14919,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="25.2" customHeight="1">
-      <c r="A43" s="404"/>
+    <row r="43" spans="1:19" ht="25.15" customHeight="1">
+      <c r="A43" s="406"/>
       <c r="B43" s="405" t="s">
         <v>19</v>
       </c>
@@ -14939,68 +14933,68 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="25.2" customHeight="1">
+    <row r="44" spans="1:19" ht="25.15" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:19" ht="4.95" customHeight="1">
+    <row r="45" spans="1:19" ht="4.9000000000000004" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="E45" s="12"/>
     </row>
     <row r="46" spans="1:19" ht="21" customHeight="1">
-      <c r="A46" s="404" t="s">
+      <c r="A46" s="406" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="406"/>
+      <c r="B46" s="412"/>
       <c r="C46" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="404" t="s">
+      <c r="D46" s="406" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="404"/>
-      <c r="F46" s="404"/>
-      <c r="G46" s="404" t="s">
+      <c r="E46" s="406"/>
+      <c r="F46" s="406"/>
+      <c r="G46" s="406" t="s">
         <v>54</v>
       </c>
-      <c r="H46" s="404"/>
-      <c r="I46" s="404"/>
-      <c r="J46" s="391" t="s">
+      <c r="H46" s="406"/>
+      <c r="I46" s="406"/>
+      <c r="J46" s="401" t="s">
         <v>55</v>
       </c>
-      <c r="K46" s="392"/>
-      <c r="L46" s="392"/>
-      <c r="M46" s="392"/>
-      <c r="N46" s="392"/>
-      <c r="O46" s="393"/>
+      <c r="K46" s="402"/>
+      <c r="L46" s="402"/>
+      <c r="M46" s="402"/>
+      <c r="N46" s="402"/>
+      <c r="O46" s="403"/>
       <c r="P46" s="17"/>
-      <c r="Q46" s="394" t="s">
+      <c r="Q46" s="413" t="s">
         <v>60</v>
       </c>
-      <c r="R46" s="395"/>
+      <c r="R46" s="414"/>
     </row>
     <row r="47" spans="1:19" ht="21" customHeight="1">
-      <c r="A47" s="399" t="s">
+      <c r="A47" s="407" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="400"/>
+      <c r="B47" s="408"/>
       <c r="C47" s="14"/>
-      <c r="D47" s="391"/>
-      <c r="E47" s="392"/>
-      <c r="F47" s="393"/>
-      <c r="G47" s="391"/>
-      <c r="H47" s="392"/>
-      <c r="I47" s="393"/>
-      <c r="J47" s="401"/>
-      <c r="K47" s="402"/>
-      <c r="L47" s="402"/>
-      <c r="M47" s="402"/>
-      <c r="N47" s="402"/>
-      <c r="O47" s="403"/>
+      <c r="D47" s="401"/>
+      <c r="E47" s="402"/>
+      <c r="F47" s="403"/>
+      <c r="G47" s="401"/>
+      <c r="H47" s="402"/>
+      <c r="I47" s="403"/>
+      <c r="J47" s="409"/>
+      <c r="K47" s="410"/>
+      <c r="L47" s="410"/>
+      <c r="M47" s="410"/>
+      <c r="N47" s="410"/>
+      <c r="O47" s="411"/>
       <c r="P47" s="18"/>
       <c r="Q47" s="22" t="s">
         <v>56</v>
@@ -15011,23 +15005,23 @@
       <c r="S47" s="5"/>
     </row>
     <row r="48" spans="1:19" ht="21" customHeight="1">
-      <c r="A48" s="399" t="s">
+      <c r="A48" s="407" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="400"/>
+      <c r="B48" s="408"/>
       <c r="C48" s="14"/>
-      <c r="D48" s="391"/>
-      <c r="E48" s="392"/>
-      <c r="F48" s="393"/>
-      <c r="G48" s="391"/>
-      <c r="H48" s="392"/>
-      <c r="I48" s="393"/>
-      <c r="J48" s="401"/>
-      <c r="K48" s="402"/>
-      <c r="L48" s="402"/>
-      <c r="M48" s="402"/>
-      <c r="N48" s="402"/>
-      <c r="O48" s="403"/>
+      <c r="D48" s="401"/>
+      <c r="E48" s="402"/>
+      <c r="F48" s="403"/>
+      <c r="G48" s="401"/>
+      <c r="H48" s="402"/>
+      <c r="I48" s="403"/>
+      <c r="J48" s="409"/>
+      <c r="K48" s="410"/>
+      <c r="L48" s="410"/>
+      <c r="M48" s="410"/>
+      <c r="N48" s="410"/>
+      <c r="O48" s="411"/>
       <c r="P48" s="18"/>
       <c r="Q48" s="22" t="s">
         <v>58</v>
@@ -15038,23 +15032,23 @@
       <c r="S48" s="19"/>
     </row>
     <row r="49" spans="1:19" ht="21" customHeight="1">
-      <c r="A49" s="399" t="s">
+      <c r="A49" s="407" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="399"/>
+      <c r="B49" s="407"/>
       <c r="C49" s="14"/>
-      <c r="D49" s="391"/>
-      <c r="E49" s="392"/>
-      <c r="F49" s="393"/>
-      <c r="G49" s="391"/>
-      <c r="H49" s="392"/>
-      <c r="I49" s="393"/>
-      <c r="J49" s="401"/>
-      <c r="K49" s="402"/>
-      <c r="L49" s="402"/>
-      <c r="M49" s="402"/>
-      <c r="N49" s="402"/>
-      <c r="O49" s="403"/>
+      <c r="D49" s="401"/>
+      <c r="E49" s="402"/>
+      <c r="F49" s="403"/>
+      <c r="G49" s="401"/>
+      <c r="H49" s="402"/>
+      <c r="I49" s="403"/>
+      <c r="J49" s="409"/>
+      <c r="K49" s="410"/>
+      <c r="L49" s="410"/>
+      <c r="M49" s="410"/>
+      <c r="N49" s="410"/>
+      <c r="O49" s="411"/>
       <c r="P49" s="18"/>
       <c r="Q49" s="20" t="s">
         <v>59</v>
@@ -15071,19 +15065,38 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q3:S4"/>
-    <mergeCell ref="A6:B8"/>
-    <mergeCell ref="C6:S6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D7:S7"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="J46:O46"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="J49:O49"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="J47:O47"/>
+    <mergeCell ref="J48:O48"/>
+    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="AL8:AN8"/>
     <mergeCell ref="AO8:AQ8"/>
     <mergeCell ref="AR8:AT8"/>
@@ -15100,38 +15113,19 @@
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="J49:O49"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="J47:O47"/>
-    <mergeCell ref="J48:O48"/>
-    <mergeCell ref="G46:I46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="Q46:R46"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="J46:O46"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D7:S7"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q3:S4"/>
+    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="S8:S9"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15142,15 +15136,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D82F59-BE09-4F9C-81D2-26BAD193372A}">
   <dimension ref="D11:F17"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="33.69921875" customWidth="1"/>
+    <col min="5" max="5" width="33.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="4:6" ht="14.4" thickBot="1"/>
+    <row r="11" spans="4:6" ht="15" thickBot="1"/>
     <row r="12" spans="4:6" s="71" customFormat="1">
-      <c r="D12" s="416" t="s">
+      <c r="D12" s="415" t="s">
         <v>119</v>
       </c>
       <c r="E12" s="72" t="s">
@@ -15159,20 +15153,20 @@
       <c r="F12" s="73"/>
     </row>
     <row r="13" spans="4:6" s="71" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="D13" s="417"/>
+      <c r="D13" s="416"/>
       <c r="E13" s="74" t="s">
         <v>125</v>
       </c>
       <c r="F13" s="73"/>
     </row>
-    <row r="14" spans="4:6" s="71" customFormat="1" ht="14.4" thickBot="1">
-      <c r="D14" s="418"/>
+    <row r="14" spans="4:6" s="71" customFormat="1" ht="15" thickBot="1">
+      <c r="D14" s="417"/>
       <c r="E14" s="75" t="s">
         <v>121</v>
       </c>
       <c r="F14" s="73"/>
     </row>
-    <row r="15" spans="4:6" s="71" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
+    <row r="15" spans="4:6" s="71" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
       <c r="D15" s="76" t="s">
         <v>122</v>
       </c>
@@ -15181,7 +15175,7 @@
       </c>
       <c r="F15" s="73"/>
     </row>
-    <row r="16" spans="4:6" s="71" customFormat="1" ht="14.4" thickBot="1">
+    <row r="16" spans="4:6" s="71" customFormat="1" ht="15" thickBot="1">
       <c r="D16" s="76" t="s">
         <v>124</v>
       </c>
@@ -15190,7 +15184,7 @@
       </c>
       <c r="F16" s="73"/>
     </row>
-    <row r="17" spans="4:6" ht="23.4">
+    <row r="17" spans="4:6" ht="23.25">
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
       <c r="F17" s="30"/>

--- a/customers/cpall/excel_templates/logistic_plan_รอบเช้าต่างจังหวัด.xlsx
+++ b/customers/cpall/excel_templates/logistic_plan_รอบเช้าต่างจังหวัด.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User7\Desktop\PRD-Plan\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C2B910-0C0E-44BB-97D5-787E99529B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE11151-F012-43CF-B5CC-B4CF4BB18762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="582" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="582" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="บางบัวทอง-ผลิต" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'บางบัวทอง-ผลิต (2)'!$B$10:$R$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'บางบัวทอง-ผลิต (4)'!$B$10:$R$54</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
@@ -51,7 +54,7 @@
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2636,6 +2639,9 @@
     <xf numFmtId="3" fontId="91" fillId="2" borderId="31" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="52" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2648,19 +2654,106 @@
     <xf numFmtId="3" fontId="53" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="89" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="85" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="85" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="86" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="86" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2669,37 +2762,67 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="85" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="85" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="86" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="86" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="86" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="7" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="81" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2783,151 +2906,91 @@
     <xf numFmtId="0" fontId="66" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="7" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="6" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="6" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="89" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="86" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="63" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="68" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="68" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="53" fillId="12" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="53" fillId="12" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2978,61 +3041,16 @@
     <xf numFmtId="0" fontId="35" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="68" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="68" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="53" fillId="12" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="53" fillId="12" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="63" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3047,25 +3065,73 @@
     <xf numFmtId="0" fontId="72" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3074,66 +3140,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="44" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3141,9 +3147,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="4" borderId="24" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3237,6 +3240,9 @@
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_ClassificationId">
@@ -3589,34 +3595,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:AK57"/>
-  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="5.69921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.75" style="30" customWidth="1"/>
+    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
     <col min="2" max="2" width="18" style="3" customWidth="1"/>
-    <col min="3" max="3" width="134.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="23.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.375" style="3" customWidth="1"/>
-    <col min="6" max="10" width="35.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="28.625" style="3" customWidth="1"/>
-    <col min="12" max="14" width="35.125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="35.125" style="29" customWidth="1"/>
-    <col min="16" max="16" width="29.75" style="29" customWidth="1"/>
-    <col min="17" max="17" width="34.25" style="29" customWidth="1"/>
-    <col min="18" max="18" width="34.25" style="36" customWidth="1"/>
+    <col min="3" max="3" width="134.19921875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="23.19921875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.3984375" style="3" customWidth="1"/>
+    <col min="6" max="10" width="35.09765625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="28.59765625" style="3" customWidth="1"/>
+    <col min="12" max="14" width="35.09765625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="35.09765625" style="29" customWidth="1"/>
+    <col min="16" max="16" width="29.69921875" style="29" customWidth="1"/>
+    <col min="17" max="17" width="34.19921875" style="29" customWidth="1"/>
+    <col min="18" max="18" width="34.19921875" style="36" customWidth="1"/>
     <col min="19" max="19" width="26" style="29" customWidth="1"/>
-    <col min="20" max="20" width="25.25" style="127" customWidth="1"/>
-    <col min="21" max="21" width="8.375" style="67" customWidth="1"/>
-    <col min="22" max="22" width="27.875" style="206" customWidth="1"/>
-    <col min="23" max="23" width="24.875" style="206" customWidth="1"/>
-    <col min="24" max="24" width="27.875" style="206" customWidth="1"/>
+    <col min="20" max="20" width="25.19921875" style="127" customWidth="1"/>
+    <col min="21" max="21" width="8.3984375" style="67" customWidth="1"/>
+    <col min="22" max="22" width="27.8984375" style="206" customWidth="1"/>
+    <col min="23" max="23" width="24.8984375" style="206" customWidth="1"/>
+    <col min="24" max="24" width="27.8984375" style="206" customWidth="1"/>
     <col min="25" max="25" width="22" style="206" customWidth="1"/>
-    <col min="26" max="26" width="27.875" style="206" customWidth="1"/>
-    <col min="27" max="36" width="5.75" style="3"/>
-    <col min="37" max="37" width="13.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="5.75" style="3"/>
+    <col min="26" max="26" width="27.8984375" style="206" customWidth="1"/>
+    <col min="27" max="36" width="5.69921875" style="3"/>
+    <col min="37" max="37" width="13.69921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="5.69921875" style="3"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:37" s="30" customFormat="1" ht="31.9" customHeight="1">
+    <row r="4" spans="2:37" s="30" customFormat="1" ht="31.95" customHeight="1">
       <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -3627,8 +3633,8 @@
       <c r="I4" s="37"/>
       <c r="J4" s="28"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="298"/>
-      <c r="M4" s="298"/>
+      <c r="L4" s="287"/>
+      <c r="M4" s="287"/>
       <c r="N4" s="54"/>
       <c r="O4" s="55"/>
       <c r="P4" s="55"/>
@@ -3724,39 +3730,39 @@
       <c r="O8" s="36"/>
     </row>
     <row r="9" spans="2:37" ht="15" customHeight="1">
-      <c r="E9" s="313" t="s">
+      <c r="E9" s="304" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="313"/>
-      <c r="G9" s="313"/>
-      <c r="H9" s="313"/>
-      <c r="I9" s="313"/>
-      <c r="J9" s="313"/>
-      <c r="K9" s="313"/>
-      <c r="L9" s="313"/>
-      <c r="M9" s="313"/>
-      <c r="N9" s="313"/>
-      <c r="O9" s="313"/>
-      <c r="P9" s="313"/>
-    </row>
-    <row r="10" spans="2:37" s="30" customFormat="1" ht="71.45" customHeight="1" thickBot="1">
-      <c r="B10" s="301" t="s">
+      <c r="F9" s="304"/>
+      <c r="G9" s="304"/>
+      <c r="H9" s="304"/>
+      <c r="I9" s="304"/>
+      <c r="J9" s="304"/>
+      <c r="K9" s="304"/>
+      <c r="L9" s="304"/>
+      <c r="M9" s="304"/>
+      <c r="N9" s="304"/>
+      <c r="O9" s="304"/>
+      <c r="P9" s="304"/>
+    </row>
+    <row r="10" spans="2:37" s="30" customFormat="1" ht="71.400000000000006" customHeight="1" thickBot="1">
+      <c r="B10" s="292" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="301"/>
-      <c r="D10" s="301"/>
-      <c r="E10" s="313"/>
-      <c r="F10" s="313"/>
-      <c r="G10" s="313"/>
-      <c r="H10" s="313"/>
-      <c r="I10" s="313"/>
-      <c r="J10" s="313"/>
-      <c r="K10" s="313"/>
-      <c r="L10" s="313"/>
-      <c r="M10" s="313"/>
-      <c r="N10" s="313"/>
-      <c r="O10" s="313"/>
-      <c r="P10" s="313"/>
+      <c r="C10" s="292"/>
+      <c r="D10" s="292"/>
+      <c r="E10" s="304"/>
+      <c r="F10" s="304"/>
+      <c r="G10" s="304"/>
+      <c r="H10" s="304"/>
+      <c r="I10" s="304"/>
+      <c r="J10" s="304"/>
+      <c r="K10" s="304"/>
+      <c r="L10" s="304"/>
+      <c r="M10" s="304"/>
+      <c r="N10" s="304"/>
+      <c r="O10" s="304"/>
+      <c r="P10" s="304"/>
       <c r="Q10" s="197"/>
       <c r="R10" s="197"/>
       <c r="S10" s="29"/>
@@ -3770,9 +3776,9 @@
       <c r="AA10" s="35"/>
     </row>
     <row r="11" spans="2:37" s="30" customFormat="1" ht="3" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="302"/>
-      <c r="C11" s="302"/>
-      <c r="D11" s="302"/>
+      <c r="B11" s="293"/>
+      <c r="C11" s="293"/>
+      <c r="D11" s="293"/>
       <c r="E11" s="198"/>
       <c r="F11" s="198"/>
       <c r="G11" s="198"/>
@@ -3791,108 +3797,108 @@
       <c r="T11" s="128"/>
       <c r="U11" s="34"/>
       <c r="V11" s="206"/>
-      <c r="W11" s="332"/>
-      <c r="X11" s="333"/>
-      <c r="Y11" s="333"/>
-      <c r="Z11" s="333"/>
-      <c r="AA11" s="334"/>
-    </row>
-    <row r="12" spans="2:37" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
-      <c r="B12" s="282" t="s">
+      <c r="W11" s="266"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
+      <c r="AA11" s="268"/>
+    </row>
+    <row r="12" spans="2:37" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
+      <c r="B12" s="322" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="283"/>
-      <c r="D12" s="288" t="s">
+      <c r="C12" s="323"/>
+      <c r="D12" s="328" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="291" t="s">
+      <c r="E12" s="331" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="292"/>
-      <c r="G12" s="293" t="s">
+      <c r="F12" s="332"/>
+      <c r="G12" s="333" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="294"/>
-      <c r="I12" s="273" t="s">
+      <c r="H12" s="334"/>
+      <c r="I12" s="313" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="274"/>
-      <c r="K12" s="307" t="s">
+      <c r="J12" s="314"/>
+      <c r="K12" s="298" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="308"/>
-      <c r="M12" s="309"/>
-      <c r="N12" s="317" t="s">
+      <c r="L12" s="299"/>
+      <c r="M12" s="300"/>
+      <c r="N12" s="308" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="318"/>
-      <c r="P12" s="319"/>
-      <c r="Q12" s="275" t="s">
+      <c r="O12" s="309"/>
+      <c r="P12" s="310"/>
+      <c r="Q12" s="315" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="276"/>
-      <c r="S12" s="279" t="s">
+      <c r="R12" s="316"/>
+      <c r="S12" s="319" t="s">
         <v>78</v>
       </c>
-      <c r="T12" s="295" t="s">
+      <c r="T12" s="335" t="s">
         <v>79</v>
       </c>
-      <c r="V12" s="345" t="s">
+      <c r="V12" s="262" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="269" t="s">
+      <c r="W12" s="260" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="343" t="s">
+      <c r="X12" s="258" t="s">
         <v>85</v>
       </c>
-      <c r="Y12" s="269" t="s">
+      <c r="Y12" s="260" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="330" t="s">
+      <c r="Z12" s="264" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:37" s="30" customFormat="1" ht="60.6" customHeight="1" thickBot="1">
-      <c r="B13" s="284"/>
-      <c r="C13" s="285"/>
-      <c r="D13" s="289"/>
-      <c r="E13" s="271" t="s">
+      <c r="B13" s="324"/>
+      <c r="C13" s="325"/>
+      <c r="D13" s="329"/>
+      <c r="E13" s="311" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="272"/>
-      <c r="G13" s="303" t="s">
+      <c r="F13" s="312"/>
+      <c r="G13" s="294" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="304"/>
-      <c r="I13" s="305" t="s">
+      <c r="H13" s="295"/>
+      <c r="I13" s="296" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="306"/>
-      <c r="K13" s="310" t="s">
+      <c r="J13" s="297"/>
+      <c r="K13" s="301" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="311"/>
-      <c r="M13" s="312"/>
-      <c r="N13" s="314" t="s">
+      <c r="L13" s="302"/>
+      <c r="M13" s="303"/>
+      <c r="N13" s="305" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="315"/>
-      <c r="P13" s="316"/>
-      <c r="Q13" s="277"/>
-      <c r="R13" s="278"/>
-      <c r="S13" s="280"/>
-      <c r="T13" s="296"/>
-      <c r="V13" s="346"/>
-      <c r="W13" s="270"/>
-      <c r="X13" s="344"/>
-      <c r="Y13" s="270"/>
-      <c r="Z13" s="331"/>
+      <c r="O13" s="306"/>
+      <c r="P13" s="307"/>
+      <c r="Q13" s="317"/>
+      <c r="R13" s="318"/>
+      <c r="S13" s="320"/>
+      <c r="T13" s="336"/>
+      <c r="V13" s="263"/>
+      <c r="W13" s="261"/>
+      <c r="X13" s="259"/>
+      <c r="Y13" s="261"/>
+      <c r="Z13" s="265"/>
     </row>
     <row r="14" spans="2:37" s="30" customFormat="1" ht="75" customHeight="1" thickBot="1">
-      <c r="B14" s="286"/>
-      <c r="C14" s="287"/>
-      <c r="D14" s="290"/>
+      <c r="B14" s="326"/>
+      <c r="C14" s="327"/>
+      <c r="D14" s="330"/>
       <c r="E14" s="182" t="s">
         <v>0</v>
       </c>
@@ -3935,8 +3941,8 @@
       <c r="R14" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="S14" s="281"/>
-      <c r="T14" s="297"/>
+      <c r="S14" s="321"/>
+      <c r="T14" s="337"/>
       <c r="V14" s="207"/>
       <c r="W14" s="208"/>
       <c r="X14" s="209"/>
@@ -3946,14 +3952,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B15" s="258">
+    <row r="15" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B15" s="288">
         <v>1</v>
       </c>
       <c r="C15" s="199" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="299">
+      <c r="D15" s="290">
         <v>36</v>
       </c>
       <c r="E15" s="235"/>
@@ -3968,18 +3974,18 @@
       <c r="N15" s="236"/>
       <c r="O15" s="237"/>
       <c r="P15" s="237"/>
-      <c r="Q15" s="260">
+      <c r="Q15" s="254">
         <f>SUM(E15:P15)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="264">
+      <c r="R15" s="256">
         <f>'บางบัวทอง-รถ'!C10</f>
         <v>0</v>
       </c>
-      <c r="S15" s="249">
+      <c r="S15" s="250">
         <v>260</v>
       </c>
-      <c r="T15" s="251">
+      <c r="T15" s="252">
         <f>SUM(S15-Q15)</f>
         <v>260</v>
       </c>
@@ -4008,12 +4014,12 @@
         <v>32 P</v>
       </c>
     </row>
-    <row r="16" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B16" s="259"/>
+    <row r="16" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B16" s="289"/>
       <c r="C16" s="203" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="300"/>
+      <c r="D16" s="291"/>
       <c r="E16" s="238" t="str">
         <f t="shared" ref="E16:P16" si="1">IF(E15=0, "", IF(MOD(E15, $D$15) = 0, E15 / $D$15, IF(INT(E15 / $D$15) = 0, MOD(E15, $D$15) &amp; " P", INT(E15 / $D$15) &amp; " + " &amp; MOD(E15, $D$15) &amp; " P")))</f>
         <v/>
@@ -4062,10 +4068,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="261"/>
-      <c r="R16" s="263"/>
-      <c r="S16" s="250"/>
-      <c r="T16" s="252"/>
+      <c r="Q16" s="255"/>
+      <c r="R16" s="257"/>
+      <c r="S16" s="251"/>
+      <c r="T16" s="253"/>
       <c r="V16" s="215"/>
       <c r="W16" s="216"/>
       <c r="X16" s="217"/>
@@ -4075,14 +4081,14 @@
         <v>129</v>
       </c>
     </row>
-    <row r="17" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B17" s="258">
+    <row r="17" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B17" s="288">
         <v>2</v>
       </c>
       <c r="C17" s="200" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="258">
+      <c r="D17" s="288">
         <v>32</v>
       </c>
       <c r="E17" s="235"/>
@@ -4097,18 +4103,18 @@
       <c r="N17" s="236"/>
       <c r="O17" s="237"/>
       <c r="P17" s="237"/>
-      <c r="Q17" s="260">
+      <c r="Q17" s="254">
         <f>SUM(E17:P17)</f>
         <v>0</v>
       </c>
-      <c r="R17" s="264">
+      <c r="R17" s="256">
         <f>'บางบัวทอง-รถ'!C11</f>
         <v>0</v>
       </c>
-      <c r="S17" s="249">
+      <c r="S17" s="250">
         <v>650</v>
       </c>
-      <c r="T17" s="251">
+      <c r="T17" s="252">
         <f>SUM(S17-Q17)</f>
         <v>650</v>
       </c>
@@ -4137,12 +4143,12 @@
         <v>4 + 1 P</v>
       </c>
     </row>
-    <row r="18" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B18" s="259"/>
+    <row r="18" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B18" s="289"/>
       <c r="C18" s="204" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="259"/>
+      <c r="D18" s="289"/>
       <c r="E18" s="238" t="str">
         <f>IF(E17=0, "", IF(MOD(E17, $D$17) = 0, E17 / $D$17, IF(INT(E17 / $D$17) = 0, MOD(E17, $D$17) &amp; " P", INT(E17 / $D$17) &amp; " + " &amp; MOD(E17, $D$17) &amp; " P")))</f>
         <v/>
@@ -4191,10 +4197,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="261"/>
-      <c r="R18" s="263"/>
-      <c r="S18" s="250"/>
-      <c r="T18" s="252"/>
+      <c r="Q18" s="255"/>
+      <c r="R18" s="257"/>
+      <c r="S18" s="251"/>
+      <c r="T18" s="253"/>
       <c r="V18" s="215"/>
       <c r="W18" s="216"/>
       <c r="X18" s="217"/>
@@ -4204,14 +4210,14 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B19" s="258">
+    <row r="19" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B19" s="288">
         <v>3</v>
       </c>
       <c r="C19" s="200" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="258">
+      <c r="D19" s="288">
         <v>36</v>
       </c>
       <c r="E19" s="240"/>
@@ -4226,18 +4232,18 @@
       <c r="N19" s="241"/>
       <c r="O19" s="243"/>
       <c r="P19" s="243"/>
-      <c r="Q19" s="260">
+      <c r="Q19" s="254">
         <f>SUM(E19:P19)</f>
         <v>0</v>
       </c>
-      <c r="R19" s="264">
+      <c r="R19" s="256">
         <f>'บางบัวทอง-รถ'!C12</f>
         <v>0</v>
       </c>
-      <c r="S19" s="249">
+      <c r="S19" s="250">
         <v>260</v>
       </c>
-      <c r="T19" s="251">
+      <c r="T19" s="252">
         <f>SUM(S19-Q19)</f>
         <v>260</v>
       </c>
@@ -4266,12 +4272,12 @@
         <v>1 + 18 P</v>
       </c>
     </row>
-    <row r="20" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B20" s="259"/>
+    <row r="20" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B20" s="289"/>
       <c r="C20" s="205" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="259"/>
+      <c r="D20" s="289"/>
       <c r="E20" s="238" t="str">
         <f>IF(E19=0, "", IF(MOD(E19, $D$19) = 0, E19 / $D$19, IF(INT(E19 / $D$19) = 0, MOD(E19, $D$19) &amp; " P", INT(E19 / $D$19) &amp; " + " &amp; MOD(E19, $D$19) &amp; " P")))</f>
         <v/>
@@ -4320,10 +4326,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="261"/>
-      <c r="R20" s="263"/>
-      <c r="S20" s="250"/>
-      <c r="T20" s="252"/>
+      <c r="Q20" s="255"/>
+      <c r="R20" s="257"/>
+      <c r="S20" s="251"/>
+      <c r="T20" s="253"/>
       <c r="V20" s="215"/>
       <c r="W20" s="216"/>
       <c r="X20" s="217"/>
@@ -4333,14 +4339,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B21" s="258">
+    <row r="21" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B21" s="288">
         <v>4</v>
       </c>
       <c r="C21" s="200" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="258">
+      <c r="D21" s="288">
         <v>14</v>
       </c>
       <c r="E21" s="235"/>
@@ -4355,18 +4361,18 @@
       <c r="N21" s="235"/>
       <c r="O21" s="235"/>
       <c r="P21" s="235"/>
-      <c r="Q21" s="260">
+      <c r="Q21" s="254">
         <f>SUM(E21:P21)</f>
         <v>0</v>
       </c>
-      <c r="R21" s="264">
+      <c r="R21" s="256">
         <f>'บางบัวทอง-รถ'!C13</f>
         <v>0</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="250">
         <v>220</v>
       </c>
-      <c r="T21" s="251">
+      <c r="T21" s="252">
         <f>SUM(S21-Q21)</f>
         <v>220</v>
       </c>
@@ -4395,12 +4401,12 @@
         <v>12 P</v>
       </c>
     </row>
-    <row r="22" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
-      <c r="B22" s="259"/>
+    <row r="22" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
+      <c r="B22" s="289"/>
       <c r="C22" s="204" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="259"/>
+      <c r="D22" s="289"/>
       <c r="E22" s="238" t="str">
         <f t="shared" ref="E22:P22" si="7">IF(E21=0, "", IF(MOD(E21, $D$21) = 0, E21/ $D$21, IF(INT(E21 / $D$21) = 0, MOD(E21, $D$21) &amp; " P", INT(E21 / $D$21) &amp; " + " &amp; MOD(E21, $D$21) &amp; " P")))</f>
         <v/>
@@ -4449,10 +4455,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q22" s="261"/>
-      <c r="R22" s="263"/>
-      <c r="S22" s="250"/>
-      <c r="T22" s="252"/>
+      <c r="Q22" s="255"/>
+      <c r="R22" s="257"/>
+      <c r="S22" s="251"/>
+      <c r="T22" s="253"/>
       <c r="V22" s="215"/>
       <c r="W22" s="216"/>
       <c r="X22" s="217"/>
@@ -4462,14 +4468,14 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="23" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B23" s="174">
         <v>5</v>
       </c>
       <c r="C23" s="200" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="256">
+      <c r="D23" s="341">
         <v>14</v>
       </c>
       <c r="E23" s="235"/>
@@ -4484,18 +4490,18 @@
       <c r="N23" s="235"/>
       <c r="O23" s="235"/>
       <c r="P23" s="235"/>
-      <c r="Q23" s="260">
+      <c r="Q23" s="254">
         <f>SUM(E23:P23)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="264">
+      <c r="R23" s="256">
         <f>'บางบัวทอง-รถ'!C14</f>
         <v>0</v>
       </c>
-      <c r="S23" s="249">
+      <c r="S23" s="250">
         <v>230</v>
       </c>
-      <c r="T23" s="251">
+      <c r="T23" s="252">
         <f>SUM(S23-Q23)</f>
         <v>230</v>
       </c>
@@ -4524,12 +4530,12 @@
         <v>16 + 3 P</v>
       </c>
     </row>
-    <row r="24" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="24" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B24" s="175"/>
       <c r="C24" s="204" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="257"/>
+      <c r="D24" s="342"/>
       <c r="E24" s="244" t="str">
         <f t="shared" ref="E24:P24" si="9">IF(E23=0, "", IF(MOD(E23, $D$23) = 0, E23/ $D$23, IF(INT(E23 / $D$23) = 0, MOD(E23, $D$23) &amp; " P", INT(E23 / $D$23) &amp; " + " &amp; MOD(E23, $D$23) &amp; " P")))</f>
         <v/>
@@ -4578,10 +4584,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q24" s="261"/>
-      <c r="R24" s="263"/>
-      <c r="S24" s="250"/>
-      <c r="T24" s="252"/>
+      <c r="Q24" s="255"/>
+      <c r="R24" s="257"/>
+      <c r="S24" s="251"/>
+      <c r="T24" s="253"/>
       <c r="V24" s="215"/>
       <c r="W24" s="216"/>
       <c r="X24" s="217"/>
@@ -4591,14 +4597,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="25" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B25" s="174">
         <v>6</v>
       </c>
       <c r="C25" s="200" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="258">
+      <c r="D25" s="288">
         <v>32</v>
       </c>
       <c r="E25" s="235"/>
@@ -4613,18 +4619,18 @@
       <c r="N25" s="236"/>
       <c r="O25" s="237"/>
       <c r="P25" s="237"/>
-      <c r="Q25" s="260">
+      <c r="Q25" s="254">
         <f>SUM(E25:P25)</f>
         <v>0</v>
       </c>
-      <c r="R25" s="264">
+      <c r="R25" s="256">
         <f>'บางบัวทอง-รถ'!C15</f>
         <v>0</v>
       </c>
-      <c r="S25" s="249">
+      <c r="S25" s="250">
         <v>320</v>
       </c>
-      <c r="T25" s="251">
+      <c r="T25" s="252">
         <f>SUM(S25-Q25)</f>
         <v>320</v>
       </c>
@@ -4653,12 +4659,12 @@
         <v>25 P</v>
       </c>
     </row>
-    <row r="26" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="26" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B26" s="175"/>
       <c r="C26" s="204" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="259"/>
+      <c r="D26" s="289"/>
       <c r="E26" s="238" t="str">
         <f t="shared" ref="E26:P26" si="11">IF(E25=0, "", IF(MOD(E25, $D$25) = 0, E25/ $D$25, IF(INT(E25 / $D$25) = 0, MOD(E25, $D$25) &amp; " P", INT(E25 / $D$25) &amp; " + " &amp; MOD(E25, $D$25) &amp; " P")))</f>
         <v/>
@@ -4707,10 +4713,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q26" s="261"/>
-      <c r="R26" s="263"/>
-      <c r="S26" s="250"/>
-      <c r="T26" s="252"/>
+      <c r="Q26" s="255"/>
+      <c r="R26" s="257"/>
+      <c r="S26" s="251"/>
+      <c r="T26" s="253"/>
       <c r="V26" s="215"/>
       <c r="W26" s="216"/>
       <c r="X26" s="217"/>
@@ -4720,14 +4726,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="27" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B27" s="174">
         <v>7</v>
       </c>
       <c r="C27" s="201" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="256">
+      <c r="D27" s="341">
         <v>27</v>
       </c>
       <c r="E27" s="235"/>
@@ -4742,18 +4748,18 @@
       <c r="N27" s="236"/>
       <c r="O27" s="237"/>
       <c r="P27" s="237"/>
-      <c r="Q27" s="260">
+      <c r="Q27" s="254">
         <f>SUM(E27:P27)</f>
         <v>0</v>
       </c>
-      <c r="R27" s="264">
+      <c r="R27" s="256">
         <f>'บางบัวทอง-รถ'!C16</f>
         <v>0</v>
       </c>
-      <c r="S27" s="249">
+      <c r="S27" s="250">
         <v>280</v>
       </c>
-      <c r="T27" s="251">
+      <c r="T27" s="252">
         <f>SUM(S27-Q27)</f>
         <v>280</v>
       </c>
@@ -4782,12 +4788,12 @@
         <v>2 P</v>
       </c>
     </row>
-    <row r="28" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="28" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B28" s="175"/>
       <c r="C28" s="204" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="257"/>
+      <c r="D28" s="342"/>
       <c r="E28" s="238" t="str">
         <f t="shared" ref="E28:P28" si="13">IF(E27=0, "", IF(MOD(E27, $D$27) = 0, E27/ $D$27, IF(INT(E27 / $D$27) = 0, MOD(E27, $D$27) &amp; " P", INT(E27 / $D$27) &amp; " + " &amp; MOD(E27, $D$27) &amp; " P")))</f>
         <v/>
@@ -4836,10 +4842,10 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q28" s="261"/>
-      <c r="R28" s="263"/>
-      <c r="S28" s="250"/>
-      <c r="T28" s="252"/>
+      <c r="Q28" s="255"/>
+      <c r="R28" s="257"/>
+      <c r="S28" s="251"/>
+      <c r="T28" s="253"/>
       <c r="V28" s="211"/>
       <c r="W28" s="216"/>
       <c r="X28" s="217"/>
@@ -4849,7 +4855,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="29" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B29" s="174">
         <v>8</v>
       </c>
@@ -4871,18 +4877,18 @@
       <c r="N29" s="241"/>
       <c r="O29" s="243"/>
       <c r="P29" s="243"/>
-      <c r="Q29" s="260">
+      <c r="Q29" s="254">
         <f>SUM(E29:P29)</f>
         <v>0</v>
       </c>
-      <c r="R29" s="264">
+      <c r="R29" s="256">
         <f>'บางบัวทอง-รถ'!C17</f>
         <v>0</v>
       </c>
-      <c r="S29" s="249">
+      <c r="S29" s="250">
         <v>680</v>
       </c>
-      <c r="T29" s="251">
+      <c r="T29" s="252">
         <f>SUM(S29-Q29)</f>
         <v>680</v>
       </c>
@@ -4911,7 +4917,7 @@
         <v>2 + 2 P</v>
       </c>
     </row>
-    <row r="30" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="30" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B30" s="175"/>
       <c r="C30" s="204" t="s">
         <v>113</v>
@@ -4965,10 +4971,10 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q30" s="261"/>
-      <c r="R30" s="263"/>
-      <c r="S30" s="250"/>
-      <c r="T30" s="252"/>
+      <c r="Q30" s="255"/>
+      <c r="R30" s="257"/>
+      <c r="S30" s="251"/>
+      <c r="T30" s="253"/>
       <c r="V30" s="211"/>
       <c r="W30" s="216"/>
       <c r="X30" s="217"/>
@@ -4978,7 +4984,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="31" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B31" s="174">
         <v>9</v>
       </c>
@@ -5000,18 +5006,18 @@
       <c r="N31" s="241"/>
       <c r="O31" s="243"/>
       <c r="P31" s="243"/>
-      <c r="Q31" s="260">
+      <c r="Q31" s="254">
         <f>SUM(E31:P31)</f>
         <v>0</v>
       </c>
-      <c r="R31" s="262">
+      <c r="R31" s="343">
         <f>'บางบัวทอง-รถ'!C18</f>
         <v>0</v>
       </c>
-      <c r="S31" s="249">
+      <c r="S31" s="250">
         <v>160</v>
       </c>
-      <c r="T31" s="251">
+      <c r="T31" s="252">
         <f>SUM(S31-Q31)</f>
         <v>160</v>
       </c>
@@ -5040,7 +5046,7 @@
         <v>1 + 14 P</v>
       </c>
     </row>
-    <row r="32" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="32" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B32" s="175"/>
       <c r="C32" s="205" t="s">
         <v>107</v>
@@ -5094,10 +5100,10 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q32" s="261"/>
-      <c r="R32" s="263"/>
-      <c r="S32" s="250"/>
-      <c r="T32" s="252"/>
+      <c r="Q32" s="255"/>
+      <c r="R32" s="257"/>
+      <c r="S32" s="251"/>
+      <c r="T32" s="253"/>
       <c r="V32" s="211"/>
       <c r="W32" s="216"/>
       <c r="X32" s="217"/>
@@ -5107,14 +5113,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="33" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B33" s="174">
         <v>10</v>
       </c>
       <c r="C33" s="202" t="s">
         <v>129</v>
       </c>
-      <c r="D33" s="267">
+      <c r="D33" s="346">
         <v>15</v>
       </c>
       <c r="E33" s="240"/>
@@ -5129,18 +5135,18 @@
       <c r="N33" s="241"/>
       <c r="O33" s="243"/>
       <c r="P33" s="243"/>
-      <c r="Q33" s="260">
+      <c r="Q33" s="254">
         <f>SUM(E33:P33)</f>
         <v>0</v>
       </c>
-      <c r="R33" s="262">
+      <c r="R33" s="343">
         <f>'บางบัวทอง-รถ'!C19</f>
         <v>0</v>
       </c>
-      <c r="S33" s="249">
+      <c r="S33" s="250">
         <v>160</v>
       </c>
-      <c r="T33" s="251">
+      <c r="T33" s="252">
         <f>SUM(S33-Q33)</f>
         <v>160</v>
       </c>
@@ -5169,12 +5175,12 @@
         <v>1 + 13 P</v>
       </c>
     </row>
-    <row r="34" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="34" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B34" s="175"/>
       <c r="C34" s="204" t="s">
         <v>130</v>
       </c>
-      <c r="D34" s="268"/>
+      <c r="D34" s="347"/>
       <c r="E34" s="238" t="str">
         <f>IF(E33=0, "", IF(MOD(E33, $D$33) = 0, E33/ $D$33, IF(INT(E33 / $D$33) = 0, MOD(E33, $D$33) &amp; " P", INT(E33 / $D$33) &amp; " + " &amp; MOD(E33, $D$33) &amp; " P")))</f>
         <v/>
@@ -5223,10 +5229,10 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="Q34" s="261"/>
-      <c r="R34" s="263"/>
-      <c r="S34" s="250"/>
-      <c r="T34" s="252"/>
+      <c r="Q34" s="255"/>
+      <c r="R34" s="257"/>
+      <c r="S34" s="251"/>
+      <c r="T34" s="253"/>
       <c r="V34" s="211"/>
       <c r="W34" s="216"/>
       <c r="X34" s="217"/>
@@ -5236,7 +5242,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="35" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B35" s="174">
         <v>11</v>
       </c>
@@ -5258,18 +5264,18 @@
       <c r="N35" s="242"/>
       <c r="O35" s="246"/>
       <c r="P35" s="246"/>
-      <c r="Q35" s="260">
+      <c r="Q35" s="254">
         <f>SUM(E35:P35)</f>
         <v>0</v>
       </c>
-      <c r="R35" s="264">
+      <c r="R35" s="256">
         <f>'บางบัวทอง-รถ'!C20</f>
         <v>0</v>
       </c>
-      <c r="S35" s="249">
+      <c r="S35" s="250">
         <v>50</v>
       </c>
-      <c r="T35" s="251">
+      <c r="T35" s="252">
         <f t="shared" ref="T35" si="18">SUM(S35-Q35)</f>
         <v>50</v>
       </c>
@@ -5298,7 +5304,7 @@
         <v>2 + 4 P</v>
       </c>
     </row>
-    <row r="36" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="36" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B36" s="175"/>
       <c r="C36" s="205" t="s">
         <v>114</v>
@@ -5352,17 +5358,17 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q36" s="261"/>
-      <c r="R36" s="263"/>
-      <c r="S36" s="250"/>
-      <c r="T36" s="252"/>
+      <c r="Q36" s="255"/>
+      <c r="R36" s="257"/>
+      <c r="S36" s="251"/>
+      <c r="T36" s="253"/>
       <c r="V36" s="211"/>
       <c r="W36" s="216"/>
       <c r="X36" s="217"/>
       <c r="Y36" s="212"/>
       <c r="Z36" s="218"/>
     </row>
-    <row r="37" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="37" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B37" s="174">
         <v>12</v>
       </c>
@@ -5384,18 +5390,18 @@
       <c r="N37" s="235"/>
       <c r="O37" s="235"/>
       <c r="P37" s="235"/>
-      <c r="Q37" s="260">
+      <c r="Q37" s="254">
         <f>SUM(E37:P37)</f>
         <v>0</v>
       </c>
-      <c r="R37" s="264">
+      <c r="R37" s="256">
         <f>'บางบัวทอง-รถ'!C21</f>
         <v>0</v>
       </c>
-      <c r="S37" s="249">
+      <c r="S37" s="250">
         <v>190</v>
       </c>
-      <c r="T37" s="251">
+      <c r="T37" s="252">
         <f t="shared" ref="T37" si="20">SUM(S37-Q37)</f>
         <v>190</v>
       </c>
@@ -5424,7 +5430,7 @@
         <v>2 + 3 P</v>
       </c>
     </row>
-    <row r="38" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="38" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B38" s="175"/>
       <c r="C38" s="205" t="s">
         <v>134</v>
@@ -5478,17 +5484,17 @@
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Q38" s="261"/>
-      <c r="R38" s="263"/>
-      <c r="S38" s="250"/>
-      <c r="T38" s="252"/>
+      <c r="Q38" s="255"/>
+      <c r="R38" s="257"/>
+      <c r="S38" s="251"/>
+      <c r="T38" s="253"/>
       <c r="V38" s="211"/>
       <c r="W38" s="216"/>
       <c r="X38" s="217"/>
       <c r="Y38" s="212"/>
       <c r="Z38" s="218"/>
     </row>
-    <row r="39" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="39" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B39" s="174">
         <v>13</v>
       </c>
@@ -5510,18 +5516,18 @@
       <c r="N39" s="235"/>
       <c r="O39" s="235"/>
       <c r="P39" s="235"/>
-      <c r="Q39" s="260">
+      <c r="Q39" s="254">
         <f>SUM(E39:P39)</f>
         <v>0</v>
       </c>
-      <c r="R39" s="264">
+      <c r="R39" s="256">
         <f>'บางบัวทอง-รถ'!C22</f>
         <v>0</v>
       </c>
-      <c r="S39" s="249">
+      <c r="S39" s="250">
         <v>100</v>
       </c>
-      <c r="T39" s="251">
+      <c r="T39" s="252">
         <f t="shared" ref="T39" si="22">SUM(S39-Q39)</f>
         <v>100</v>
       </c>
@@ -5550,7 +5556,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="40" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B40" s="175"/>
       <c r="C40" s="205" t="s">
         <v>118</v>
@@ -5604,17 +5610,17 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q40" s="261"/>
-      <c r="R40" s="263"/>
-      <c r="S40" s="250"/>
-      <c r="T40" s="252"/>
+      <c r="Q40" s="255"/>
+      <c r="R40" s="257"/>
+      <c r="S40" s="251"/>
+      <c r="T40" s="253"/>
       <c r="V40" s="211"/>
       <c r="W40" s="216"/>
       <c r="X40" s="217"/>
       <c r="Y40" s="212"/>
       <c r="Z40" s="218"/>
     </row>
-    <row r="41" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="41" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B41" s="174">
         <v>14</v>
       </c>
@@ -5636,18 +5642,18 @@
       <c r="N41" s="235"/>
       <c r="O41" s="235"/>
       <c r="P41" s="235"/>
-      <c r="Q41" s="260">
+      <c r="Q41" s="254">
         <f>SUM(E41:P41)</f>
         <v>0</v>
       </c>
-      <c r="R41" s="264">
+      <c r="R41" s="256">
         <f>'บางบัวทอง-รถ'!C23</f>
         <v>0</v>
       </c>
-      <c r="S41" s="249">
+      <c r="S41" s="250">
         <v>812</v>
       </c>
-      <c r="T41" s="251">
+      <c r="T41" s="252">
         <f t="shared" ref="T41" si="24">SUM(S41-Q41)</f>
         <v>812</v>
       </c>
@@ -5676,7 +5682,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="42" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B42" s="175"/>
       <c r="C42" s="205" t="s">
         <v>132</v>
@@ -5730,17 +5736,17 @@
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="Q42" s="261"/>
-      <c r="R42" s="263"/>
-      <c r="S42" s="250"/>
-      <c r="T42" s="252"/>
+      <c r="Q42" s="255"/>
+      <c r="R42" s="257"/>
+      <c r="S42" s="251"/>
+      <c r="T42" s="253"/>
       <c r="V42" s="211"/>
       <c r="W42" s="216"/>
       <c r="X42" s="217"/>
       <c r="Y42" s="212"/>
       <c r="Z42" s="218"/>
     </row>
-    <row r="43" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="43" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B43" s="174">
         <v>15</v>
       </c>
@@ -5762,18 +5768,18 @@
       <c r="N43" s="235"/>
       <c r="O43" s="235"/>
       <c r="P43" s="235"/>
-      <c r="Q43" s="260">
+      <c r="Q43" s="254">
         <f>SUM(E43:P43)</f>
         <v>0</v>
       </c>
-      <c r="R43" s="264">
+      <c r="R43" s="256">
         <f>'บางบัวทอง-รถ'!C24</f>
         <v>0</v>
       </c>
-      <c r="S43" s="249">
+      <c r="S43" s="250">
         <v>400</v>
       </c>
-      <c r="T43" s="251">
+      <c r="T43" s="252">
         <f t="shared" ref="T43" si="26">SUM(S43-Q43)</f>
         <v>400</v>
       </c>
@@ -5802,7 +5808,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="44" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B44" s="175"/>
       <c r="C44" s="204" t="s">
         <v>115</v>
@@ -5856,17 +5862,17 @@
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="Q44" s="261"/>
-      <c r="R44" s="263"/>
-      <c r="S44" s="250"/>
-      <c r="T44" s="252"/>
+      <c r="Q44" s="255"/>
+      <c r="R44" s="257"/>
+      <c r="S44" s="251"/>
+      <c r="T44" s="253"/>
       <c r="V44" s="211"/>
       <c r="W44" s="216"/>
       <c r="X44" s="217"/>
       <c r="Y44" s="212"/>
       <c r="Z44" s="218"/>
     </row>
-    <row r="45" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="45" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B45" s="174">
         <v>16</v>
       </c>
@@ -5888,18 +5894,18 @@
       <c r="N45" s="235"/>
       <c r="O45" s="235"/>
       <c r="P45" s="235"/>
-      <c r="Q45" s="260">
+      <c r="Q45" s="254">
         <f>SUM(E45:P45)</f>
         <v>0</v>
       </c>
-      <c r="R45" s="264">
+      <c r="R45" s="256">
         <f>'บางบัวทอง-รถ'!C25</f>
         <v>0</v>
       </c>
-      <c r="S45" s="249">
+      <c r="S45" s="250">
         <v>200</v>
       </c>
-      <c r="T45" s="251">
+      <c r="T45" s="252">
         <f t="shared" ref="T45" si="28">SUM(S45-Q45)</f>
         <v>200</v>
       </c>
@@ -5928,7 +5934,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="46" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B46" s="175"/>
       <c r="C46" s="204" t="s">
         <v>116</v>
@@ -5943,7 +5949,7 @@
         <v/>
       </c>
       <c r="G46" s="238" t="str">
-        <f t="shared" ref="F46:P46" si="29">IF(G45=0, "", IF(MOD(G45, $D$45) = 0, G45/ $D$45, IF(INT(G45 / $D$45) = 0, MOD(G45, $D$45) &amp; " P", INT(G45 / $D$45) &amp; " + " &amp; MOD(G45, $D$45) &amp; " P")))</f>
+        <f t="shared" ref="G46:P46" si="29">IF(G45=0, "", IF(MOD(G45, $D$45) = 0, G45/ $D$45, IF(INT(G45 / $D$45) = 0, MOD(G45, $D$45) &amp; " P", INT(G45 / $D$45) &amp; " + " &amp; MOD(G45, $D$45) &amp; " P")))</f>
         <v/>
       </c>
       <c r="H46" s="248" t="str">
@@ -5982,17 +5988,17 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="Q46" s="261"/>
-      <c r="R46" s="263"/>
-      <c r="S46" s="250"/>
-      <c r="T46" s="252"/>
+      <c r="Q46" s="255"/>
+      <c r="R46" s="257"/>
+      <c r="S46" s="251"/>
+      <c r="T46" s="253"/>
       <c r="V46" s="211"/>
       <c r="W46" s="216"/>
       <c r="X46" s="217"/>
       <c r="Y46" s="212"/>
       <c r="Z46" s="218"/>
     </row>
-    <row r="47" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="47" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B47" s="223">
         <v>17</v>
       </c>
@@ -6014,18 +6020,18 @@
       <c r="N47" s="235"/>
       <c r="O47" s="235"/>
       <c r="P47" s="235"/>
-      <c r="Q47" s="260">
+      <c r="Q47" s="254">
         <f>SUM(E47:P47)</f>
         <v>0</v>
       </c>
-      <c r="R47" s="264">
+      <c r="R47" s="256">
         <f>'บางบัวทอง-รถ'!C26</f>
         <v>0</v>
       </c>
-      <c r="S47" s="249">
+      <c r="S47" s="250">
         <v>110</v>
       </c>
-      <c r="T47" s="251">
+      <c r="T47" s="252">
         <f t="shared" ref="T47" si="30">SUM(S47-Q47)</f>
         <v>110</v>
       </c>
@@ -6054,7 +6060,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="48" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B48" s="224"/>
       <c r="C48" s="205" t="s">
         <v>117</v>
@@ -6108,17 +6114,17 @@
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="Q48" s="261"/>
-      <c r="R48" s="263"/>
-      <c r="S48" s="250"/>
-      <c r="T48" s="252"/>
+      <c r="Q48" s="255"/>
+      <c r="R48" s="257"/>
+      <c r="S48" s="251"/>
+      <c r="T48" s="253"/>
       <c r="V48" s="211"/>
       <c r="W48" s="216"/>
       <c r="X48" s="217"/>
       <c r="Y48" s="212"/>
       <c r="Z48" s="218"/>
     </row>
-    <row r="49" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="49" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B49" s="174">
         <v>18</v>
       </c>
@@ -6126,7 +6132,7 @@
         <v>146</v>
       </c>
       <c r="D49" s="230">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E49" s="235"/>
       <c r="F49" s="235"/>
@@ -6140,18 +6146,18 @@
       <c r="N49" s="235"/>
       <c r="O49" s="235"/>
       <c r="P49" s="235"/>
-      <c r="Q49" s="260">
+      <c r="Q49" s="254">
         <f>SUM(E49:P49)</f>
         <v>0</v>
       </c>
-      <c r="R49" s="264">
+      <c r="R49" s="256">
         <f>'บางบัวทอง-รถ'!C27</f>
         <v>0</v>
       </c>
-      <c r="S49" s="249">
+      <c r="S49" s="250">
         <v>50</v>
       </c>
-      <c r="T49" s="251">
+      <c r="T49" s="252">
         <f t="shared" ref="T49" si="32">SUM(S49-Q49)</f>
         <v>50</v>
       </c>
@@ -6180,7 +6186,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:37" s="30" customFormat="1" ht="55.9" customHeight="1" thickBot="1">
+    <row r="50" spans="2:37" s="30" customFormat="1" ht="55.95" customHeight="1" thickBot="1">
       <c r="B50" s="175"/>
       <c r="C50" s="233" t="s">
         <v>145</v>
@@ -6234,67 +6240,67 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="Q50" s="261"/>
-      <c r="R50" s="263"/>
-      <c r="S50" s="250"/>
-      <c r="T50" s="252"/>
+      <c r="Q50" s="255"/>
+      <c r="R50" s="257"/>
+      <c r="S50" s="251"/>
+      <c r="T50" s="253"/>
       <c r="V50" s="211"/>
       <c r="W50" s="216"/>
       <c r="X50" s="217"/>
       <c r="Y50" s="212"/>
       <c r="Z50" s="218"/>
     </row>
-    <row r="51" spans="2:37" s="30" customFormat="1" ht="79.900000000000006" customHeight="1" thickBot="1">
-      <c r="B51" s="340" t="s">
+    <row r="51" spans="2:37" s="30" customFormat="1" ht="79.95" customHeight="1" thickBot="1">
+      <c r="B51" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="341"/>
-      <c r="D51" s="342"/>
-      <c r="E51" s="418">
+      <c r="C51" s="275"/>
+      <c r="D51" s="276"/>
+      <c r="E51" s="249">
         <f>-SUM(ROUNDUP(E15/$D$15,0), ROUNDUP(E17/$D$17,0), ROUNDUP(E19/$D$19,0), ROUNDUP(E21/$D$21,0), ROUNDUP(E23/$D$23,0), ROUNDUP(E25/$D$25,0), ROUNDUP(E27/$D$27,0), ROUNDUP(E29/$D$29,0), ROUNDUP(E31/$D$31,0), ROUNDUP(E33/$D$33,0), ROUNDUP(E35/$D$35,0), ROUNDUP(E37/$D$37,0), ROUNDUP(E39/$D$39,0), ROUNDUP(E41/$D$41,0), ROUNDUP(E43/$D$43,0), ROUNDUP(E45/$D$45,0), ROUNDUP(E47/$D$47,0), ROUNDUP(E49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="F51" s="418">
+      <c r="F51" s="249">
         <f>-SUM(ROUNDUP(F15/$D$15,0), ROUNDUP(F17/$D$17,0), ROUNDUP(F19/$D$19,0), ROUNDUP(F21/$D$21,0), ROUNDUP(F23/$D$23,0), ROUNDUP(F25/$D$25,0), ROUNDUP(F27/$D$27,0), ROUNDUP(F29/$D$29,0), ROUNDUP(F31/$D$31,0), ROUNDUP(F33/$D$33,0), ROUNDUP(F35/$D$35,0), ROUNDUP(F37/$D$37,0), ROUNDUP(F39/$D$39,0), ROUNDUP(F41/$D$41,0), ROUNDUP(F43/$D$43,0), ROUNDUP(F45/$D$45,0), ROUNDUP(F47/$D$47,0), ROUNDUP(F49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="G51" s="418">
+      <c r="G51" s="249">
         <f>-SUM(ROUNDUP(G15/$D$15,0), ROUNDUP(G17/$D$17,0), ROUNDUP(G19/$D$19,0), ROUNDUP(G21/$D$21,0), ROUNDUP(G23/$D$23,0), ROUNDUP(G25/$D$25,0), ROUNDUP(G27/$D$27,0), ROUNDUP(G29/$D$29,0), ROUNDUP(G31/$D$31,0), ROUNDUP(G33/$D$33,0), ROUNDUP(G35/$D$35,0), ROUNDUP(G37/$D$37,0), ROUNDUP(G39/$D$39,0), ROUNDUP(G41/$D$41,0), ROUNDUP(G43/$D$43,0), ROUNDUP(G45/$D$45,0), ROUNDUP(G47/$D$47,0), ROUNDUP(G49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="H51" s="418">
+      <c r="H51" s="249">
         <f>-SUM(ROUNDUP(H15/$D$15,0), ROUNDUP(H17/$D$17,0), ROUNDUP(H19/$D$19,0), ROUNDUP(H21/$D$21,0), ROUNDUP(H23/$D$23,0), ROUNDUP(H25/$D$25,0), ROUNDUP(H27/$D$27,0), ROUNDUP(H29/$D$29,0), ROUNDUP(H31/$D$31,0), ROUNDUP(H33/$D$33,0), ROUNDUP(H35/$D$35,0), ROUNDUP(H37/$D$37,0), ROUNDUP(H39/$D$39,0), ROUNDUP(H41/$D$41,0), ROUNDUP(H43/$D$43,0), ROUNDUP(H45/$D$45,0), ROUNDUP(H47/$D$47,0), ROUNDUP(H49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="I51" s="418">
+      <c r="I51" s="249">
         <f>-SUM(ROUNDUP(I15/$D$15,0), ROUNDUP(I17/$D$17,0), ROUNDUP(I19/$D$19,0), ROUNDUP(I21/$D$21,0), ROUNDUP(I23/$D$23,0), ROUNDUP(I25/$D$25,0), ROUNDUP(I27/$D$27,0), ROUNDUP(I29/$D$29,0), ROUNDUP(I31/$D$31,0), ROUNDUP(I33/$D$33,0), ROUNDUP(I35/$D$35,0), ROUNDUP(I37/$D$37,0), ROUNDUP(I39/$D$39,0), ROUNDUP(I41/$D$41,0), ROUNDUP(I43/$D$43,0), ROUNDUP(I45/$D$45,0), ROUNDUP(I47/$D$47,0), ROUNDUP(I49/$D$49,0))</f>
         <v>0</v>
       </c>
-      <c r="J51" s="418">
-        <f t="shared" ref="F51:P51" si="34">-SUM(ROUNDUP(J15/$D$15,0), ROUNDUP(J17/$D$17,0), ROUNDUP(J19/$D$19,0), ROUNDUP(J21/$D$21,0), ROUNDUP(J23/$D$23,0), ROUNDUP(J25/$D$25,0), ROUNDUP(J27/$D$27,0), ROUNDUP(J29/$D$29,0), ROUNDUP(J31/$D$31,0), ROUNDUP(J33/$D$33,0), ROUNDUP(J35/$D$35,0), ROUNDUP(J37/$D$37,0), ROUNDUP(J39/$D$39,0), ROUNDUP(J41/$D$41,0), ROUNDUP(J43/$D$43,0), ROUNDUP(J45/$D$45,0), ROUNDUP(J47/$D$47,0), ROUNDUP(J49/$D$49,0))</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="418">
+      <c r="J51" s="249">
+        <f t="shared" ref="J51:P51" si="34">-SUM(ROUNDUP(J15/$D$15,0), ROUNDUP(J17/$D$17,0), ROUNDUP(J19/$D$19,0), ROUNDUP(J21/$D$21,0), ROUNDUP(J23/$D$23,0), ROUNDUP(J25/$D$25,0), ROUNDUP(J27/$D$27,0), ROUNDUP(J29/$D$29,0), ROUNDUP(J31/$D$31,0), ROUNDUP(J33/$D$33,0), ROUNDUP(J35/$D$35,0), ROUNDUP(J37/$D$37,0), ROUNDUP(J39/$D$39,0), ROUNDUP(J41/$D$41,0), ROUNDUP(J43/$D$43,0), ROUNDUP(J45/$D$45,0), ROUNDUP(J47/$D$47,0), ROUNDUP(J49/$D$49,0))</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="249">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="L51" s="418">
+      <c r="L51" s="249">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="M51" s="418">
+      <c r="M51" s="249">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="N51" s="418">
+      <c r="N51" s="249">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="O51" s="418">
+      <c r="O51" s="249">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="P51" s="418">
+      <c r="P51" s="249">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
@@ -6311,38 +6317,38 @@
       <c r="Y51" s="222"/>
       <c r="Z51" s="221"/>
     </row>
-    <row r="52" spans="2:37" ht="22.9" customHeight="1" thickBot="1"/>
-    <row r="53" spans="2:37" s="30" customFormat="1" ht="58.15" customHeight="1" thickBot="1">
-      <c r="B53" s="324" t="s">
+    <row r="52" spans="2:37" ht="22.95" customHeight="1" thickBot="1"/>
+    <row r="53" spans="2:37" s="30" customFormat="1" ht="58.2" customHeight="1" thickBot="1">
+      <c r="B53" s="281" t="s">
         <v>49</v>
       </c>
-      <c r="C53" s="325"/>
-      <c r="D53" s="324" t="s">
+      <c r="C53" s="282"/>
+      <c r="D53" s="281" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="325"/>
-      <c r="F53" s="324" t="s">
+      <c r="E53" s="282"/>
+      <c r="F53" s="281" t="s">
         <v>54</v>
       </c>
-      <c r="G53" s="325"/>
-      <c r="H53" s="324" t="s">
+      <c r="G53" s="282"/>
+      <c r="H53" s="281" t="s">
         <v>71</v>
       </c>
-      <c r="I53" s="325"/>
-      <c r="J53" s="265" t="s">
+      <c r="I53" s="282"/>
+      <c r="J53" s="344" t="s">
         <v>88</v>
       </c>
-      <c r="K53" s="266"/>
-      <c r="L53" s="266"/>
-      <c r="M53" s="266"/>
-      <c r="N53" s="266"/>
-      <c r="O53" s="266"/>
-      <c r="P53" s="266"/>
-      <c r="Q53" s="253">
+      <c r="K53" s="345"/>
+      <c r="L53" s="345"/>
+      <c r="M53" s="345"/>
+      <c r="N53" s="345"/>
+      <c r="O53" s="345"/>
+      <c r="P53" s="345"/>
+      <c r="Q53" s="338">
         <f>SUM(R51)</f>
         <v>0</v>
       </c>
-      <c r="R53" s="255" t="s">
+      <c r="R53" s="340" t="s">
         <v>89</v>
       </c>
       <c r="T53" s="36"/>
@@ -6352,26 +6358,26 @@
       <c r="Y53" s="206"/>
       <c r="Z53" s="206"/>
     </row>
-    <row r="54" spans="2:37" s="30" customFormat="1" ht="52.9" customHeight="1">
-      <c r="B54" s="326" t="s">
+    <row r="54" spans="2:37" s="30" customFormat="1" ht="52.95" customHeight="1">
+      <c r="B54" s="283" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="327"/>
-      <c r="D54" s="328"/>
-      <c r="E54" s="329"/>
-      <c r="F54" s="328"/>
-      <c r="G54" s="329"/>
-      <c r="H54" s="328"/>
-      <c r="I54" s="329"/>
-      <c r="J54" s="265"/>
-      <c r="K54" s="266"/>
-      <c r="L54" s="266"/>
-      <c r="M54" s="266"/>
-      <c r="N54" s="266"/>
-      <c r="O54" s="266"/>
-      <c r="P54" s="266"/>
-      <c r="Q54" s="254"/>
-      <c r="R54" s="255"/>
+      <c r="C54" s="284"/>
+      <c r="D54" s="285"/>
+      <c r="E54" s="286"/>
+      <c r="F54" s="285"/>
+      <c r="G54" s="286"/>
+      <c r="H54" s="285"/>
+      <c r="I54" s="286"/>
+      <c r="J54" s="344"/>
+      <c r="K54" s="345"/>
+      <c r="L54" s="345"/>
+      <c r="M54" s="345"/>
+      <c r="N54" s="345"/>
+      <c r="O54" s="345"/>
+      <c r="P54" s="345"/>
+      <c r="Q54" s="339"/>
+      <c r="R54" s="340"/>
       <c r="T54" s="36"/>
       <c r="V54" s="206"/>
       <c r="W54" s="206"/>
@@ -6379,26 +6385,26 @@
       <c r="Y54" s="206"/>
       <c r="Z54" s="206"/>
     </row>
-    <row r="55" spans="2:37" s="30" customFormat="1" ht="52.9" customHeight="1" thickBot="1">
-      <c r="B55" s="335" t="s">
+    <row r="55" spans="2:37" s="30" customFormat="1" ht="52.95" customHeight="1" thickBot="1">
+      <c r="B55" s="269" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="336"/>
-      <c r="D55" s="337"/>
-      <c r="E55" s="338"/>
-      <c r="F55" s="337"/>
-      <c r="G55" s="338"/>
-      <c r="H55" s="337"/>
-      <c r="I55" s="338"/>
+      <c r="C55" s="270"/>
+      <c r="D55" s="271"/>
+      <c r="E55" s="272"/>
+      <c r="F55" s="271"/>
+      <c r="G55" s="272"/>
+      <c r="H55" s="271"/>
+      <c r="I55" s="272"/>
       <c r="J55" s="38"/>
       <c r="M55" s="67"/>
-      <c r="N55" s="339" t="s">
+      <c r="N55" s="273" t="s">
         <v>73</v>
       </c>
-      <c r="O55" s="339"/>
-      <c r="P55" s="339"/>
-      <c r="Q55" s="339"/>
-      <c r="R55" s="339"/>
+      <c r="O55" s="273"/>
+      <c r="P55" s="273"/>
+      <c r="Q55" s="273"/>
+      <c r="R55" s="273"/>
       <c r="T55" s="36"/>
       <c r="V55" s="206"/>
       <c r="W55" s="206"/>
@@ -6406,17 +6412,17 @@
       <c r="Y55" s="206"/>
       <c r="Z55" s="206"/>
     </row>
-    <row r="56" spans="2:37" s="30" customFormat="1" ht="52.9" customHeight="1" thickBot="1">
-      <c r="B56" s="320" t="s">
+    <row r="56" spans="2:37" s="30" customFormat="1" ht="52.95" customHeight="1" thickBot="1">
+      <c r="B56" s="277" t="s">
         <v>76</v>
       </c>
-      <c r="C56" s="321"/>
-      <c r="D56" s="322"/>
-      <c r="E56" s="323"/>
-      <c r="F56" s="322"/>
-      <c r="G56" s="323"/>
-      <c r="H56" s="322"/>
-      <c r="I56" s="323"/>
+      <c r="C56" s="278"/>
+      <c r="D56" s="279"/>
+      <c r="E56" s="280"/>
+      <c r="F56" s="279"/>
+      <c r="G56" s="280"/>
+      <c r="H56" s="279"/>
+      <c r="I56" s="280"/>
       <c r="J56" s="38"/>
       <c r="K56" s="234" t="s">
         <v>77</v>
@@ -6441,7 +6447,7 @@
       <c r="Y56" s="206"/>
       <c r="Z56" s="206"/>
     </row>
-    <row r="57" spans="2:37" s="30" customFormat="1" ht="64.150000000000006" customHeight="1" thickBot="1">
+    <row r="57" spans="2:37" s="30" customFormat="1" ht="64.2" customHeight="1" thickBot="1">
       <c r="B57" s="38"/>
       <c r="C57" s="38"/>
       <c r="D57" s="89"/>
@@ -6468,6 +6474,111 @@
     </row>
   </sheetData>
   <mergeCells count="129">
+    <mergeCell ref="S47:S48"/>
+    <mergeCell ref="T47:T48"/>
+    <mergeCell ref="Q53:Q54"/>
+    <mergeCell ref="R53:R54"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="J53:P54"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="Q47:Q48"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="Q12:R13"/>
+    <mergeCell ref="S12:S14"/>
+    <mergeCell ref="B12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="T12:T14"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B10:D11"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="E9:P10"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="N55:R55"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="Q49:Q50"/>
+    <mergeCell ref="R49:R50"/>
+    <mergeCell ref="S49:S50"/>
+    <mergeCell ref="T49:T50"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="T29:T30"/>
     <mergeCell ref="S45:S46"/>
     <mergeCell ref="T45:T46"/>
     <mergeCell ref="Q43:Q44"/>
@@ -6492,111 +6603,6 @@
     <mergeCell ref="T35:T36"/>
     <mergeCell ref="T27:T28"/>
     <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="Z12:Z13"/>
-    <mergeCell ref="W11:AA11"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="N55:R55"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="Q49:Q50"/>
-    <mergeCell ref="R49:R50"/>
-    <mergeCell ref="S49:S50"/>
-    <mergeCell ref="T49:T50"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B10:D11"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="E9:P10"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="Y12:Y13"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="Q12:R13"/>
-    <mergeCell ref="S12:S14"/>
-    <mergeCell ref="B12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="T12:T14"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="T47:T48"/>
-    <mergeCell ref="Q53:Q54"/>
-    <mergeCell ref="R53:R54"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="J53:P54"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="R45:R46"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="Q47:Q48"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="S29:S30"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6608,28 +6614,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F73E104-985C-4BC0-B1FE-3BA893F14D77}">
   <dimension ref="B4:AK54"/>
-  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="5.69921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.75" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22.625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="183.625" style="30" customWidth="1"/>
-    <col min="4" max="4" width="29.25" style="30" customWidth="1"/>
-    <col min="5" max="8" width="54.125" style="30" customWidth="1"/>
-    <col min="9" max="14" width="49.75" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="49.75" style="29" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="49.75" style="29" customWidth="1"/>
-    <col min="18" max="18" width="49.75" style="36" customWidth="1"/>
-    <col min="19" max="19" width="27.375" style="29" customWidth="1"/>
-    <col min="20" max="20" width="27.375" style="127" customWidth="1"/>
+    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
+    <col min="2" max="2" width="22.59765625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="183.59765625" style="30" customWidth="1"/>
+    <col min="4" max="4" width="29.19921875" style="30" customWidth="1"/>
+    <col min="5" max="8" width="54.09765625" style="30" customWidth="1"/>
+    <col min="9" max="14" width="49.69921875" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="49.69921875" style="29" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="49.69921875" style="29" customWidth="1"/>
+    <col min="18" max="18" width="49.69921875" style="36" customWidth="1"/>
+    <col min="19" max="19" width="27.3984375" style="29" customWidth="1"/>
+    <col min="20" max="20" width="27.3984375" style="127" customWidth="1"/>
     <col min="21" max="21" width="9.5" style="67" customWidth="1"/>
-    <col min="22" max="25" width="35.875" style="67" customWidth="1"/>
-    <col min="26" max="26" width="35.875" style="30" customWidth="1"/>
-    <col min="27" max="36" width="5.75" style="30"/>
-    <col min="37" max="37" width="10.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="5.75" style="30"/>
+    <col min="22" max="25" width="35.8984375" style="67" customWidth="1"/>
+    <col min="26" max="26" width="35.8984375" style="30" customWidth="1"/>
+    <col min="27" max="36" width="5.69921875" style="30"/>
+    <col min="37" max="37" width="10.09765625" style="30" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="5.69921875" style="30"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:37" ht="31.9" customHeight="1">
+    <row r="4" spans="2:37" ht="31.95" customHeight="1">
       <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -6640,8 +6646,8 @@
       <c r="I4" s="37"/>
       <c r="J4" s="28"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="298"/>
-      <c r="M4" s="298"/>
+      <c r="L4" s="287"/>
+      <c r="M4" s="287"/>
       <c r="N4" s="54"/>
       <c r="O4" s="55"/>
       <c r="P4" s="55"/>
@@ -6671,157 +6677,157 @@
       <c r="M7" s="49"/>
     </row>
     <row r="9" spans="2:37" ht="15" customHeight="1" thickBot="1"/>
-    <row r="10" spans="2:37" ht="71.45" customHeight="1" thickBot="1">
-      <c r="B10" s="347" t="s">
+    <row r="10" spans="2:37" ht="71.400000000000006" customHeight="1" thickBot="1">
+      <c r="B10" s="367" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="347"/>
-      <c r="D10" s="347"/>
-      <c r="E10" s="349" t="s">
+      <c r="C10" s="367"/>
+      <c r="D10" s="367"/>
+      <c r="E10" s="369" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="350"/>
-      <c r="G10" s="350"/>
-      <c r="H10" s="350"/>
-      <c r="I10" s="350"/>
-      <c r="J10" s="350"/>
-      <c r="K10" s="350"/>
-      <c r="L10" s="350"/>
-      <c r="M10" s="350"/>
-      <c r="N10" s="350"/>
-      <c r="O10" s="350"/>
-      <c r="P10" s="350"/>
-      <c r="Q10" s="350"/>
-      <c r="R10" s="351"/>
+      <c r="F10" s="370"/>
+      <c r="G10" s="370"/>
+      <c r="H10" s="370"/>
+      <c r="I10" s="370"/>
+      <c r="J10" s="370"/>
+      <c r="K10" s="370"/>
+      <c r="L10" s="370"/>
+      <c r="M10" s="370"/>
+      <c r="N10" s="370"/>
+      <c r="O10" s="370"/>
+      <c r="P10" s="370"/>
+      <c r="Q10" s="370"/>
+      <c r="R10" s="371"/>
       <c r="U10" s="29"/>
       <c r="Z10" s="67"/>
       <c r="AA10" s="35"/>
     </row>
     <row r="11" spans="2:37" ht="3" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="348"/>
-      <c r="C11" s="348"/>
-      <c r="D11" s="348"/>
-      <c r="E11" s="352"/>
-      <c r="F11" s="353"/>
-      <c r="G11" s="353"/>
-      <c r="H11" s="353"/>
-      <c r="I11" s="353"/>
-      <c r="J11" s="353"/>
-      <c r="K11" s="353"/>
-      <c r="L11" s="353"/>
-      <c r="M11" s="353"/>
-      <c r="N11" s="353"/>
-      <c r="O11" s="353"/>
-      <c r="P11" s="353"/>
-      <c r="Q11" s="353"/>
-      <c r="R11" s="354"/>
+      <c r="B11" s="368"/>
+      <c r="C11" s="368"/>
+      <c r="D11" s="368"/>
+      <c r="E11" s="372"/>
+      <c r="F11" s="373"/>
+      <c r="G11" s="373"/>
+      <c r="H11" s="373"/>
+      <c r="I11" s="373"/>
+      <c r="J11" s="373"/>
+      <c r="K11" s="373"/>
+      <c r="L11" s="373"/>
+      <c r="M11" s="373"/>
+      <c r="N11" s="373"/>
+      <c r="O11" s="373"/>
+      <c r="P11" s="373"/>
+      <c r="Q11" s="373"/>
+      <c r="R11" s="374"/>
       <c r="S11" s="68"/>
       <c r="T11" s="128"/>
       <c r="U11" s="34"/>
-      <c r="W11" s="332"/>
-      <c r="X11" s="333"/>
-      <c r="Y11" s="333"/>
-      <c r="Z11" s="333"/>
-      <c r="AA11" s="334"/>
+      <c r="W11" s="266"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
+      <c r="AA11" s="268"/>
     </row>
     <row r="12" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B12" s="282" t="s">
+      <c r="B12" s="322" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="283"/>
-      <c r="D12" s="288" t="s">
+      <c r="C12" s="323"/>
+      <c r="D12" s="328" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="291" t="s">
+      <c r="E12" s="331" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="292"/>
-      <c r="G12" s="293" t="s">
+      <c r="F12" s="332"/>
+      <c r="G12" s="333" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="294"/>
-      <c r="I12" s="273" t="s">
+      <c r="H12" s="334"/>
+      <c r="I12" s="313" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="274"/>
-      <c r="K12" s="307" t="s">
+      <c r="J12" s="314"/>
+      <c r="K12" s="298" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="308"/>
-      <c r="M12" s="309"/>
-      <c r="N12" s="317" t="s">
+      <c r="L12" s="299"/>
+      <c r="M12" s="300"/>
+      <c r="N12" s="308" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="318"/>
+      <c r="O12" s="309"/>
       <c r="P12" s="139"/>
-      <c r="Q12" s="275" t="s">
+      <c r="Q12" s="315" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="276"/>
-      <c r="S12" s="279" t="s">
+      <c r="R12" s="316"/>
+      <c r="S12" s="319" t="s">
         <v>78</v>
       </c>
-      <c r="T12" s="295" t="s">
+      <c r="T12" s="335" t="s">
         <v>79</v>
       </c>
       <c r="U12" s="30"/>
-      <c r="V12" s="361" t="s">
+      <c r="V12" s="381" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="357" t="s">
+      <c r="W12" s="377" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="355" t="s">
+      <c r="X12" s="375" t="s">
         <v>85</v>
       </c>
-      <c r="Y12" s="357" t="s">
+      <c r="Y12" s="377" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="359" t="s">
+      <c r="Z12" s="379" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B13" s="284"/>
-      <c r="C13" s="285"/>
-      <c r="D13" s="289"/>
-      <c r="E13" s="291" t="s">
+      <c r="B13" s="324"/>
+      <c r="C13" s="325"/>
+      <c r="D13" s="329"/>
+      <c r="E13" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="292"/>
-      <c r="G13" s="293" t="s">
+      <c r="F13" s="332"/>
+      <c r="G13" s="333" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="294"/>
-      <c r="I13" s="273" t="s">
+      <c r="H13" s="334"/>
+      <c r="I13" s="313" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="274"/>
-      <c r="K13" s="307" t="s">
+      <c r="J13" s="314"/>
+      <c r="K13" s="298" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="308"/>
-      <c r="M13" s="309"/>
-      <c r="N13" s="317" t="s">
+      <c r="L13" s="299"/>
+      <c r="M13" s="300"/>
+      <c r="N13" s="308" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="318"/>
+      <c r="O13" s="309"/>
       <c r="P13" s="139"/>
-      <c r="Q13" s="277"/>
-      <c r="R13" s="278"/>
-      <c r="S13" s="280"/>
-      <c r="T13" s="296"/>
+      <c r="Q13" s="317"/>
+      <c r="R13" s="318"/>
+      <c r="S13" s="320"/>
+      <c r="T13" s="336"/>
       <c r="U13" s="30"/>
-      <c r="V13" s="362"/>
-      <c r="W13" s="358"/>
-      <c r="X13" s="356"/>
-      <c r="Y13" s="358"/>
-      <c r="Z13" s="360"/>
+      <c r="V13" s="382"/>
+      <c r="W13" s="378"/>
+      <c r="X13" s="376"/>
+      <c r="Y13" s="378"/>
+      <c r="Z13" s="380"/>
     </row>
     <row r="14" spans="2:37" ht="129" customHeight="1" thickBot="1">
-      <c r="B14" s="286"/>
-      <c r="C14" s="287"/>
-      <c r="D14" s="290"/>
+      <c r="B14" s="326"/>
+      <c r="C14" s="327"/>
+      <c r="D14" s="330"/>
       <c r="E14" s="130" t="s">
         <v>0</v>
       </c>
@@ -6864,8 +6870,8 @@
       <c r="R14" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="S14" s="281"/>
-      <c r="T14" s="297"/>
+      <c r="S14" s="321"/>
+      <c r="T14" s="337"/>
       <c r="U14" s="30"/>
       <c r="V14" s="91"/>
       <c r="W14" s="92"/>
@@ -6877,13 +6883,13 @@
       </c>
     </row>
     <row r="15" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B15" s="363">
+      <c r="B15" s="361">
         <v>1</v>
       </c>
       <c r="C15" s="161" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="371">
+      <c r="D15" s="365">
         <v>36</v>
       </c>
       <c r="E15" s="145">
@@ -6906,17 +6912,17 @@
       <c r="N15" s="146"/>
       <c r="O15" s="147"/>
       <c r="P15" s="147"/>
-      <c r="Q15" s="367">
+      <c r="Q15" s="352">
         <f>SUM(E15:P15)</f>
         <v>141</v>
       </c>
-      <c r="R15" s="369">
+      <c r="R15" s="354">
         <v>6</v>
       </c>
-      <c r="S15" s="249">
+      <c r="S15" s="250">
         <v>350</v>
       </c>
-      <c r="T15" s="251">
+      <c r="T15" s="252">
         <f>SUM(S15-Q15)</f>
         <v>209</v>
       </c>
@@ -6947,11 +6953,11 @@
       </c>
     </row>
     <row r="16" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B16" s="364"/>
+      <c r="B16" s="362"/>
       <c r="C16" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="372"/>
+      <c r="D16" s="366"/>
       <c r="E16" s="148" t="str">
         <f t="shared" ref="E16:P16" si="1">IF(E15=0, "", IF(MOD(E15, $D$15) = 0, E15 / $D$15, IF(INT(E15 / $D$15) = 0, MOD(E15, $D$15) &amp; " P", INT(E15 / $D$15) &amp; " + " &amp; MOD(E15, $D$15) &amp; " P")))</f>
         <v>18 P</v>
@@ -7000,10 +7006,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="368"/>
-      <c r="R16" s="370"/>
-      <c r="S16" s="250"/>
-      <c r="T16" s="252"/>
+      <c r="Q16" s="353"/>
+      <c r="R16" s="355"/>
+      <c r="S16" s="251"/>
+      <c r="T16" s="253"/>
       <c r="U16" s="30"/>
       <c r="V16" s="99"/>
       <c r="W16" s="100"/>
@@ -7015,13 +7021,13 @@
       </c>
     </row>
     <row r="17" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B17" s="363">
+      <c r="B17" s="361">
         <v>2</v>
       </c>
       <c r="C17" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="365">
+      <c r="D17" s="363">
         <v>32</v>
       </c>
       <c r="E17" s="145">
@@ -7044,17 +7050,17 @@
       <c r="N17" s="146"/>
       <c r="O17" s="147"/>
       <c r="P17" s="147"/>
-      <c r="Q17" s="367">
+      <c r="Q17" s="352">
         <f>SUM(E17:P17)</f>
         <v>298</v>
       </c>
-      <c r="R17" s="369">
+      <c r="R17" s="354">
         <v>12</v>
       </c>
-      <c r="S17" s="249">
+      <c r="S17" s="250">
         <v>790</v>
       </c>
-      <c r="T17" s="251">
+      <c r="T17" s="252">
         <f>SUM(S17-Q17)</f>
         <v>492</v>
       </c>
@@ -7085,11 +7091,11 @@
       </c>
     </row>
     <row r="18" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B18" s="364"/>
+      <c r="B18" s="362"/>
       <c r="C18" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="366"/>
+      <c r="D18" s="364"/>
       <c r="E18" s="148" t="str">
         <f t="shared" ref="E18:P18" si="3">IF(E17=0, "", IF(MOD(E17, $D$17) = 0, E17 / $D$17, IF(INT(E17 / $D$17) = 0, MOD(E17, $D$17) &amp; " P", INT(E17 / $D$17) &amp; " + " &amp; MOD(E17, $D$17) &amp; " P")))</f>
         <v>1 + 3 P</v>
@@ -7138,10 +7144,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="368"/>
-      <c r="R18" s="370"/>
-      <c r="S18" s="250"/>
-      <c r="T18" s="252"/>
+      <c r="Q18" s="353"/>
+      <c r="R18" s="355"/>
+      <c r="S18" s="251"/>
+      <c r="T18" s="253"/>
       <c r="U18" s="30"/>
       <c r="V18" s="99"/>
       <c r="W18" s="100"/>
@@ -7153,13 +7159,13 @@
       </c>
     </row>
     <row r="19" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B19" s="363">
+      <c r="B19" s="361">
         <v>3</v>
       </c>
       <c r="C19" s="163" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="365">
+      <c r="D19" s="363">
         <v>36</v>
       </c>
       <c r="E19" s="150">
@@ -7182,17 +7188,17 @@
       <c r="N19" s="151"/>
       <c r="O19" s="153"/>
       <c r="P19" s="153"/>
-      <c r="Q19" s="367">
+      <c r="Q19" s="352">
         <f>SUM(E19:P19)</f>
         <v>73</v>
       </c>
-      <c r="R19" s="369">
+      <c r="R19" s="354">
         <v>5</v>
       </c>
-      <c r="S19" s="249">
+      <c r="S19" s="250">
         <v>240</v>
       </c>
-      <c r="T19" s="251">
+      <c r="T19" s="252">
         <f>SUM(S19-Q19)</f>
         <v>167</v>
       </c>
@@ -7223,11 +7229,11 @@
       </c>
     </row>
     <row r="20" spans="2:37" ht="72" customHeight="1" thickBot="1">
-      <c r="B20" s="364"/>
+      <c r="B20" s="362"/>
       <c r="C20" s="165" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="366"/>
+      <c r="D20" s="364"/>
       <c r="E20" s="148" t="str">
         <f t="shared" ref="E20:P20" si="5">IF(E19=0, "", IF(MOD(E19, $D$19) = 0, E19/ $D$19, IF(INT(E19 / $D$19) = 0, MOD(E19, $D$19) &amp; " P", INT(E19 / $D$19) &amp; " + " &amp; MOD(E19, $D$19) &amp; " P")))</f>
         <v>3 P</v>
@@ -7276,10 +7282,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="368"/>
-      <c r="R20" s="370"/>
-      <c r="S20" s="250"/>
-      <c r="T20" s="252"/>
+      <c r="Q20" s="353"/>
+      <c r="R20" s="355"/>
+      <c r="S20" s="251"/>
+      <c r="T20" s="253"/>
       <c r="U20" s="30"/>
       <c r="V20" s="99"/>
       <c r="W20" s="100"/>
@@ -7291,13 +7297,13 @@
       </c>
     </row>
     <row r="21" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B21" s="363">
+      <c r="B21" s="361">
         <v>4</v>
       </c>
       <c r="C21" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="365">
+      <c r="D21" s="363">
         <v>32</v>
       </c>
       <c r="E21" s="145">
@@ -7320,17 +7326,17 @@
       <c r="N21" s="146"/>
       <c r="O21" s="147"/>
       <c r="P21" s="147"/>
-      <c r="Q21" s="367">
+      <c r="Q21" s="352">
         <f>SUM(E21:P21)</f>
         <v>699</v>
       </c>
-      <c r="R21" s="369">
+      <c r="R21" s="354">
         <v>24</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="250">
         <v>1272</v>
       </c>
-      <c r="T21" s="251">
+      <c r="T21" s="252">
         <f>SUM(S21-Q21)</f>
         <v>573</v>
       </c>
@@ -7361,11 +7367,11 @@
       </c>
     </row>
     <row r="22" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B22" s="364"/>
+      <c r="B22" s="362"/>
       <c r="C22" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="366"/>
+      <c r="D22" s="364"/>
       <c r="E22" s="148" t="str">
         <f t="shared" ref="E22:P22" si="7">IF(E21=0, "", IF(MOD(E21, $D$21) = 0, E21/ $D$21, IF(INT(E21 / $D$21) = 0, MOD(E21, $D$21) &amp; " P", INT(E21 / $D$21) &amp; " + " &amp; MOD(E21, $D$21) &amp; " P")))</f>
         <v>4 + 3 P</v>
@@ -7414,10 +7420,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q22" s="368"/>
-      <c r="R22" s="370"/>
-      <c r="S22" s="250"/>
-      <c r="T22" s="252"/>
+      <c r="Q22" s="353"/>
+      <c r="R22" s="355"/>
+      <c r="S22" s="251"/>
+      <c r="T22" s="253"/>
       <c r="U22" s="30"/>
       <c r="V22" s="99"/>
       <c r="W22" s="100"/>
@@ -7435,7 +7441,7 @@
       <c r="C23" s="166" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="373">
+      <c r="D23" s="359">
         <v>18</v>
       </c>
       <c r="E23" s="154">
@@ -7458,17 +7464,17 @@
       <c r="N23" s="155"/>
       <c r="O23" s="157"/>
       <c r="P23" s="157"/>
-      <c r="Q23" s="367">
+      <c r="Q23" s="352">
         <f>SUM(E23:P23)</f>
         <v>34</v>
       </c>
-      <c r="R23" s="369">
+      <c r="R23" s="354">
         <v>4</v>
       </c>
-      <c r="S23" s="249">
+      <c r="S23" s="250">
         <v>100</v>
       </c>
-      <c r="T23" s="251">
+      <c r="T23" s="252">
         <f>SUM(S23-Q23)</f>
         <v>66</v>
       </c>
@@ -7503,7 +7509,7 @@
       <c r="C24" s="164" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="374"/>
+      <c r="D24" s="360"/>
       <c r="E24" s="158" t="str">
         <f t="shared" ref="E24:P24" si="9">IF(E23=0, "", IF(MOD(E23, $D$23) = 0, E23/ $D$23, IF(INT(E23 / $D$23) = 0, MOD(E23, $D$23) &amp; " P", INT(E23 / $D$23) &amp; " + " &amp; MOD(E23, $D$23) &amp; " P")))</f>
         <v>3 P</v>
@@ -7552,10 +7558,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q24" s="368"/>
-      <c r="R24" s="370"/>
-      <c r="S24" s="250"/>
-      <c r="T24" s="252"/>
+      <c r="Q24" s="353"/>
+      <c r="R24" s="355"/>
+      <c r="S24" s="251"/>
+      <c r="T24" s="253"/>
       <c r="U24" s="30"/>
       <c r="V24" s="99"/>
       <c r="W24" s="100"/>
@@ -7573,7 +7579,7 @@
       <c r="C25" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="375">
+      <c r="D25" s="350">
         <v>36</v>
       </c>
       <c r="E25" s="145">
@@ -7596,17 +7602,17 @@
       <c r="N25" s="146"/>
       <c r="O25" s="147"/>
       <c r="P25" s="147"/>
-      <c r="Q25" s="367">
+      <c r="Q25" s="352">
         <f>SUM(E25:P25)</f>
         <v>192</v>
       </c>
-      <c r="R25" s="369">
+      <c r="R25" s="354">
         <v>8</v>
       </c>
-      <c r="S25" s="249">
+      <c r="S25" s="250">
         <v>650</v>
       </c>
-      <c r="T25" s="251">
+      <c r="T25" s="252">
         <f>SUM(S25-Q25)</f>
         <v>458</v>
       </c>
@@ -7641,7 +7647,7 @@
       <c r="C26" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="376"/>
+      <c r="D26" s="351"/>
       <c r="E26" s="148" t="str">
         <f t="shared" ref="E26:P26" si="11">IF(E25=0, "", IF(MOD(E25, $D$25) = 0, E25/ $D$25, IF(INT(E25 / $D$25) = 0, MOD(E25, $D$25) &amp; " P", INT(E25 / $D$25) &amp; " + " &amp; MOD(E25, $D$25) &amp; " P")))</f>
         <v>10 P</v>
@@ -7690,10 +7696,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q26" s="368"/>
-      <c r="R26" s="370"/>
-      <c r="S26" s="250"/>
-      <c r="T26" s="252"/>
+      <c r="Q26" s="353"/>
+      <c r="R26" s="355"/>
+      <c r="S26" s="251"/>
+      <c r="T26" s="253"/>
       <c r="U26" s="30"/>
       <c r="V26" s="99"/>
       <c r="W26" s="100"/>
@@ -7711,7 +7717,7 @@
       <c r="C27" s="163" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="375">
+      <c r="D27" s="350">
         <v>20</v>
       </c>
       <c r="E27" s="145">
@@ -7734,17 +7740,17 @@
       <c r="N27" s="146"/>
       <c r="O27" s="147"/>
       <c r="P27" s="147"/>
-      <c r="Q27" s="367">
+      <c r="Q27" s="352">
         <f>SUM(E27:P27)</f>
         <v>49</v>
       </c>
-      <c r="R27" s="369">
+      <c r="R27" s="354">
         <v>5</v>
       </c>
-      <c r="S27" s="249">
+      <c r="S27" s="250">
         <v>140</v>
       </c>
-      <c r="T27" s="251">
+      <c r="T27" s="252">
         <f>SUM(S27-Q27)</f>
         <v>91</v>
       </c>
@@ -7779,7 +7785,7 @@
       <c r="C28" s="165" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="376"/>
+      <c r="D28" s="351"/>
       <c r="E28" s="148" t="str">
         <f t="shared" ref="E28:P28" si="13">IF(E27=0, "", IF(MOD(E27, $D$27) = 0, E27/ $D$27, IF(INT(E27 / $D$27) = 0, MOD(E27, $D$27) &amp; " P", INT(E27 / $D$27) &amp; " + " &amp; MOD(E27, $D$27) &amp; " P")))</f>
         <v>7 P</v>
@@ -7828,10 +7834,10 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q28" s="368"/>
-      <c r="R28" s="370"/>
-      <c r="S28" s="250"/>
-      <c r="T28" s="252"/>
+      <c r="Q28" s="353"/>
+      <c r="R28" s="355"/>
+      <c r="S28" s="251"/>
+      <c r="T28" s="253"/>
       <c r="U28" s="30"/>
       <c r="V28" s="95"/>
       <c r="W28" s="100"/>
@@ -7849,7 +7855,7 @@
       <c r="C29" s="167" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="375">
+      <c r="D29" s="350">
         <v>15</v>
       </c>
       <c r="E29" s="150">
@@ -7872,17 +7878,17 @@
       <c r="N29" s="151"/>
       <c r="O29" s="153"/>
       <c r="P29" s="153"/>
-      <c r="Q29" s="367">
+      <c r="Q29" s="352">
         <f>SUM(E29:P29)</f>
         <v>94</v>
       </c>
-      <c r="R29" s="369">
+      <c r="R29" s="354">
         <v>8</v>
       </c>
-      <c r="S29" s="249">
+      <c r="S29" s="250">
         <v>240</v>
       </c>
-      <c r="T29" s="251">
+      <c r="T29" s="252">
         <f>SUM(S29-Q29)</f>
         <v>146</v>
       </c>
@@ -7917,7 +7923,7 @@
       <c r="C30" s="164" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="376"/>
+      <c r="D30" s="351"/>
       <c r="E30" s="148" t="str">
         <f t="shared" ref="E30:P30" si="14">IF(E29=0, "", IF(MOD(E29, $D$29) = 0, E29/ $D$29, IF(INT(E29 / $D$29) = 0, MOD(E29, $D$29) &amp; " P", INT(E29 / $D$29) &amp; " + " &amp; MOD(E29, $D$29) &amp; " P")))</f>
         <v>10 P</v>
@@ -7966,10 +7972,10 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q30" s="368"/>
-      <c r="R30" s="370"/>
-      <c r="S30" s="250"/>
-      <c r="T30" s="252"/>
+      <c r="Q30" s="353"/>
+      <c r="R30" s="355"/>
+      <c r="S30" s="251"/>
+      <c r="T30" s="253"/>
       <c r="U30" s="30"/>
       <c r="V30" s="95"/>
       <c r="W30" s="100"/>
@@ -7987,7 +7993,7 @@
       <c r="C31" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="375">
+      <c r="D31" s="350">
         <v>45</v>
       </c>
       <c r="E31" s="150">
@@ -8010,17 +8016,17 @@
       <c r="N31" s="151"/>
       <c r="O31" s="153"/>
       <c r="P31" s="153"/>
-      <c r="Q31" s="367">
+      <c r="Q31" s="352">
         <f>SUM(E31:P31)</f>
         <v>9</v>
       </c>
-      <c r="R31" s="377">
+      <c r="R31" s="358">
         <v>3</v>
       </c>
-      <c r="S31" s="249">
+      <c r="S31" s="250">
         <v>70</v>
       </c>
-      <c r="T31" s="251">
+      <c r="T31" s="252">
         <f>SUM(S31-Q31)</f>
         <v>61</v>
       </c>
@@ -8055,7 +8061,7 @@
       <c r="C32" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="376"/>
+      <c r="D32" s="351"/>
       <c r="E32" s="148" t="str">
         <f t="shared" ref="E32:P32" si="16">IF(E31=0, "", IF(MOD(E31, $D$31) = 0, E31/ $D$31, IF(INT(E31 / $D$31) = 0, MOD(E31, $D$31) &amp; " P", INT(E31 / $D$31) &amp; " + " &amp; MOD(E31, $D$31) &amp; " P")))</f>
         <v>1 P</v>
@@ -8104,10 +8110,10 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q32" s="368"/>
-      <c r="R32" s="370"/>
-      <c r="S32" s="250"/>
-      <c r="T32" s="252"/>
+      <c r="Q32" s="353"/>
+      <c r="R32" s="355"/>
+      <c r="S32" s="251"/>
+      <c r="T32" s="253"/>
       <c r="U32" s="30"/>
       <c r="V32" s="95"/>
       <c r="W32" s="100"/>
@@ -8125,7 +8131,7 @@
       <c r="C33" s="167" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="375">
+      <c r="D33" s="350">
         <v>15</v>
       </c>
       <c r="E33" s="150">
@@ -8148,17 +8154,17 @@
       <c r="N33" s="151"/>
       <c r="O33" s="153"/>
       <c r="P33" s="153"/>
-      <c r="Q33" s="367">
+      <c r="Q33" s="352">
         <f>SUM(E33:P33)</f>
         <v>134</v>
       </c>
-      <c r="R33" s="377">
+      <c r="R33" s="358">
         <v>11</v>
       </c>
-      <c r="S33" s="249">
+      <c r="S33" s="250">
         <v>320</v>
       </c>
-      <c r="T33" s="251">
+      <c r="T33" s="252">
         <f t="shared" ref="T33" si="17">SUM(S33-Q33)</f>
         <v>186</v>
       </c>
@@ -8193,7 +8199,7 @@
       <c r="C34" s="165" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="376"/>
+      <c r="D34" s="351"/>
       <c r="E34" s="148" t="str">
         <f>IF(E33=0, "", IF(MOD(E33, $D$33) = 0, E33/ $D$33, IF(INT(E33 / $D$33) = 0, MOD(E33, $D$33) &amp; " P", INT(E33 / $D$33) &amp; " + " &amp; MOD(E33, $D$33) &amp; " P")))</f>
         <v>1 + 8 P</v>
@@ -8242,10 +8248,10 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q34" s="368"/>
-      <c r="R34" s="370"/>
-      <c r="S34" s="250"/>
-      <c r="T34" s="252"/>
+      <c r="Q34" s="353"/>
+      <c r="R34" s="355"/>
+      <c r="S34" s="251"/>
+      <c r="T34" s="253"/>
       <c r="U34" s="30"/>
       <c r="V34" s="95"/>
       <c r="W34" s="100"/>
@@ -8263,7 +8269,7 @@
       <c r="C35" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="375">
+      <c r="D35" s="350">
         <v>15</v>
       </c>
       <c r="E35" s="159">
@@ -8286,17 +8292,17 @@
       <c r="N35" s="152"/>
       <c r="O35" s="160"/>
       <c r="P35" s="160"/>
-      <c r="Q35" s="367">
+      <c r="Q35" s="352">
         <f>SUM(E35:P35)</f>
         <v>82</v>
       </c>
-      <c r="R35" s="369">
+      <c r="R35" s="354">
         <v>7</v>
       </c>
-      <c r="S35" s="249">
+      <c r="S35" s="250">
         <v>190</v>
       </c>
-      <c r="T35" s="378">
+      <c r="T35" s="356">
         <f t="shared" ref="T35" si="19">SUM(S35-Q35)</f>
         <v>108</v>
       </c>
@@ -8331,7 +8337,7 @@
       <c r="C36" s="165" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="376"/>
+      <c r="D36" s="351"/>
       <c r="E36" s="148" t="str">
         <f>IF(E35=0, "", IF(MOD(E35, $D$35) = 0, E35/ $D$35, IF(INT(E35 / $D$35) = 0, MOD(E35, $D$35) &amp; " P", INT(E35 / $D$35) &amp; " + " &amp; MOD(E35, $D$35) &amp; " P")))</f>
         <v>9 P</v>
@@ -8380,10 +8386,10 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q36" s="368"/>
-      <c r="R36" s="370"/>
-      <c r="S36" s="250"/>
-      <c r="T36" s="379"/>
+      <c r="Q36" s="353"/>
+      <c r="R36" s="355"/>
+      <c r="S36" s="251"/>
+      <c r="T36" s="357"/>
       <c r="U36" s="30"/>
       <c r="V36" s="95"/>
       <c r="W36" s="100"/>
@@ -8398,7 +8404,7 @@
       <c r="C37" s="167" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="375">
+      <c r="D37" s="350">
         <v>27</v>
       </c>
       <c r="E37" s="145">
@@ -8421,17 +8427,17 @@
       <c r="N37" s="145"/>
       <c r="O37" s="145"/>
       <c r="P37" s="145"/>
-      <c r="Q37" s="367">
+      <c r="Q37" s="352">
         <f>SUM(E37:P37)</f>
         <v>192</v>
       </c>
-      <c r="R37" s="369">
+      <c r="R37" s="354">
         <v>9</v>
       </c>
-      <c r="S37" s="249">
+      <c r="S37" s="250">
         <v>440</v>
       </c>
-      <c r="T37" s="378">
+      <c r="T37" s="356">
         <f t="shared" ref="T37" si="21">SUM(S37-Q37)</f>
         <v>248</v>
       </c>
@@ -8466,7 +8472,7 @@
       <c r="C38" s="165" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="376"/>
+      <c r="D38" s="351"/>
       <c r="E38" s="148" t="str">
         <f>IF(E37=0, "", IF(MOD(E37, $D$37) = 0, E37/ $D$37, IF(INT(E37 / $D$37) = 0, MOD(E37, $D$37) &amp; " P", INT(E37 / $D$37) &amp; " + " &amp; MOD(E37, $D$37) &amp; " P")))</f>
         <v>1 + 2 P</v>
@@ -8515,10 +8521,10 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q38" s="368"/>
-      <c r="R38" s="370"/>
-      <c r="S38" s="250"/>
-      <c r="T38" s="379"/>
+      <c r="Q38" s="353"/>
+      <c r="R38" s="355"/>
+      <c r="S38" s="251"/>
+      <c r="T38" s="357"/>
       <c r="U38" s="30"/>
       <c r="V38" s="95"/>
       <c r="W38" s="100"/>
@@ -8533,7 +8539,7 @@
       <c r="C39" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="375">
+      <c r="D39" s="350">
         <v>20</v>
       </c>
       <c r="E39" s="145">
@@ -8556,17 +8562,17 @@
       <c r="N39" s="145"/>
       <c r="O39" s="145"/>
       <c r="P39" s="145"/>
-      <c r="Q39" s="367">
+      <c r="Q39" s="352">
         <f>SUM(E39:P39)</f>
         <v>213</v>
       </c>
-      <c r="R39" s="369">
+      <c r="R39" s="354">
         <v>12</v>
       </c>
-      <c r="S39" s="249">
+      <c r="S39" s="250">
         <v>450</v>
       </c>
-      <c r="T39" s="378">
+      <c r="T39" s="356">
         <f t="shared" ref="T39" si="23">SUM(S39-Q39)</f>
         <v>237</v>
       </c>
@@ -8601,7 +8607,7 @@
       <c r="C40" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="D40" s="376"/>
+      <c r="D40" s="351"/>
       <c r="E40" s="148" t="str">
         <f>IF(E39=0, "", IF(MOD(E39, $D$39) = 0, E39/ $D$39, IF(INT(E39 / $D$39) = 0, MOD(E39, $D$39) &amp; " P", INT(E39 / $D$39) &amp; " + " &amp; MOD(E39, $D$39) &amp; " P")))</f>
         <v>14 P</v>
@@ -8650,10 +8656,10 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="Q40" s="368"/>
-      <c r="R40" s="370"/>
-      <c r="S40" s="250"/>
-      <c r="T40" s="379"/>
+      <c r="Q40" s="353"/>
+      <c r="R40" s="355"/>
+      <c r="S40" s="251"/>
+      <c r="T40" s="357"/>
       <c r="U40" s="30"/>
       <c r="V40" s="95"/>
       <c r="W40" s="100"/>
@@ -8668,7 +8674,7 @@
       <c r="C41" s="166" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="375">
+      <c r="D41" s="350">
         <v>32</v>
       </c>
       <c r="E41" s="145">
@@ -8691,17 +8697,17 @@
       <c r="N41" s="145"/>
       <c r="O41" s="145"/>
       <c r="P41" s="145"/>
-      <c r="Q41" s="367">
+      <c r="Q41" s="352">
         <f>SUM(E41:P41)</f>
         <v>93</v>
       </c>
-      <c r="R41" s="369">
+      <c r="R41" s="354">
         <v>5</v>
       </c>
-      <c r="S41" s="249">
+      <c r="S41" s="250">
         <v>220</v>
       </c>
-      <c r="T41" s="251">
+      <c r="T41" s="252">
         <f t="shared" ref="T41" si="25">SUM(S41-Q41)</f>
         <v>127</v>
       </c>
@@ -8736,7 +8742,7 @@
       <c r="C42" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="D42" s="376"/>
+      <c r="D42" s="351"/>
       <c r="E42" s="148" t="str">
         <f>IF(E41=0, "", IF(MOD(E41, $D$41) = 0, E41/ $D$41, IF(INT(E41 / $D$41) = 0, MOD(E41, $D$41) &amp; " P", INT(E41 / $D$41) &amp; " + " &amp; MOD(E41, $D$41) &amp; " P")))</f>
         <v>7 P</v>
@@ -8785,10 +8791,10 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="Q42" s="368"/>
-      <c r="R42" s="370"/>
-      <c r="S42" s="250"/>
-      <c r="T42" s="252"/>
+      <c r="Q42" s="353"/>
+      <c r="R42" s="355"/>
+      <c r="S42" s="251"/>
+      <c r="T42" s="253"/>
       <c r="U42" s="30"/>
       <c r="V42" s="95"/>
       <c r="W42" s="100"/>
@@ -8803,7 +8809,7 @@
       <c r="C43" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="375">
+      <c r="D43" s="350">
         <v>15</v>
       </c>
       <c r="E43" s="145">
@@ -8826,17 +8832,17 @@
       <c r="N43" s="145"/>
       <c r="O43" s="145"/>
       <c r="P43" s="145"/>
-      <c r="Q43" s="367">
+      <c r="Q43" s="352">
         <f>SUM(E43:P43)</f>
         <v>40</v>
       </c>
-      <c r="R43" s="369">
+      <c r="R43" s="354">
         <v>5</v>
       </c>
-      <c r="S43" s="249">
+      <c r="S43" s="250">
         <v>100</v>
       </c>
-      <c r="T43" s="251">
+      <c r="T43" s="252">
         <f t="shared" ref="T43" si="27">SUM(S43-Q43)</f>
         <v>60</v>
       </c>
@@ -8871,7 +8877,7 @@
       <c r="C44" s="165" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="376"/>
+      <c r="D44" s="351"/>
       <c r="E44" s="148" t="str">
         <f>IF(E43=0, "", IF(MOD(E43, $D$43) = 0, E43/ $D$43, IF(INT(E43 / $D$43) = 0, MOD(E43, $D$43) &amp; " P", INT(E43 / $D$43) &amp; " + " &amp; MOD(E43, $D$43) &amp; " P")))</f>
         <v>5 P</v>
@@ -8920,10 +8926,10 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="Q44" s="368"/>
-      <c r="R44" s="370"/>
-      <c r="S44" s="250"/>
-      <c r="T44" s="252"/>
+      <c r="Q44" s="353"/>
+      <c r="R44" s="355"/>
+      <c r="S44" s="251"/>
+      <c r="T44" s="253"/>
       <c r="U44" s="30"/>
       <c r="V44" s="95"/>
       <c r="W44" s="100"/>
@@ -8932,11 +8938,11 @@
       <c r="Z44" s="102"/>
     </row>
     <row r="45" spans="2:37" ht="73.5" customHeight="1" thickBot="1">
-      <c r="B45" s="340" t="s">
+      <c r="B45" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="341"/>
-      <c r="D45" s="342"/>
+      <c r="C45" s="275"/>
+      <c r="D45" s="276"/>
       <c r="E45" s="84">
         <v>-22</v>
       </c>
@@ -8973,7 +8979,7 @@
       <c r="Y45" s="106"/>
       <c r="Z45" s="105"/>
     </row>
-    <row r="46" spans="2:37" ht="13.15" customHeight="1" thickBot="1">
+    <row r="46" spans="2:37" ht="13.2" customHeight="1" thickBot="1">
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -9001,92 +9007,92 @@
     <row r="47" spans="2:37" ht="105" hidden="1" customHeight="1" thickBot="1"/>
     <row r="48" spans="2:37" ht="37.5" hidden="1" customHeight="1" thickBot="1"/>
     <row r="49" spans="2:20" ht="48.75" hidden="1" customHeight="1" thickBot="1"/>
-    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.900000000000006" customHeight="1" thickBot="1">
-      <c r="B50" s="324" t="s">
+    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.95" customHeight="1" thickBot="1">
+      <c r="B50" s="281" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="325"/>
-      <c r="D50" s="324" t="s">
+      <c r="C50" s="282"/>
+      <c r="D50" s="281" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="325"/>
-      <c r="F50" s="324" t="s">
+      <c r="E50" s="282"/>
+      <c r="F50" s="281" t="s">
         <v>54</v>
       </c>
-      <c r="G50" s="325"/>
-      <c r="H50" s="324" t="s">
+      <c r="G50" s="282"/>
+      <c r="H50" s="281" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="325"/>
+      <c r="I50" s="282"/>
       <c r="J50" s="38"/>
-      <c r="M50" s="266" t="s">
+      <c r="M50" s="345" t="s">
         <v>88</v>
       </c>
-      <c r="N50" s="266"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="380">
+      <c r="N50" s="345"/>
+      <c r="O50" s="345"/>
+      <c r="P50" s="345"/>
+      <c r="Q50" s="348">
         <f>SUM(R45)</f>
         <v>124</v>
       </c>
-      <c r="R50" s="255" t="s">
+      <c r="R50" s="340" t="s">
         <v>89</v>
       </c>
       <c r="T50" s="36"/>
     </row>
-    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1">
-      <c r="B51" s="326" t="s">
+    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1">
+      <c r="B51" s="283" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="327"/>
-      <c r="D51" s="328"/>
-      <c r="E51" s="329"/>
-      <c r="F51" s="328"/>
-      <c r="G51" s="329"/>
-      <c r="H51" s="328"/>
-      <c r="I51" s="329"/>
+      <c r="C51" s="284"/>
+      <c r="D51" s="285"/>
+      <c r="E51" s="286"/>
+      <c r="F51" s="285"/>
+      <c r="G51" s="286"/>
+      <c r="H51" s="285"/>
+      <c r="I51" s="286"/>
       <c r="J51" s="38"/>
-      <c r="M51" s="266"/>
-      <c r="N51" s="266"/>
-      <c r="O51" s="266"/>
-      <c r="P51" s="266"/>
-      <c r="Q51" s="381"/>
-      <c r="R51" s="255"/>
+      <c r="M51" s="345"/>
+      <c r="N51" s="345"/>
+      <c r="O51" s="345"/>
+      <c r="P51" s="345"/>
+      <c r="Q51" s="349"/>
+      <c r="R51" s="340"/>
       <c r="T51" s="36"/>
     </row>
-    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
-      <c r="B52" s="335" t="s">
+    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
+      <c r="B52" s="269" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="336"/>
-      <c r="D52" s="337"/>
-      <c r="E52" s="338"/>
-      <c r="F52" s="337"/>
-      <c r="G52" s="338"/>
-      <c r="H52" s="337"/>
-      <c r="I52" s="338"/>
+      <c r="C52" s="270"/>
+      <c r="D52" s="271"/>
+      <c r="E52" s="272"/>
+      <c r="F52" s="271"/>
+      <c r="G52" s="272"/>
+      <c r="H52" s="271"/>
+      <c r="I52" s="272"/>
       <c r="J52" s="38"/>
       <c r="M52" s="67"/>
-      <c r="N52" s="339" t="s">
+      <c r="N52" s="273" t="s">
         <v>73</v>
       </c>
-      <c r="O52" s="339"/>
-      <c r="P52" s="339"/>
-      <c r="Q52" s="339"/>
-      <c r="R52" s="339"/>
+      <c r="O52" s="273"/>
+      <c r="P52" s="273"/>
+      <c r="Q52" s="273"/>
+      <c r="R52" s="273"/>
       <c r="T52" s="36"/>
     </row>
-    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
-      <c r="B53" s="320" t="s">
+    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
+      <c r="B53" s="277" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="321"/>
-      <c r="D53" s="322"/>
-      <c r="E53" s="323"/>
-      <c r="F53" s="322"/>
-      <c r="G53" s="323"/>
-      <c r="H53" s="322"/>
-      <c r="I53" s="323"/>
+      <c r="C53" s="278"/>
+      <c r="D53" s="279"/>
+      <c r="E53" s="280"/>
+      <c r="F53" s="279"/>
+      <c r="G53" s="280"/>
+      <c r="H53" s="279"/>
+      <c r="I53" s="280"/>
       <c r="J53" s="38"/>
       <c r="K53" s="53" t="s">
         <v>77</v>
@@ -9108,7 +9114,7 @@
       </c>
       <c r="T53" s="36"/>
     </row>
-    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.150000000000006" customHeight="1" thickBot="1">
+    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.2" customHeight="1" thickBot="1">
       <c r="B54" s="38"/>
       <c r="C54" s="38"/>
       <c r="D54" s="89"/>
@@ -9130,106 +9136,6 @@
     </row>
   </sheetData>
   <mergeCells count="124">
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="N52:R52"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="M50:P51"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="S43:S44"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:S36"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="T33:T34"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="E10:R11"/>
@@ -9254,6 +9160,106 @@
     <mergeCell ref="T12:T14"/>
     <mergeCell ref="V12:V13"/>
     <mergeCell ref="W12:W13"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="N52:R52"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="M50:P51"/>
+    <mergeCell ref="Q50:Q51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0"/>
@@ -9264,29 +9270,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96D3011-5F30-4B22-86C3-114347F44C10}">
   <dimension ref="B4:AK54"/>
-  <sheetFormatPr defaultColWidth="5.75" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="5.69921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.75" style="30" customWidth="1"/>
-    <col min="2" max="2" width="22.625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="174.875" style="30" customWidth="1"/>
-    <col min="4" max="4" width="28.625" style="30" customWidth="1"/>
-    <col min="5" max="8" width="34.75" style="30" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="47.875" style="30" customWidth="1"/>
-    <col min="15" max="15" width="47.875" style="29" customWidth="1"/>
-    <col min="16" max="16" width="47.875" style="29" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="47.875" style="29" customWidth="1"/>
-    <col min="18" max="18" width="47.875" style="36" customWidth="1"/>
-    <col min="19" max="19" width="27.375" style="29" customWidth="1"/>
-    <col min="20" max="20" width="27.375" style="127" customWidth="1"/>
+    <col min="1" max="1" width="5.69921875" style="30" customWidth="1"/>
+    <col min="2" max="2" width="22.59765625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="174.8984375" style="30" customWidth="1"/>
+    <col min="4" max="4" width="28.59765625" style="30" customWidth="1"/>
+    <col min="5" max="8" width="34.69921875" style="30" hidden="1" customWidth="1"/>
+    <col min="9" max="14" width="47.8984375" style="30" customWidth="1"/>
+    <col min="15" max="15" width="47.8984375" style="29" customWidth="1"/>
+    <col min="16" max="16" width="47.8984375" style="29" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="47.8984375" style="29" customWidth="1"/>
+    <col min="18" max="18" width="47.8984375" style="36" customWidth="1"/>
+    <col min="19" max="19" width="27.3984375" style="29" customWidth="1"/>
+    <col min="20" max="20" width="27.3984375" style="127" customWidth="1"/>
     <col min="21" max="21" width="9.5" style="67" customWidth="1"/>
-    <col min="22" max="25" width="35.875" style="67" customWidth="1"/>
-    <col min="26" max="26" width="35.875" style="30" customWidth="1"/>
-    <col min="27" max="36" width="5.75" style="30"/>
-    <col min="37" max="37" width="10.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="5.75" style="30"/>
+    <col min="22" max="25" width="35.8984375" style="67" customWidth="1"/>
+    <col min="26" max="26" width="35.8984375" style="30" customWidth="1"/>
+    <col min="27" max="36" width="5.69921875" style="30"/>
+    <col min="37" max="37" width="10.09765625" style="30" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="5.69921875" style="30"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:37" ht="31.9" customHeight="1">
+    <row r="4" spans="2:37" ht="31.95" customHeight="1">
       <c r="B4" s="27"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
@@ -9297,8 +9303,8 @@
       <c r="I4" s="37"/>
       <c r="J4" s="28"/>
       <c r="K4" s="49"/>
-      <c r="L4" s="298"/>
-      <c r="M4" s="298"/>
+      <c r="L4" s="287"/>
+      <c r="M4" s="287"/>
       <c r="N4" s="54"/>
       <c r="O4" s="55"/>
       <c r="P4" s="55"/>
@@ -9328,157 +9334,157 @@
       <c r="M7" s="49"/>
     </row>
     <row r="9" spans="2:37" ht="15" customHeight="1" thickBot="1"/>
-    <row r="10" spans="2:37" ht="71.45" customHeight="1" thickBot="1">
-      <c r="B10" s="347" t="s">
+    <row r="10" spans="2:37" ht="71.400000000000006" customHeight="1" thickBot="1">
+      <c r="B10" s="367" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="347"/>
-      <c r="D10" s="347"/>
-      <c r="E10" s="349" t="s">
+      <c r="C10" s="367"/>
+      <c r="D10" s="367"/>
+      <c r="E10" s="369" t="s">
         <v>137</v>
       </c>
-      <c r="F10" s="350"/>
-      <c r="G10" s="350"/>
-      <c r="H10" s="350"/>
-      <c r="I10" s="350"/>
-      <c r="J10" s="350"/>
-      <c r="K10" s="350"/>
-      <c r="L10" s="350"/>
-      <c r="M10" s="350"/>
-      <c r="N10" s="350"/>
-      <c r="O10" s="350"/>
-      <c r="P10" s="350"/>
-      <c r="Q10" s="350"/>
-      <c r="R10" s="351"/>
+      <c r="F10" s="370"/>
+      <c r="G10" s="370"/>
+      <c r="H10" s="370"/>
+      <c r="I10" s="370"/>
+      <c r="J10" s="370"/>
+      <c r="K10" s="370"/>
+      <c r="L10" s="370"/>
+      <c r="M10" s="370"/>
+      <c r="N10" s="370"/>
+      <c r="O10" s="370"/>
+      <c r="P10" s="370"/>
+      <c r="Q10" s="370"/>
+      <c r="R10" s="371"/>
       <c r="U10" s="29"/>
       <c r="Z10" s="67"/>
       <c r="AA10" s="35"/>
     </row>
     <row r="11" spans="2:37" ht="3" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="348"/>
-      <c r="C11" s="348"/>
-      <c r="D11" s="348"/>
-      <c r="E11" s="352"/>
-      <c r="F11" s="353"/>
-      <c r="G11" s="353"/>
-      <c r="H11" s="353"/>
-      <c r="I11" s="353"/>
-      <c r="J11" s="353"/>
-      <c r="K11" s="353"/>
-      <c r="L11" s="353"/>
-      <c r="M11" s="353"/>
-      <c r="N11" s="353"/>
-      <c r="O11" s="353"/>
-      <c r="P11" s="353"/>
-      <c r="Q11" s="353"/>
-      <c r="R11" s="354"/>
+      <c r="B11" s="368"/>
+      <c r="C11" s="368"/>
+      <c r="D11" s="368"/>
+      <c r="E11" s="372"/>
+      <c r="F11" s="373"/>
+      <c r="G11" s="373"/>
+      <c r="H11" s="373"/>
+      <c r="I11" s="373"/>
+      <c r="J11" s="373"/>
+      <c r="K11" s="373"/>
+      <c r="L11" s="373"/>
+      <c r="M11" s="373"/>
+      <c r="N11" s="373"/>
+      <c r="O11" s="373"/>
+      <c r="P11" s="373"/>
+      <c r="Q11" s="373"/>
+      <c r="R11" s="374"/>
       <c r="S11" s="68"/>
       <c r="T11" s="128"/>
       <c r="U11" s="34"/>
-      <c r="W11" s="332"/>
-      <c r="X11" s="333"/>
-      <c r="Y11" s="333"/>
-      <c r="Z11" s="333"/>
-      <c r="AA11" s="334"/>
+      <c r="W11" s="266"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
+      <c r="AA11" s="268"/>
     </row>
     <row r="12" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B12" s="282" t="s">
+      <c r="B12" s="322" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="283"/>
-      <c r="D12" s="288" t="s">
+      <c r="C12" s="323"/>
+      <c r="D12" s="328" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="291" t="s">
+      <c r="E12" s="331" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="292"/>
-      <c r="G12" s="293" t="s">
+      <c r="F12" s="332"/>
+      <c r="G12" s="333" t="s">
         <v>99</v>
       </c>
-      <c r="H12" s="294"/>
-      <c r="I12" s="273" t="s">
+      <c r="H12" s="334"/>
+      <c r="I12" s="313" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="274"/>
-      <c r="K12" s="307" t="s">
+      <c r="J12" s="314"/>
+      <c r="K12" s="298" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="308"/>
-      <c r="M12" s="309"/>
-      <c r="N12" s="317" t="s">
+      <c r="L12" s="299"/>
+      <c r="M12" s="300"/>
+      <c r="N12" s="308" t="s">
         <v>102</v>
       </c>
-      <c r="O12" s="318"/>
+      <c r="O12" s="309"/>
       <c r="P12" s="139"/>
-      <c r="Q12" s="275" t="s">
+      <c r="Q12" s="315" t="s">
         <v>68</v>
       </c>
-      <c r="R12" s="276"/>
-      <c r="S12" s="279" t="s">
+      <c r="R12" s="316"/>
+      <c r="S12" s="319" t="s">
         <v>78</v>
       </c>
-      <c r="T12" s="295" t="s">
+      <c r="T12" s="335" t="s">
         <v>79</v>
       </c>
       <c r="U12" s="30"/>
-      <c r="V12" s="361" t="s">
+      <c r="V12" s="381" t="s">
         <v>82</v>
       </c>
-      <c r="W12" s="357" t="s">
+      <c r="W12" s="377" t="s">
         <v>83</v>
       </c>
-      <c r="X12" s="355" t="s">
+      <c r="X12" s="375" t="s">
         <v>85</v>
       </c>
-      <c r="Y12" s="357" t="s">
+      <c r="Y12" s="377" t="s">
         <v>84</v>
       </c>
-      <c r="Z12" s="359" t="s">
+      <c r="Z12" s="379" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:37" ht="72.75" customHeight="1" thickBot="1">
-      <c r="B13" s="284"/>
-      <c r="C13" s="285"/>
-      <c r="D13" s="289"/>
-      <c r="E13" s="291" t="s">
+      <c r="B13" s="324"/>
+      <c r="C13" s="325"/>
+      <c r="D13" s="329"/>
+      <c r="E13" s="331" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="292"/>
-      <c r="G13" s="293" t="s">
+      <c r="F13" s="332"/>
+      <c r="G13" s="333" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="294"/>
-      <c r="I13" s="273" t="s">
+      <c r="H13" s="334"/>
+      <c r="I13" s="313" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="274"/>
-      <c r="K13" s="307" t="s">
+      <c r="J13" s="314"/>
+      <c r="K13" s="298" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="308"/>
-      <c r="M13" s="309"/>
-      <c r="N13" s="317" t="s">
+      <c r="L13" s="299"/>
+      <c r="M13" s="300"/>
+      <c r="N13" s="308" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="318"/>
+      <c r="O13" s="309"/>
       <c r="P13" s="139"/>
-      <c r="Q13" s="277"/>
-      <c r="R13" s="278"/>
-      <c r="S13" s="280"/>
-      <c r="T13" s="296"/>
+      <c r="Q13" s="317"/>
+      <c r="R13" s="318"/>
+      <c r="S13" s="320"/>
+      <c r="T13" s="336"/>
       <c r="U13" s="30"/>
-      <c r="V13" s="362"/>
-      <c r="W13" s="358"/>
-      <c r="X13" s="356"/>
-      <c r="Y13" s="358"/>
-      <c r="Z13" s="360"/>
+      <c r="V13" s="382"/>
+      <c r="W13" s="378"/>
+      <c r="X13" s="376"/>
+      <c r="Y13" s="378"/>
+      <c r="Z13" s="380"/>
     </row>
     <row r="14" spans="2:37" ht="129" customHeight="1" thickBot="1">
-      <c r="B14" s="286"/>
-      <c r="C14" s="287"/>
-      <c r="D14" s="290"/>
+      <c r="B14" s="326"/>
+      <c r="C14" s="327"/>
+      <c r="D14" s="330"/>
       <c r="E14" s="130" t="s">
         <v>0</v>
       </c>
@@ -9521,8 +9527,8 @@
       <c r="R14" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="S14" s="281"/>
-      <c r="T14" s="297"/>
+      <c r="S14" s="321"/>
+      <c r="T14" s="337"/>
       <c r="U14" s="30"/>
       <c r="V14" s="91"/>
       <c r="W14" s="92"/>
@@ -9534,13 +9540,13 @@
       </c>
     </row>
     <row r="15" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B15" s="363">
+      <c r="B15" s="361">
         <v>1</v>
       </c>
       <c r="C15" s="161" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="384">
+      <c r="D15" s="389">
         <v>36</v>
       </c>
       <c r="E15" s="115"/>
@@ -9569,17 +9575,17 @@
         <v>18</v>
       </c>
       <c r="P15" s="117"/>
-      <c r="Q15" s="367">
+      <c r="Q15" s="352">
         <f>SUM(E15:P15)</f>
         <v>168</v>
       </c>
-      <c r="R15" s="369">
+      <c r="R15" s="354">
         <v>8</v>
       </c>
-      <c r="S15" s="249">
+      <c r="S15" s="250">
         <v>350</v>
       </c>
-      <c r="T15" s="251">
+      <c r="T15" s="252">
         <f>SUM(S15-Q15)</f>
         <v>182</v>
       </c>
@@ -9610,11 +9616,11 @@
       </c>
     </row>
     <row r="16" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B16" s="364"/>
+      <c r="B16" s="362"/>
       <c r="C16" s="162" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="385"/>
+      <c r="D16" s="390"/>
       <c r="E16" s="118" t="str">
         <f t="shared" ref="E16:P16" si="1">IF(E15=0, "", IF(MOD(E15, $D$15) = 0, E15 / $D$15, IF(INT(E15 / $D$15) = 0, MOD(E15, $D$15) &amp; " P", INT(E15 / $D$15) &amp; " + " &amp; MOD(E15, $D$15) &amp; " P")))</f>
         <v/>
@@ -9663,10 +9669,10 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="368"/>
-      <c r="R16" s="370"/>
-      <c r="S16" s="250"/>
-      <c r="T16" s="252"/>
+      <c r="Q16" s="353"/>
+      <c r="R16" s="355"/>
+      <c r="S16" s="251"/>
+      <c r="T16" s="253"/>
       <c r="U16" s="30"/>
       <c r="V16" s="99"/>
       <c r="W16" s="100"/>
@@ -9678,13 +9684,13 @@
       </c>
     </row>
     <row r="17" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B17" s="363">
+      <c r="B17" s="361">
         <v>2</v>
       </c>
       <c r="C17" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="382">
+      <c r="D17" s="387">
         <v>32</v>
       </c>
       <c r="E17" s="115"/>
@@ -9713,17 +9719,17 @@
         <v>23</v>
       </c>
       <c r="P17" s="117"/>
-      <c r="Q17" s="367">
+      <c r="Q17" s="352">
         <f>SUM(E17:P17)</f>
         <v>455</v>
       </c>
-      <c r="R17" s="369">
+      <c r="R17" s="354">
         <v>18</v>
       </c>
-      <c r="S17" s="249">
+      <c r="S17" s="250">
         <v>790</v>
       </c>
-      <c r="T17" s="251">
+      <c r="T17" s="252">
         <f>SUM(S17-Q17)</f>
         <v>335</v>
       </c>
@@ -9754,11 +9760,11 @@
       </c>
     </row>
     <row r="18" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B18" s="364"/>
+      <c r="B18" s="362"/>
       <c r="C18" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="383"/>
+      <c r="D18" s="388"/>
       <c r="E18" s="118" t="str">
         <f t="shared" ref="E18:P18" si="3">IF(E17=0, "", IF(MOD(E17, $D$17) = 0, E17 / $D$17, IF(INT(E17 / $D$17) = 0, MOD(E17, $D$17) &amp; " P", INT(E17 / $D$17) &amp; " + " &amp; MOD(E17, $D$17) &amp; " P")))</f>
         <v/>
@@ -9807,10 +9813,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q18" s="368"/>
-      <c r="R18" s="370"/>
-      <c r="S18" s="250"/>
-      <c r="T18" s="252"/>
+      <c r="Q18" s="353"/>
+      <c r="R18" s="355"/>
+      <c r="S18" s="251"/>
+      <c r="T18" s="253"/>
       <c r="U18" s="30"/>
       <c r="V18" s="99"/>
       <c r="W18" s="100"/>
@@ -9822,13 +9828,13 @@
       </c>
     </row>
     <row r="19" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B19" s="363">
+      <c r="B19" s="361">
         <v>3</v>
       </c>
       <c r="C19" s="163" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="382">
+      <c r="D19" s="387">
         <v>36</v>
       </c>
       <c r="E19" s="119"/>
@@ -9857,17 +9863,17 @@
         <v>6</v>
       </c>
       <c r="P19" s="122"/>
-      <c r="Q19" s="367">
+      <c r="Q19" s="352">
         <f>SUM(E19:P19)</f>
         <v>117</v>
       </c>
-      <c r="R19" s="369">
+      <c r="R19" s="354">
         <v>8</v>
       </c>
-      <c r="S19" s="249">
+      <c r="S19" s="250">
         <v>240</v>
       </c>
-      <c r="T19" s="251">
+      <c r="T19" s="252">
         <f>SUM(S19-Q19)</f>
         <v>123</v>
       </c>
@@ -9898,11 +9904,11 @@
       </c>
     </row>
     <row r="20" spans="2:37" ht="72" customHeight="1" thickBot="1">
-      <c r="B20" s="364"/>
+      <c r="B20" s="362"/>
       <c r="C20" s="165" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="383"/>
+      <c r="D20" s="388"/>
       <c r="E20" s="118" t="str">
         <f t="shared" ref="E20:P20" si="5">IF(E19=0, "", IF(MOD(E19, $D$19) = 0, E19/ $D$19, IF(INT(E19 / $D$19) = 0, MOD(E19, $D$19) &amp; " P", INT(E19 / $D$19) &amp; " + " &amp; MOD(E19, $D$19) &amp; " P")))</f>
         <v/>
@@ -9951,10 +9957,10 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="368"/>
-      <c r="R20" s="370"/>
-      <c r="S20" s="250"/>
-      <c r="T20" s="252"/>
+      <c r="Q20" s="353"/>
+      <c r="R20" s="355"/>
+      <c r="S20" s="251"/>
+      <c r="T20" s="253"/>
       <c r="U20" s="30"/>
       <c r="V20" s="99"/>
       <c r="W20" s="100"/>
@@ -9966,13 +9972,13 @@
       </c>
     </row>
     <row r="21" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B21" s="363">
+      <c r="B21" s="361">
         <v>4</v>
       </c>
       <c r="C21" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="382">
+      <c r="D21" s="387">
         <v>32</v>
       </c>
       <c r="E21" s="115"/>
@@ -10001,17 +10007,17 @@
         <v>68</v>
       </c>
       <c r="P21" s="117"/>
-      <c r="Q21" s="367">
+      <c r="Q21" s="352">
         <f>SUM(E21:P21)</f>
         <v>571</v>
       </c>
-      <c r="R21" s="369">
+      <c r="R21" s="354">
         <v>23</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="250">
         <v>1272</v>
       </c>
-      <c r="T21" s="251">
+      <c r="T21" s="252">
         <f>SUM(S21-Q21)</f>
         <v>701</v>
       </c>
@@ -10042,11 +10048,11 @@
       </c>
     </row>
     <row r="22" spans="2:37" ht="72.599999999999994" customHeight="1" thickBot="1">
-      <c r="B22" s="364"/>
+      <c r="B22" s="362"/>
       <c r="C22" s="164" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="383"/>
+      <c r="D22" s="388"/>
       <c r="E22" s="118" t="str">
         <f t="shared" ref="E22:P22" si="7">IF(E21=0, "", IF(MOD(E21, $D$21) = 0, E21/ $D$21, IF(INT(E21 / $D$21) = 0, MOD(E21, $D$21) &amp; " P", INT(E21 / $D$21) &amp; " + " &amp; MOD(E21, $D$21) &amp; " P")))</f>
         <v/>
@@ -10095,10 +10101,10 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q22" s="368"/>
-      <c r="R22" s="370"/>
-      <c r="S22" s="250"/>
-      <c r="T22" s="252"/>
+      <c r="Q22" s="353"/>
+      <c r="R22" s="355"/>
+      <c r="S22" s="251"/>
+      <c r="T22" s="253"/>
       <c r="U22" s="30"/>
       <c r="V22" s="99"/>
       <c r="W22" s="100"/>
@@ -10116,7 +10122,7 @@
       <c r="C23" s="166" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="386">
+      <c r="D23" s="385">
         <v>18</v>
       </c>
       <c r="E23" s="123"/>
@@ -10145,17 +10151,17 @@
         <v>2</v>
       </c>
       <c r="P23" s="125"/>
-      <c r="Q23" s="367">
+      <c r="Q23" s="352">
         <f>SUM(E23:P23)</f>
         <v>40</v>
       </c>
-      <c r="R23" s="369">
+      <c r="R23" s="354">
         <v>8</v>
       </c>
-      <c r="S23" s="249">
+      <c r="S23" s="250">
         <v>100</v>
       </c>
-      <c r="T23" s="251">
+      <c r="T23" s="252">
         <f>SUM(S23-Q23)</f>
         <v>60</v>
       </c>
@@ -10190,7 +10196,7 @@
       <c r="C24" s="164" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="387"/>
+      <c r="D24" s="386"/>
       <c r="E24" s="126" t="str">
         <f t="shared" ref="E24:P24" si="9">IF(E23=0, "", IF(MOD(E23, $D$23) = 0, E23/ $D$23, IF(INT(E23 / $D$23) = 0, MOD(E23, $D$23) &amp; " P", INT(E23 / $D$23) &amp; " + " &amp; MOD(E23, $D$23) &amp; " P")))</f>
         <v/>
@@ -10239,10 +10245,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q24" s="368"/>
-      <c r="R24" s="370"/>
-      <c r="S24" s="250"/>
-      <c r="T24" s="252"/>
+      <c r="Q24" s="353"/>
+      <c r="R24" s="355"/>
+      <c r="S24" s="251"/>
+      <c r="T24" s="253"/>
       <c r="U24" s="30"/>
       <c r="V24" s="99"/>
       <c r="W24" s="100"/>
@@ -10260,7 +10266,7 @@
       <c r="C25" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="388">
+      <c r="D25" s="383">
         <v>36</v>
       </c>
       <c r="E25" s="115"/>
@@ -10289,17 +10295,17 @@
         <v>20</v>
       </c>
       <c r="P25" s="117"/>
-      <c r="Q25" s="367">
+      <c r="Q25" s="352">
         <f>SUM(E25:P25)</f>
         <v>437</v>
       </c>
-      <c r="R25" s="369">
+      <c r="R25" s="354">
         <v>16</v>
       </c>
-      <c r="S25" s="249">
+      <c r="S25" s="250">
         <v>650</v>
       </c>
-      <c r="T25" s="251">
+      <c r="T25" s="252">
         <f>SUM(S25-Q25)</f>
         <v>213</v>
       </c>
@@ -10334,7 +10340,7 @@
       <c r="C26" s="164" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="389"/>
+      <c r="D26" s="384"/>
       <c r="E26" s="118" t="str">
         <f t="shared" ref="E26:P26" si="11">IF(E25=0, "", IF(MOD(E25, $D$25) = 0, E25/ $D$25, IF(INT(E25 / $D$25) = 0, MOD(E25, $D$25) &amp; " P", INT(E25 / $D$25) &amp; " + " &amp; MOD(E25, $D$25) &amp; " P")))</f>
         <v/>
@@ -10383,10 +10389,10 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q26" s="368"/>
-      <c r="R26" s="370"/>
-      <c r="S26" s="250"/>
-      <c r="T26" s="252"/>
+      <c r="Q26" s="353"/>
+      <c r="R26" s="355"/>
+      <c r="S26" s="251"/>
+      <c r="T26" s="253"/>
       <c r="U26" s="30"/>
       <c r="V26" s="99"/>
       <c r="W26" s="100"/>
@@ -10404,7 +10410,7 @@
       <c r="C27" s="163" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="388">
+      <c r="D27" s="383">
         <v>20</v>
       </c>
       <c r="E27" s="115"/>
@@ -10433,17 +10439,17 @@
         <v>8</v>
       </c>
       <c r="P27" s="117"/>
-      <c r="Q27" s="367">
+      <c r="Q27" s="352">
         <f>SUM(E27:P27)</f>
         <v>75</v>
       </c>
-      <c r="R27" s="369">
+      <c r="R27" s="354">
         <v>7</v>
       </c>
-      <c r="S27" s="249">
+      <c r="S27" s="250">
         <v>140</v>
       </c>
-      <c r="T27" s="251">
+      <c r="T27" s="252">
         <f>SUM(S27-Q27)</f>
         <v>65</v>
       </c>
@@ -10478,7 +10484,7 @@
       <c r="C28" s="165" t="s">
         <v>107</v>
       </c>
-      <c r="D28" s="389"/>
+      <c r="D28" s="384"/>
       <c r="E28" s="118" t="str">
         <f t="shared" ref="E28:P28" si="13">IF(E27=0, "", IF(MOD(E27, $D$27) = 0, E27/ $D$27, IF(INT(E27 / $D$27) = 0, MOD(E27, $D$27) &amp; " P", INT(E27 / $D$27) &amp; " + " &amp; MOD(E27, $D$27) &amp; " P")))</f>
         <v/>
@@ -10527,10 +10533,10 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q28" s="368"/>
-      <c r="R28" s="370"/>
-      <c r="S28" s="250"/>
-      <c r="T28" s="252"/>
+      <c r="Q28" s="353"/>
+      <c r="R28" s="355"/>
+      <c r="S28" s="251"/>
+      <c r="T28" s="253"/>
       <c r="U28" s="30"/>
       <c r="V28" s="95"/>
       <c r="W28" s="100"/>
@@ -10548,7 +10554,7 @@
       <c r="C29" s="167" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="388">
+      <c r="D29" s="383">
         <v>15</v>
       </c>
       <c r="E29" s="119"/>
@@ -10577,17 +10583,17 @@
         <v>15</v>
       </c>
       <c r="P29" s="122"/>
-      <c r="Q29" s="367">
+      <c r="Q29" s="352">
         <f>SUM(E29:P29)</f>
         <v>122</v>
       </c>
-      <c r="R29" s="369">
+      <c r="R29" s="354">
         <v>10</v>
       </c>
-      <c r="S29" s="249">
+      <c r="S29" s="250">
         <v>240</v>
       </c>
-      <c r="T29" s="251">
+      <c r="T29" s="252">
         <f>SUM(S29-Q29)</f>
         <v>118</v>
       </c>
@@ -10622,7 +10628,7 @@
       <c r="C30" s="164" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="389"/>
+      <c r="D30" s="384"/>
       <c r="E30" s="118" t="str">
         <f t="shared" ref="E30:P30" si="14">IF(E29=0, "", IF(MOD(E29, $D$29) = 0, E29/ $D$29, IF(INT(E29 / $D$29) = 0, MOD(E29, $D$29) &amp; " P", INT(E29 / $D$29) &amp; " + " &amp; MOD(E29, $D$29) &amp; " P")))</f>
         <v/>
@@ -10671,10 +10677,10 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q30" s="368"/>
-      <c r="R30" s="370"/>
-      <c r="S30" s="250"/>
-      <c r="T30" s="252"/>
+      <c r="Q30" s="353"/>
+      <c r="R30" s="355"/>
+      <c r="S30" s="251"/>
+      <c r="T30" s="253"/>
       <c r="U30" s="30"/>
       <c r="V30" s="95"/>
       <c r="W30" s="100"/>
@@ -10692,7 +10698,7 @@
       <c r="C31" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="388">
+      <c r="D31" s="383">
         <v>45</v>
       </c>
       <c r="E31" s="119"/>
@@ -10721,17 +10727,17 @@
         <v>1</v>
       </c>
       <c r="P31" s="122"/>
-      <c r="Q31" s="367">
+      <c r="Q31" s="352">
         <f>SUM(E31:P31)</f>
         <v>17</v>
       </c>
-      <c r="R31" s="377">
+      <c r="R31" s="358">
         <v>5</v>
       </c>
-      <c r="S31" s="249">
+      <c r="S31" s="250">
         <v>70</v>
       </c>
-      <c r="T31" s="251">
+      <c r="T31" s="252">
         <f>SUM(S31-Q31)</f>
         <v>53</v>
       </c>
@@ -10766,7 +10772,7 @@
       <c r="C32" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="389"/>
+      <c r="D32" s="384"/>
       <c r="E32" s="118" t="str">
         <f t="shared" ref="E32:P32" si="16">IF(E31=0, "", IF(MOD(E31, $D$31) = 0, E31/ $D$31, IF(INT(E31 / $D$31) = 0, MOD(E31, $D$31) &amp; " P", INT(E31 / $D$31) &amp; " + " &amp; MOD(E31, $D$31) &amp; " P")))</f>
         <v/>
@@ -10815,10 +10821,10 @@
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q32" s="368"/>
-      <c r="R32" s="370"/>
-      <c r="S32" s="250"/>
-      <c r="T32" s="252"/>
+      <c r="Q32" s="353"/>
+      <c r="R32" s="355"/>
+      <c r="S32" s="251"/>
+      <c r="T32" s="253"/>
       <c r="U32" s="30"/>
       <c r="V32" s="95"/>
       <c r="W32" s="100"/>
@@ -10836,7 +10842,7 @@
       <c r="C33" s="167" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="388">
+      <c r="D33" s="383">
         <v>15</v>
       </c>
       <c r="E33" s="119"/>
@@ -10865,17 +10871,17 @@
         <v>19</v>
       </c>
       <c r="P33" s="122"/>
-      <c r="Q33" s="367">
+      <c r="Q33" s="352">
         <f>SUM(E33:P33)</f>
         <v>179</v>
       </c>
-      <c r="R33" s="377">
+      <c r="R33" s="358">
         <v>17</v>
       </c>
-      <c r="S33" s="249">
+      <c r="S33" s="250">
         <v>320</v>
       </c>
-      <c r="T33" s="251">
+      <c r="T33" s="252">
         <f t="shared" ref="T33" si="17">SUM(S33-Q33)</f>
         <v>141</v>
       </c>
@@ -10910,7 +10916,7 @@
       <c r="C34" s="165" t="s">
         <v>134</v>
       </c>
-      <c r="D34" s="389"/>
+      <c r="D34" s="384"/>
       <c r="E34" s="118" t="str">
         <f>IF(E33=0, "", IF(MOD(E33, $D$33) = 0, E33/ $D$33, IF(INT(E33 / $D$33) = 0, MOD(E33, $D$33) &amp; " P", INT(E33 / $D$33) &amp; " + " &amp; MOD(E33, $D$33) &amp; " P")))</f>
         <v/>
@@ -10959,10 +10965,10 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q34" s="368"/>
-      <c r="R34" s="370"/>
-      <c r="S34" s="250"/>
-      <c r="T34" s="252"/>
+      <c r="Q34" s="353"/>
+      <c r="R34" s="355"/>
+      <c r="S34" s="251"/>
+      <c r="T34" s="253"/>
       <c r="U34" s="30"/>
       <c r="V34" s="95"/>
       <c r="W34" s="100"/>
@@ -10980,7 +10986,7 @@
       <c r="C35" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="388">
+      <c r="D35" s="383">
         <v>15</v>
       </c>
       <c r="E35" s="140"/>
@@ -11009,17 +11015,17 @@
         <v>10</v>
       </c>
       <c r="P35" s="141"/>
-      <c r="Q35" s="367">
+      <c r="Q35" s="352">
         <f>SUM(E35:P35)</f>
         <v>141</v>
       </c>
-      <c r="R35" s="369">
+      <c r="R35" s="354">
         <v>11</v>
       </c>
-      <c r="S35" s="249">
+      <c r="S35" s="250">
         <v>190</v>
       </c>
-      <c r="T35" s="378">
+      <c r="T35" s="356">
         <f t="shared" ref="T35" si="19">SUM(S35-Q35)</f>
         <v>49</v>
       </c>
@@ -11054,7 +11060,7 @@
       <c r="C36" s="165" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="389"/>
+      <c r="D36" s="384"/>
       <c r="E36" s="118" t="str">
         <f>IF(E35=0, "", IF(MOD(E35, $D$35) = 0, E35/ $D$35, IF(INT(E35 / $D$35) = 0, MOD(E35, $D$35) &amp; " P", INT(E35 / $D$35) &amp; " + " &amp; MOD(E35, $D$35) &amp; " P")))</f>
         <v/>
@@ -11103,10 +11109,10 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q36" s="368"/>
-      <c r="R36" s="370"/>
-      <c r="S36" s="250"/>
-      <c r="T36" s="379"/>
+      <c r="Q36" s="353"/>
+      <c r="R36" s="355"/>
+      <c r="S36" s="251"/>
+      <c r="T36" s="357"/>
       <c r="U36" s="30"/>
       <c r="V36" s="95"/>
       <c r="W36" s="100"/>
@@ -11121,7 +11127,7 @@
       <c r="C37" s="167" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="388">
+      <c r="D37" s="383">
         <v>27</v>
       </c>
       <c r="E37" s="115"/>
@@ -11150,17 +11156,17 @@
         <v>35</v>
       </c>
       <c r="P37" s="115"/>
-      <c r="Q37" s="367">
+      <c r="Q37" s="352">
         <f>SUM(E37:P37)</f>
         <v>256</v>
       </c>
-      <c r="R37" s="369">
+      <c r="R37" s="354">
         <v>13</v>
       </c>
-      <c r="S37" s="249">
+      <c r="S37" s="250">
         <v>440</v>
       </c>
-      <c r="T37" s="378">
+      <c r="T37" s="356">
         <f t="shared" ref="T37" si="21">SUM(S37-Q37)</f>
         <v>184</v>
       </c>
@@ -11195,7 +11201,7 @@
       <c r="C38" s="165" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="389"/>
+      <c r="D38" s="384"/>
       <c r="E38" s="118" t="str">
         <f>IF(E37=0, "", IF(MOD(E37, $D$37) = 0, E37/ $D$37, IF(INT(E37 / $D$37) = 0, MOD(E37, $D$37) &amp; " P", INT(E37 / $D$37) &amp; " + " &amp; MOD(E37, $D$37) &amp; " P")))</f>
         <v/>
@@ -11244,10 +11250,10 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q38" s="368"/>
-      <c r="R38" s="370"/>
-      <c r="S38" s="250"/>
-      <c r="T38" s="379"/>
+      <c r="Q38" s="353"/>
+      <c r="R38" s="355"/>
+      <c r="S38" s="251"/>
+      <c r="T38" s="357"/>
       <c r="U38" s="30"/>
       <c r="V38" s="95"/>
       <c r="W38" s="100"/>
@@ -11262,7 +11268,7 @@
       <c r="C39" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="388">
+      <c r="D39" s="383">
         <v>20</v>
       </c>
       <c r="E39" s="115"/>
@@ -11291,17 +11297,17 @@
         <v>9</v>
       </c>
       <c r="P39" s="115"/>
-      <c r="Q39" s="367">
+      <c r="Q39" s="352">
         <f>SUM(E39:P39)</f>
         <v>243</v>
       </c>
-      <c r="R39" s="369">
+      <c r="R39" s="354">
         <v>15</v>
       </c>
-      <c r="S39" s="249">
+      <c r="S39" s="250">
         <v>450</v>
       </c>
-      <c r="T39" s="378">
+      <c r="T39" s="356">
         <f t="shared" ref="T39" si="23">SUM(S39-Q39)</f>
         <v>207</v>
       </c>
@@ -11336,7 +11342,7 @@
       <c r="C40" s="164" t="s">
         <v>115</v>
       </c>
-      <c r="D40" s="389"/>
+      <c r="D40" s="384"/>
       <c r="E40" s="118" t="str">
         <f>IF(E39=0, "", IF(MOD(E39, $D$39) = 0, E39/ $D$39, IF(INT(E39 / $D$39) = 0, MOD(E39, $D$39) &amp; " P", INT(E39 / $D$39) &amp; " + " &amp; MOD(E39, $D$39) &amp; " P")))</f>
         <v/>
@@ -11385,10 +11391,10 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="Q40" s="368"/>
-      <c r="R40" s="370"/>
-      <c r="S40" s="250"/>
-      <c r="T40" s="379"/>
+      <c r="Q40" s="353"/>
+      <c r="R40" s="355"/>
+      <c r="S40" s="251"/>
+      <c r="T40" s="357"/>
       <c r="U40" s="30"/>
       <c r="V40" s="95"/>
       <c r="W40" s="100"/>
@@ -11403,7 +11409,7 @@
       <c r="C41" s="166" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="388">
+      <c r="D41" s="383">
         <v>32</v>
       </c>
       <c r="E41" s="115"/>
@@ -11432,17 +11438,17 @@
         <v>2</v>
       </c>
       <c r="P41" s="115"/>
-      <c r="Q41" s="367">
+      <c r="Q41" s="352">
         <f>SUM(E41:P41)</f>
         <v>97</v>
       </c>
-      <c r="R41" s="369">
+      <c r="R41" s="354">
         <v>7</v>
       </c>
-      <c r="S41" s="249">
+      <c r="S41" s="250">
         <v>220</v>
       </c>
-      <c r="T41" s="251">
+      <c r="T41" s="252">
         <f t="shared" ref="T41" si="25">SUM(S41-Q41)</f>
         <v>123</v>
       </c>
@@ -11477,7 +11483,7 @@
       <c r="C42" s="164" t="s">
         <v>116</v>
       </c>
-      <c r="D42" s="389"/>
+      <c r="D42" s="384"/>
       <c r="E42" s="118" t="str">
         <f>IF(E41=0, "", IF(MOD(E41, $D$41) = 0, E41/ $D$41, IF(INT(E41 / $D$41) = 0, MOD(E41, $D$41) &amp; " P", INT(E41 / $D$41) &amp; " + " &amp; MOD(E41, $D$41) &amp; " P")))</f>
         <v/>
@@ -11526,10 +11532,10 @@
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="Q42" s="368"/>
-      <c r="R42" s="370"/>
-      <c r="S42" s="250"/>
-      <c r="T42" s="252"/>
+      <c r="Q42" s="353"/>
+      <c r="R42" s="355"/>
+      <c r="S42" s="251"/>
+      <c r="T42" s="253"/>
       <c r="U42" s="30"/>
       <c r="V42" s="95"/>
       <c r="W42" s="100"/>
@@ -11544,7 +11550,7 @@
       <c r="C43" s="163" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="388">
+      <c r="D43" s="383">
         <v>15</v>
       </c>
       <c r="E43" s="115"/>
@@ -11573,17 +11579,17 @@
         <v>0</v>
       </c>
       <c r="P43" s="115"/>
-      <c r="Q43" s="367">
+      <c r="Q43" s="352">
         <f>SUM(E43:P43)</f>
         <v>52</v>
       </c>
-      <c r="R43" s="369">
+      <c r="R43" s="354">
         <v>6</v>
       </c>
-      <c r="S43" s="249">
+      <c r="S43" s="250">
         <v>100</v>
       </c>
-      <c r="T43" s="251">
+      <c r="T43" s="252">
         <f t="shared" ref="T43" si="27">SUM(S43-Q43)</f>
         <v>48</v>
       </c>
@@ -11618,7 +11624,7 @@
       <c r="C44" s="165" t="s">
         <v>117</v>
       </c>
-      <c r="D44" s="389"/>
+      <c r="D44" s="384"/>
       <c r="E44" s="118" t="str">
         <f>IF(E43=0, "", IF(MOD(E43, $D$43) = 0, E43/ $D$43, IF(INT(E43 / $D$43) = 0, MOD(E43, $D$43) &amp; " P", INT(E43 / $D$43) &amp; " + " &amp; MOD(E43, $D$43) &amp; " P")))</f>
         <v/>
@@ -11667,10 +11673,10 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="Q44" s="368"/>
-      <c r="R44" s="370"/>
-      <c r="S44" s="250"/>
-      <c r="T44" s="252"/>
+      <c r="Q44" s="353"/>
+      <c r="R44" s="355"/>
+      <c r="S44" s="251"/>
+      <c r="T44" s="253"/>
       <c r="U44" s="30"/>
       <c r="V44" s="95"/>
       <c r="W44" s="100"/>
@@ -11679,11 +11685,11 @@
       <c r="Z44" s="102"/>
     </row>
     <row r="45" spans="2:37" ht="73.5" customHeight="1" thickBot="1">
-      <c r="B45" s="340" t="s">
+      <c r="B45" s="274" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="341"/>
-      <c r="D45" s="342"/>
+      <c r="C45" s="275"/>
+      <c r="D45" s="276"/>
       <c r="E45" s="84"/>
       <c r="F45" s="84"/>
       <c r="G45" s="84"/>
@@ -11726,7 +11732,7 @@
       <c r="Y45" s="106"/>
       <c r="Z45" s="105"/>
     </row>
-    <row r="46" spans="2:37" ht="13.15" customHeight="1" thickBot="1">
+    <row r="46" spans="2:37" ht="13.2" customHeight="1" thickBot="1">
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -11754,92 +11760,92 @@
     <row r="47" spans="2:37" ht="105" hidden="1" customHeight="1" thickBot="1"/>
     <row r="48" spans="2:37" ht="37.5" hidden="1" customHeight="1" thickBot="1"/>
     <row r="49" spans="2:20" ht="48.75" hidden="1" customHeight="1" thickBot="1"/>
-    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.900000000000006" customHeight="1" thickBot="1">
-      <c r="B50" s="324" t="s">
+    <row r="50" spans="2:20" s="30" customFormat="1" ht="64.95" customHeight="1" thickBot="1">
+      <c r="B50" s="281" t="s">
         <v>49</v>
       </c>
-      <c r="C50" s="325"/>
-      <c r="D50" s="324" t="s">
+      <c r="C50" s="282"/>
+      <c r="D50" s="281" t="s">
         <v>53</v>
       </c>
-      <c r="E50" s="325"/>
-      <c r="F50" s="324" t="s">
+      <c r="E50" s="282"/>
+      <c r="F50" s="281" t="s">
         <v>54</v>
       </c>
-      <c r="G50" s="325"/>
-      <c r="H50" s="324" t="s">
+      <c r="G50" s="282"/>
+      <c r="H50" s="281" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="325"/>
+      <c r="I50" s="282"/>
       <c r="J50" s="38"/>
-      <c r="M50" s="266" t="s">
+      <c r="M50" s="345" t="s">
         <v>88</v>
       </c>
-      <c r="N50" s="266"/>
-      <c r="O50" s="266"/>
-      <c r="P50" s="266"/>
-      <c r="Q50" s="380">
+      <c r="N50" s="345"/>
+      <c r="O50" s="345"/>
+      <c r="P50" s="345"/>
+      <c r="Q50" s="348">
         <f>SUM(R45)</f>
         <v>172</v>
       </c>
-      <c r="R50" s="255" t="s">
+      <c r="R50" s="340" t="s">
         <v>89</v>
       </c>
       <c r="T50" s="36"/>
     </row>
-    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1">
-      <c r="B51" s="326" t="s">
+    <row r="51" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1">
+      <c r="B51" s="283" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="327"/>
-      <c r="D51" s="328"/>
-      <c r="E51" s="329"/>
-      <c r="F51" s="328"/>
-      <c r="G51" s="329"/>
-      <c r="H51" s="328"/>
-      <c r="I51" s="329"/>
+      <c r="C51" s="284"/>
+      <c r="D51" s="285"/>
+      <c r="E51" s="286"/>
+      <c r="F51" s="285"/>
+      <c r="G51" s="286"/>
+      <c r="H51" s="285"/>
+      <c r="I51" s="286"/>
       <c r="J51" s="38"/>
-      <c r="M51" s="266"/>
-      <c r="N51" s="266"/>
-      <c r="O51" s="266"/>
-      <c r="P51" s="266"/>
-      <c r="Q51" s="381"/>
-      <c r="R51" s="255"/>
+      <c r="M51" s="345"/>
+      <c r="N51" s="345"/>
+      <c r="O51" s="345"/>
+      <c r="P51" s="345"/>
+      <c r="Q51" s="349"/>
+      <c r="R51" s="340"/>
       <c r="T51" s="36"/>
     </row>
-    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
-      <c r="B52" s="335" t="s">
+    <row r="52" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
+      <c r="B52" s="269" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="336"/>
-      <c r="D52" s="337"/>
-      <c r="E52" s="338"/>
-      <c r="F52" s="337"/>
-      <c r="G52" s="338"/>
-      <c r="H52" s="337"/>
-      <c r="I52" s="338"/>
+      <c r="C52" s="270"/>
+      <c r="D52" s="271"/>
+      <c r="E52" s="272"/>
+      <c r="F52" s="271"/>
+      <c r="G52" s="272"/>
+      <c r="H52" s="271"/>
+      <c r="I52" s="272"/>
       <c r="J52" s="38"/>
       <c r="M52" s="67"/>
-      <c r="N52" s="339" t="s">
+      <c r="N52" s="273" t="s">
         <v>73</v>
       </c>
-      <c r="O52" s="339"/>
-      <c r="P52" s="339"/>
-      <c r="Q52" s="339"/>
-      <c r="R52" s="339"/>
+      <c r="O52" s="273"/>
+      <c r="P52" s="273"/>
+      <c r="Q52" s="273"/>
+      <c r="R52" s="273"/>
       <c r="T52" s="36"/>
     </row>
-    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.9" customHeight="1" thickBot="1">
-      <c r="B53" s="320" t="s">
+    <row r="53" spans="2:20" s="30" customFormat="1" ht="58.95" customHeight="1" thickBot="1">
+      <c r="B53" s="277" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="321"/>
-      <c r="D53" s="322"/>
-      <c r="E53" s="323"/>
-      <c r="F53" s="322"/>
-      <c r="G53" s="323"/>
-      <c r="H53" s="322"/>
-      <c r="I53" s="323"/>
+      <c r="C53" s="278"/>
+      <c r="D53" s="279"/>
+      <c r="E53" s="280"/>
+      <c r="F53" s="279"/>
+      <c r="G53" s="280"/>
+      <c r="H53" s="279"/>
+      <c r="I53" s="280"/>
       <c r="J53" s="38"/>
       <c r="K53" s="53" t="s">
         <v>77</v>
@@ -11859,7 +11865,7 @@
       <c r="R53" s="52"/>
       <c r="T53" s="36"/>
     </row>
-    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.150000000000006" customHeight="1" thickBot="1">
+    <row r="54" spans="2:20" s="30" customFormat="1" ht="64.2" customHeight="1" thickBot="1">
       <c r="B54" s="38"/>
       <c r="C54" s="38"/>
       <c r="D54" s="89"/>
@@ -11881,106 +11887,6 @@
     </row>
   </sheetData>
   <mergeCells count="124">
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="R50:R51"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="N52:R52"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="M50:P51"/>
-    <mergeCell ref="Q50:Q51"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="S43:S44"/>
-    <mergeCell ref="T43:T44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="S39:S40"/>
-    <mergeCell ref="T39:T40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="S41:S42"/>
-    <mergeCell ref="T41:T42"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:S36"/>
-    <mergeCell ref="T35:T36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="S31:S32"/>
-    <mergeCell ref="T31:T32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="S33:S34"/>
-    <mergeCell ref="T33:T34"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="S23:S24"/>
-    <mergeCell ref="T23:T24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="S21:S22"/>
-    <mergeCell ref="T21:T22"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="E10:R11"/>
@@ -12005,6 +11911,106 @@
     <mergeCell ref="T12:T14"/>
     <mergeCell ref="V12:V13"/>
     <mergeCell ref="W12:W13"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="S21:S22"/>
+    <mergeCell ref="T21:T22"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="S23:S24"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="S31:S32"/>
+    <mergeCell ref="T31:T32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="S33:S34"/>
+    <mergeCell ref="T33:T34"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:S36"/>
+    <mergeCell ref="T35:T36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="T37:T38"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="S43:S44"/>
+    <mergeCell ref="T43:T44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="S39:S40"/>
+    <mergeCell ref="T39:T40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="S41:S42"/>
+    <mergeCell ref="T41:T42"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="R50:R51"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="N52:R52"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="M50:P51"/>
+    <mergeCell ref="Q50:Q51"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.15748031496062992" bottom="0" header="0" footer="0"/>
@@ -12016,49 +12022,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:AW50"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="51.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="3" customWidth="1"/>
-    <col min="4" max="12" width="6.75" style="3" customWidth="1"/>
-    <col min="13" max="14" width="6.75" style="30" customWidth="1"/>
-    <col min="15" max="15" width="10.25" style="3" customWidth="1"/>
-    <col min="16" max="16" width="17.25" style="3" customWidth="1"/>
-    <col min="17" max="17" width="14.25" style="3" customWidth="1"/>
-    <col min="18" max="18" width="10.75" style="3" customWidth="1"/>
-    <col min="19" max="19" width="15.75" style="3" customWidth="1"/>
-    <col min="20" max="49" width="3.75" style="3" hidden="1" customWidth="1"/>
-    <col min="50" max="16384" width="8.875" style="3"/>
+    <col min="1" max="1" width="51.69921875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" style="3" customWidth="1"/>
+    <col min="4" max="12" width="6.69921875" style="3" customWidth="1"/>
+    <col min="13" max="14" width="6.69921875" style="30" customWidth="1"/>
+    <col min="15" max="15" width="10.19921875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.19921875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="14.19921875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="10.69921875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="15.69921875" style="3" customWidth="1"/>
+    <col min="20" max="49" width="3.69921875" style="3" hidden="1" customWidth="1"/>
+    <col min="50" max="16384" width="8.8984375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="49.9" customHeight="1">
+    <row r="1" spans="1:49" ht="49.95" customHeight="1">
       <c r="A1" s="3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="390" t="s">
+      <c r="B1" s="412" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="391"/>
-      <c r="D1" s="391"/>
-      <c r="E1" s="391"/>
-      <c r="F1" s="391"/>
-      <c r="G1" s="391"/>
-      <c r="H1" s="391"/>
-      <c r="I1" s="391"/>
-      <c r="J1" s="391"/>
-      <c r="K1" s="391"/>
-      <c r="L1" s="391"/>
-      <c r="M1" s="391"/>
-      <c r="N1" s="391"/>
-      <c r="O1" s="391"/>
-      <c r="Q1" s="392" t="s">
+      <c r="C1" s="407"/>
+      <c r="D1" s="407"/>
+      <c r="E1" s="407"/>
+      <c r="F1" s="407"/>
+      <c r="G1" s="407"/>
+      <c r="H1" s="407"/>
+      <c r="I1" s="407"/>
+      <c r="J1" s="407"/>
+      <c r="K1" s="407"/>
+      <c r="L1" s="407"/>
+      <c r="M1" s="407"/>
+      <c r="N1" s="407"/>
+      <c r="O1" s="407"/>
+      <c r="Q1" s="413" t="s">
         <v>18</v>
       </c>
-      <c r="R1" s="392"/>
-      <c r="S1" s="392"/>
-    </row>
-    <row r="2" spans="1:49" ht="10.15" customHeight="1">
+      <c r="R1" s="413"/>
+      <c r="S1" s="413"/>
+    </row>
+    <row r="2" spans="1:49" ht="10.199999999999999" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -12082,23 +12088,23 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="12"/>
-      <c r="Q3" s="392" t="s">
+      <c r="Q3" s="413" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="392"/>
-      <c r="S3" s="392"/>
-    </row>
-    <row r="4" spans="1:49" ht="25.15" customHeight="1">
+      <c r="R3" s="413"/>
+      <c r="S3" s="413"/>
+    </row>
+    <row r="4" spans="1:49" ht="25.2" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="Q4" s="392"/>
-      <c r="R4" s="392"/>
-      <c r="S4" s="392"/>
-    </row>
-    <row r="5" spans="1:49" ht="4.9000000000000004" customHeight="1">
+      <c r="Q4" s="413"/>
+      <c r="R4" s="413"/>
+      <c r="S4" s="413"/>
+    </row>
+    <row r="5" spans="1:49" ht="4.95" customHeight="1">
       <c r="A5" s="5"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -12106,177 +12112,177 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
     </row>
-    <row r="6" spans="1:49" ht="25.15" customHeight="1">
-      <c r="A6" s="393" t="s">
+    <row r="6" spans="1:49" ht="25.2" customHeight="1">
+      <c r="A6" s="414" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="393"/>
-      <c r="C6" s="394" t="s">
+      <c r="B6" s="414"/>
+      <c r="C6" s="415" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="394"/>
-      <c r="E6" s="394"/>
-      <c r="F6" s="394"/>
-      <c r="G6" s="394"/>
-      <c r="H6" s="394"/>
-      <c r="I6" s="394"/>
-      <c r="J6" s="394"/>
-      <c r="K6" s="394"/>
-      <c r="L6" s="394"/>
-      <c r="M6" s="394"/>
-      <c r="N6" s="394"/>
-      <c r="O6" s="394"/>
-      <c r="P6" s="394"/>
-      <c r="Q6" s="394"/>
-      <c r="R6" s="394"/>
-      <c r="S6" s="394"/>
-    </row>
-    <row r="7" spans="1:49" ht="19.899999999999999" customHeight="1">
-      <c r="A7" s="393"/>
-      <c r="B7" s="393"/>
-      <c r="C7" s="399" t="s">
+      <c r="D6" s="415"/>
+      <c r="E6" s="415"/>
+      <c r="F6" s="415"/>
+      <c r="G6" s="415"/>
+      <c r="H6" s="415"/>
+      <c r="I6" s="415"/>
+      <c r="J6" s="415"/>
+      <c r="K6" s="415"/>
+      <c r="L6" s="415"/>
+      <c r="M6" s="415"/>
+      <c r="N6" s="415"/>
+      <c r="O6" s="415"/>
+      <c r="P6" s="415"/>
+      <c r="Q6" s="415"/>
+      <c r="R6" s="415"/>
+      <c r="S6" s="415"/>
+    </row>
+    <row r="7" spans="1:49" ht="19.95" customHeight="1">
+      <c r="A7" s="414"/>
+      <c r="B7" s="414"/>
+      <c r="C7" s="410" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="401" t="s">
+      <c r="D7" s="391" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="402"/>
-      <c r="F7" s="402"/>
-      <c r="G7" s="402"/>
-      <c r="H7" s="402"/>
-      <c r="I7" s="402"/>
-      <c r="J7" s="402"/>
-      <c r="K7" s="402"/>
-      <c r="L7" s="402"/>
-      <c r="M7" s="402"/>
-      <c r="N7" s="402"/>
-      <c r="O7" s="402"/>
-      <c r="P7" s="402"/>
-      <c r="Q7" s="402"/>
-      <c r="R7" s="402"/>
-      <c r="S7" s="403"/>
+      <c r="E7" s="392"/>
+      <c r="F7" s="392"/>
+      <c r="G7" s="392"/>
+      <c r="H7" s="392"/>
+      <c r="I7" s="392"/>
+      <c r="J7" s="392"/>
+      <c r="K7" s="392"/>
+      <c r="L7" s="392"/>
+      <c r="M7" s="392"/>
+      <c r="N7" s="392"/>
+      <c r="O7" s="392"/>
+      <c r="P7" s="392"/>
+      <c r="Q7" s="392"/>
+      <c r="R7" s="392"/>
+      <c r="S7" s="393"/>
     </row>
     <row r="8" spans="1:49" ht="15" customHeight="1">
-      <c r="A8" s="393"/>
-      <c r="B8" s="393"/>
-      <c r="C8" s="400"/>
-      <c r="D8" s="395" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="395" t="s">
+      <c r="A8" s="414"/>
+      <c r="B8" s="414"/>
+      <c r="C8" s="411"/>
+      <c r="D8" s="396" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="396" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="395" t="s">
+      <c r="F8" s="396" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="395" t="s">
+      <c r="G8" s="396" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="395" t="s">
+      <c r="H8" s="396" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="395" t="s">
+      <c r="I8" s="396" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="395" t="s">
+      <c r="J8" s="396" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="395" t="s">
+      <c r="K8" s="396" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="395" t="s">
+      <c r="L8" s="396" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="395" t="s">
+      <c r="M8" s="396" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="395" t="s">
+      <c r="N8" s="396" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="395" t="s">
+      <c r="O8" s="396" t="s">
         <v>92</v>
       </c>
       <c r="P8" s="13"/>
-      <c r="Q8" s="395" t="s">
+      <c r="Q8" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="395" t="s">
+      <c r="R8" s="396" t="s">
         <v>36</v>
       </c>
-      <c r="S8" s="395" t="s">
+      <c r="S8" s="396" t="s">
         <v>37</v>
       </c>
-      <c r="T8" s="391" t="s">
+      <c r="T8" s="407" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="391"/>
-      <c r="V8" s="391"/>
-      <c r="W8" s="391" t="s">
+      <c r="U8" s="407"/>
+      <c r="V8" s="407"/>
+      <c r="W8" s="407" t="s">
         <v>5</v>
       </c>
-      <c r="X8" s="391"/>
-      <c r="Y8" s="391"/>
-      <c r="Z8" s="391" t="s">
+      <c r="X8" s="407"/>
+      <c r="Y8" s="407"/>
+      <c r="Z8" s="407" t="s">
         <v>7</v>
       </c>
-      <c r="AA8" s="391"/>
-      <c r="AB8" s="391"/>
-      <c r="AC8" s="391" t="s">
+      <c r="AA8" s="407"/>
+      <c r="AB8" s="407"/>
+      <c r="AC8" s="407" t="s">
         <v>8</v>
       </c>
-      <c r="AD8" s="391"/>
-      <c r="AE8" s="391"/>
-      <c r="AF8" s="391" t="s">
+      <c r="AD8" s="407"/>
+      <c r="AE8" s="407"/>
+      <c r="AF8" s="407" t="s">
         <v>9</v>
       </c>
-      <c r="AG8" s="391"/>
-      <c r="AH8" s="391"/>
-      <c r="AI8" s="391" t="s">
+      <c r="AG8" s="407"/>
+      <c r="AH8" s="407"/>
+      <c r="AI8" s="407" t="s">
         <v>10</v>
       </c>
-      <c r="AJ8" s="391"/>
-      <c r="AK8" s="391"/>
-      <c r="AL8" s="391" t="s">
+      <c r="AJ8" s="407"/>
+      <c r="AK8" s="407"/>
+      <c r="AL8" s="407" t="s">
         <v>11</v>
       </c>
-      <c r="AM8" s="391"/>
-      <c r="AN8" s="391"/>
-      <c r="AO8" s="391" t="s">
+      <c r="AM8" s="407"/>
+      <c r="AN8" s="407"/>
+      <c r="AO8" s="407" t="s">
         <v>12</v>
       </c>
-      <c r="AP8" s="391"/>
-      <c r="AQ8" s="391"/>
-      <c r="AR8" s="391" t="s">
+      <c r="AP8" s="407"/>
+      <c r="AQ8" s="407"/>
+      <c r="AR8" s="407" t="s">
         <v>13</v>
       </c>
-      <c r="AS8" s="391"/>
-      <c r="AT8" s="391"/>
-      <c r="AU8" s="391" t="s">
+      <c r="AS8" s="407"/>
+      <c r="AT8" s="407"/>
+      <c r="AU8" s="407" t="s">
         <v>14</v>
       </c>
-      <c r="AV8" s="391"/>
-      <c r="AW8" s="391"/>
-    </row>
-    <row r="9" spans="1:49" ht="25.15" customHeight="1">
+      <c r="AV8" s="407"/>
+      <c r="AW8" s="407"/>
+    </row>
+    <row r="9" spans="1:49" ht="25.2" customHeight="1">
       <c r="A9" s="57" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="400"/>
-      <c r="D9" s="396"/>
-      <c r="E9" s="396"/>
-      <c r="F9" s="396"/>
-      <c r="G9" s="396"/>
-      <c r="H9" s="396"/>
-      <c r="I9" s="396"/>
-      <c r="J9" s="396"/>
-      <c r="K9" s="396"/>
-      <c r="L9" s="396"/>
-      <c r="M9" s="396"/>
-      <c r="N9" s="396"/>
-      <c r="O9" s="396"/>
+      <c r="C9" s="411"/>
+      <c r="D9" s="398"/>
+      <c r="E9" s="398"/>
+      <c r="F9" s="398"/>
+      <c r="G9" s="398"/>
+      <c r="H9" s="398"/>
+      <c r="I9" s="398"/>
+      <c r="J9" s="398"/>
+      <c r="K9" s="398"/>
+      <c r="L9" s="398"/>
+      <c r="M9" s="398"/>
+      <c r="N9" s="398"/>
+      <c r="O9" s="398"/>
       <c r="P9" s="13" t="s">
         <v>3</v>
       </c>
@@ -12374,7 +12380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="22.9" customHeight="1">
+    <row r="10" spans="1:49" ht="22.95" customHeight="1">
       <c r="A10" s="176" t="str">
         <f>'[1]บางบัวทอง-ผลิต'!C12</f>
         <v>องุ่นดำไร้เมล็ด 150 กรัม x36P</v>
@@ -12562,7 +12568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="22.9" customHeight="1">
+    <row r="11" spans="1:49" ht="22.95" customHeight="1">
       <c r="A11" s="176" t="str">
         <f>'[1]บางบัวทอง-ผลิต'!C14</f>
         <v>องุ่นแดงนอกมีเมล็ด 200 กรัม x 32 P</v>
@@ -12750,7 +12756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="22.9" customHeight="1">
+    <row r="12" spans="1:49" ht="22.95" customHeight="1">
       <c r="A12" s="179" t="s">
         <v>126</v>
       </c>
@@ -12937,7 +12943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="22.9" customHeight="1">
+    <row r="13" spans="1:49" ht="22.95" customHeight="1">
       <c r="A13" s="179" t="s">
         <v>142</v>
       </c>
@@ -13124,7 +13130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="22.9" customHeight="1">
+    <row r="14" spans="1:49" ht="22.95" customHeight="1">
       <c r="A14" s="179" t="s">
         <v>141</v>
       </c>
@@ -13218,7 +13224,7 @@
       <c r="AV14" s="9"/>
       <c r="AW14" s="10"/>
     </row>
-    <row r="15" spans="1:49" ht="22.9" customHeight="1">
+    <row r="15" spans="1:49" ht="22.95" customHeight="1">
       <c r="A15" s="179" t="s">
         <v>62</v>
       </c>
@@ -13405,7 +13411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="22.9" customHeight="1">
+    <row r="16" spans="1:49" ht="22.95" customHeight="1">
       <c r="A16" s="180" t="s">
         <v>140</v>
       </c>
@@ -13499,7 +13505,7 @@
       <c r="AV16" s="9"/>
       <c r="AW16" s="10"/>
     </row>
-    <row r="17" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="17" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A17" s="181" t="s">
         <v>63</v>
       </c>
@@ -13593,7 +13599,7 @@
       <c r="AV17" s="32"/>
       <c r="AW17" s="33"/>
     </row>
-    <row r="18" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="18" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A18" s="179" t="s">
         <v>104</v>
       </c>
@@ -13687,7 +13693,7 @@
       <c r="AV18" s="32"/>
       <c r="AW18" s="33"/>
     </row>
-    <row r="19" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="19" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A19" s="181" t="s">
         <v>129</v>
       </c>
@@ -13781,7 +13787,7 @@
       <c r="AV19" s="32"/>
       <c r="AW19" s="33"/>
     </row>
-    <row r="20" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="20" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A20" s="181" t="s">
         <v>64</v>
       </c>
@@ -13875,7 +13881,7 @@
       <c r="AV20" s="32"/>
       <c r="AW20" s="33"/>
     </row>
-    <row r="21" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="21" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A21" s="181" t="s">
         <v>133</v>
       </c>
@@ -13969,7 +13975,7 @@
       <c r="AV21" s="32"/>
       <c r="AW21" s="33"/>
     </row>
-    <row r="22" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="22" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A22" s="181" t="s">
         <v>109</v>
       </c>
@@ -14063,7 +14069,7 @@
       <c r="AV22" s="32"/>
       <c r="AW22" s="33"/>
     </row>
-    <row r="23" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="23" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A23" s="181" t="s">
         <v>131</v>
       </c>
@@ -14157,7 +14163,7 @@
       <c r="AV23" s="32"/>
       <c r="AW23" s="33"/>
     </row>
-    <row r="24" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="24" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A24" s="181" t="s">
         <v>65</v>
       </c>
@@ -14251,7 +14257,7 @@
       <c r="AV24" s="32"/>
       <c r="AW24" s="33"/>
     </row>
-    <row r="25" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="25" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A25" s="180" t="s">
         <v>66</v>
       </c>
@@ -14345,7 +14351,7 @@
       <c r="AV25" s="32"/>
       <c r="AW25" s="33"/>
     </row>
-    <row r="26" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="26" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A26" s="179" t="s">
         <v>105</v>
       </c>
@@ -14439,7 +14445,7 @@
       <c r="AV26" s="32"/>
       <c r="AW26" s="33"/>
     </row>
-    <row r="27" spans="1:49" s="30" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="27" spans="1:49" s="30" customFormat="1" ht="19.95" customHeight="1">
       <c r="A27" s="179" t="s">
         <v>105</v>
       </c>
@@ -14533,11 +14539,11 @@
       <c r="AV27" s="32"/>
       <c r="AW27" s="33"/>
     </row>
-    <row r="28" spans="1:49" s="25" customFormat="1" ht="25.15" customHeight="1">
-      <c r="A28" s="404" t="s">
+    <row r="28" spans="1:49" s="25" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A28" s="408" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="404"/>
+      <c r="B28" s="408"/>
       <c r="C28" s="109">
         <f>SUM(C10:C27)</f>
         <v>0</v>
@@ -14596,11 +14602,11 @@
       <c r="S28" s="24"/>
     </row>
     <row r="29" spans="1:49" ht="21" customHeight="1">
-      <c r="A29" s="398" t="s">
+      <c r="A29" s="409" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="398"/>
-      <c r="C29" s="398"/>
+      <c r="B29" s="409"/>
+      <c r="C29" s="409"/>
       <c r="D29" s="108">
         <f>SUM(T10:T16)</f>
         <v>0</v>
@@ -14783,7 +14789,7 @@
       <c r="C33" s="11"/>
     </row>
     <row r="34" spans="1:19" ht="18" customHeight="1">
-      <c r="A34" s="406" t="s">
+      <c r="A34" s="404" t="s">
         <v>44</v>
       </c>
       <c r="B34" s="15" t="s">
@@ -14801,7 +14807,7 @@
       </c>
     </row>
     <row r="35" spans="1:19" ht="18" customHeight="1">
-      <c r="A35" s="406"/>
+      <c r="A35" s="404"/>
       <c r="B35" s="15" t="s">
         <v>46</v>
       </c>
@@ -14818,7 +14824,7 @@
       <c r="I35" s="16"/>
     </row>
     <row r="36" spans="1:19" ht="18" customHeight="1">
-      <c r="A36" s="406"/>
+      <c r="A36" s="404"/>
       <c r="B36" s="405" t="s">
         <v>48</v>
       </c>
@@ -14832,7 +14838,7 @@
       </c>
     </row>
     <row r="37" spans="1:19" ht="18" customHeight="1">
-      <c r="A37" s="406"/>
+      <c r="A37" s="404"/>
       <c r="B37" s="405" t="s">
         <v>47</v>
       </c>
@@ -14845,7 +14851,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="18" customHeight="1">
-      <c r="A38" s="406"/>
+      <c r="A38" s="404"/>
       <c r="B38" s="405" t="s">
         <v>19</v>
       </c>
@@ -14859,7 +14865,7 @@
       </c>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1">
-      <c r="A39" s="406" t="s">
+      <c r="A39" s="404" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -14877,7 +14883,7 @@
       </c>
     </row>
     <row r="40" spans="1:19" ht="18" customHeight="1">
-      <c r="A40" s="406"/>
+      <c r="A40" s="404"/>
       <c r="B40" s="15" t="s">
         <v>46</v>
       </c>
@@ -14893,7 +14899,7 @@
       </c>
     </row>
     <row r="41" spans="1:19" ht="18" customHeight="1">
-      <c r="A41" s="406"/>
+      <c r="A41" s="404"/>
       <c r="B41" s="405" t="s">
         <v>48</v>
       </c>
@@ -14907,7 +14913,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1">
-      <c r="A42" s="406"/>
+      <c r="A42" s="404"/>
       <c r="B42" s="405" t="s">
         <v>47</v>
       </c>
@@ -14919,8 +14925,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="25.15" customHeight="1">
-      <c r="A43" s="406"/>
+    <row r="43" spans="1:19" ht="25.2" customHeight="1">
+      <c r="A43" s="404"/>
       <c r="B43" s="405" t="s">
         <v>19</v>
       </c>
@@ -14933,68 +14939,68 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="25.15" customHeight="1">
+    <row r="44" spans="1:19" ht="25.2" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
       <c r="E44" s="12"/>
     </row>
-    <row r="45" spans="1:19" ht="4.9000000000000004" customHeight="1">
+    <row r="45" spans="1:19" ht="4.95" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="E45" s="12"/>
     </row>
     <row r="46" spans="1:19" ht="21" customHeight="1">
-      <c r="A46" s="406" t="s">
+      <c r="A46" s="404" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="412"/>
+      <c r="B46" s="406"/>
       <c r="C46" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="406" t="s">
+      <c r="D46" s="404" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="406"/>
-      <c r="F46" s="406"/>
-      <c r="G46" s="406" t="s">
+      <c r="E46" s="404"/>
+      <c r="F46" s="404"/>
+      <c r="G46" s="404" t="s">
         <v>54</v>
       </c>
-      <c r="H46" s="406"/>
-      <c r="I46" s="406"/>
-      <c r="J46" s="401" t="s">
+      <c r="H46" s="404"/>
+      <c r="I46" s="404"/>
+      <c r="J46" s="391" t="s">
         <v>55</v>
       </c>
-      <c r="K46" s="402"/>
-      <c r="L46" s="402"/>
-      <c r="M46" s="402"/>
-      <c r="N46" s="402"/>
-      <c r="O46" s="403"/>
+      <c r="K46" s="392"/>
+      <c r="L46" s="392"/>
+      <c r="M46" s="392"/>
+      <c r="N46" s="392"/>
+      <c r="O46" s="393"/>
       <c r="P46" s="17"/>
-      <c r="Q46" s="413" t="s">
+      <c r="Q46" s="394" t="s">
         <v>60</v>
       </c>
-      <c r="R46" s="414"/>
+      <c r="R46" s="395"/>
     </row>
     <row r="47" spans="1:19" ht="21" customHeight="1">
-      <c r="A47" s="407" t="s">
+      <c r="A47" s="399" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="408"/>
+      <c r="B47" s="400"/>
       <c r="C47" s="14"/>
-      <c r="D47" s="401"/>
-      <c r="E47" s="402"/>
-      <c r="F47" s="403"/>
-      <c r="G47" s="401"/>
-      <c r="H47" s="402"/>
-      <c r="I47" s="403"/>
-      <c r="J47" s="409"/>
-      <c r="K47" s="410"/>
-      <c r="L47" s="410"/>
-      <c r="M47" s="410"/>
-      <c r="N47" s="410"/>
-      <c r="O47" s="411"/>
+      <c r="D47" s="391"/>
+      <c r="E47" s="392"/>
+      <c r="F47" s="393"/>
+      <c r="G47" s="391"/>
+      <c r="H47" s="392"/>
+      <c r="I47" s="393"/>
+      <c r="J47" s="401"/>
+      <c r="K47" s="402"/>
+      <c r="L47" s="402"/>
+      <c r="M47" s="402"/>
+      <c r="N47" s="402"/>
+      <c r="O47" s="403"/>
       <c r="P47" s="18"/>
       <c r="Q47" s="22" t="s">
         <v>56</v>
@@ -15005,23 +15011,23 @@
       <c r="S47" s="5"/>
     </row>
     <row r="48" spans="1:19" ht="21" customHeight="1">
-      <c r="A48" s="407" t="s">
+      <c r="A48" s="399" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="408"/>
+      <c r="B48" s="400"/>
       <c r="C48" s="14"/>
-      <c r="D48" s="401"/>
-      <c r="E48" s="402"/>
-      <c r="F48" s="403"/>
-      <c r="G48" s="401"/>
-      <c r="H48" s="402"/>
-      <c r="I48" s="403"/>
-      <c r="J48" s="409"/>
-      <c r="K48" s="410"/>
-      <c r="L48" s="410"/>
-      <c r="M48" s="410"/>
-      <c r="N48" s="410"/>
-      <c r="O48" s="411"/>
+      <c r="D48" s="391"/>
+      <c r="E48" s="392"/>
+      <c r="F48" s="393"/>
+      <c r="G48" s="391"/>
+      <c r="H48" s="392"/>
+      <c r="I48" s="393"/>
+      <c r="J48" s="401"/>
+      <c r="K48" s="402"/>
+      <c r="L48" s="402"/>
+      <c r="M48" s="402"/>
+      <c r="N48" s="402"/>
+      <c r="O48" s="403"/>
       <c r="P48" s="18"/>
       <c r="Q48" s="22" t="s">
         <v>58</v>
@@ -15032,23 +15038,23 @@
       <c r="S48" s="19"/>
     </row>
     <row r="49" spans="1:19" ht="21" customHeight="1">
-      <c r="A49" s="407" t="s">
+      <c r="A49" s="399" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="407"/>
+      <c r="B49" s="399"/>
       <c r="C49" s="14"/>
-      <c r="D49" s="401"/>
-      <c r="E49" s="402"/>
-      <c r="F49" s="403"/>
-      <c r="G49" s="401"/>
-      <c r="H49" s="402"/>
-      <c r="I49" s="403"/>
-      <c r="J49" s="409"/>
-      <c r="K49" s="410"/>
-      <c r="L49" s="410"/>
-      <c r="M49" s="410"/>
-      <c r="N49" s="410"/>
-      <c r="O49" s="411"/>
+      <c r="D49" s="391"/>
+      <c r="E49" s="392"/>
+      <c r="F49" s="393"/>
+      <c r="G49" s="391"/>
+      <c r="H49" s="392"/>
+      <c r="I49" s="393"/>
+      <c r="J49" s="401"/>
+      <c r="K49" s="402"/>
+      <c r="L49" s="402"/>
+      <c r="M49" s="402"/>
+      <c r="N49" s="402"/>
+      <c r="O49" s="403"/>
       <c r="P49" s="18"/>
       <c r="Q49" s="20" t="s">
         <v>59</v>
@@ -15065,16 +15071,41 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="Q46:R46"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="J46:O46"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="Q3:S4"/>
+    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D7:S7"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="AO8:AQ8"/>
+    <mergeCell ref="AR8:AT8"/>
+    <mergeCell ref="AU8:AW8"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="W8:Y8"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AF8:AH8"/>
+    <mergeCell ref="AI8:AK8"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -15091,41 +15122,16 @@
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="AL8:AN8"/>
-    <mergeCell ref="AO8:AQ8"/>
-    <mergeCell ref="AR8:AT8"/>
-    <mergeCell ref="AU8:AW8"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="W8:Y8"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AF8:AH8"/>
-    <mergeCell ref="AI8:AK8"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D7:S7"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="Q3:S4"/>
-    <mergeCell ref="A6:B8"/>
-    <mergeCell ref="C6:S6"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="Q46:R46"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="J46:O46"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15136,15 +15142,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D82F59-BE09-4F9C-81D2-26BAD193372A}">
   <dimension ref="D11:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="33.75" customWidth="1"/>
+    <col min="5" max="5" width="33.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="11" spans="4:6" ht="15" thickBot="1"/>
+    <row r="11" spans="4:6" ht="14.4" thickBot="1"/>
     <row r="12" spans="4:6" s="71" customFormat="1">
-      <c r="D12" s="415" t="s">
+      <c r="D12" s="416" t="s">
         <v>119</v>
       </c>
       <c r="E12" s="72" t="s">
@@ -15153,20 +15159,20 @@
       <c r="F12" s="73"/>
     </row>
     <row r="13" spans="4:6" s="71" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="D13" s="416"/>
+      <c r="D13" s="417"/>
       <c r="E13" s="74" t="s">
         <v>125</v>
       </c>
       <c r="F13" s="73"/>
     </row>
-    <row r="14" spans="4:6" s="71" customFormat="1" ht="15" thickBot="1">
-      <c r="D14" s="417"/>
+    <row r="14" spans="4:6" s="71" customFormat="1" ht="14.4" thickBot="1">
+      <c r="D14" s="418"/>
       <c r="E14" s="75" t="s">
         <v>121</v>
       </c>
       <c r="F14" s="73"/>
     </row>
-    <row r="15" spans="4:6" s="71" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+    <row r="15" spans="4:6" s="71" customFormat="1" ht="17.399999999999999" customHeight="1" thickBot="1">
       <c r="D15" s="76" t="s">
         <v>122</v>
       </c>
@@ -15175,7 +15181,7 @@
       </c>
       <c r="F15" s="73"/>
     </row>
-    <row r="16" spans="4:6" s="71" customFormat="1" ht="15" thickBot="1">
+    <row r="16" spans="4:6" s="71" customFormat="1" ht="14.4" thickBot="1">
       <c r="D16" s="76" t="s">
         <v>124</v>
       </c>
@@ -15184,7 +15190,7 @@
       </c>
       <c r="F16" s="73"/>
     </row>
-    <row r="17" spans="4:6" ht="23.25">
+    <row r="17" spans="4:6" ht="23.4">
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
       <c r="F17" s="30"/>
